--- a/outputs/seed_qa_simple/plastic_seed_qa_simple.xlsx
+++ b/outputs/seed_qa_simple/plastic_seed_qa_simple.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="seed_qa_simple" sheetId="1" r:id="R68a829b65784465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="seed_qa_simple" sheetId="1" r:id="R00eaf7d33b8742b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -372,11 +372,11 @@
     <x:col min="1" max="1" width="11.25" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="32.5" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="32.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="37.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="41.25" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="53.75" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="57.5" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="62.5" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="37.5" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="11.25" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="12.5" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="22.5" hidden="0" customWidth="1"/>
@@ -417,7 +417,7 @@
         <x:v>人工备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="82.5" customHeight="1">
+    <x:row r="2" ht="88.5" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>P001_Q01</x:v>
       </x:c>
@@ -425,22 +425,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：涂料就是会污染饮用水源区，应该直接废水是否会进入饮用水源保护区”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>Word批注/修改意见（第2条）写明：雷兆宇：涂料就是会污染饮用水源区，应该直接废水是否会进入饮用水源保护区</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...设地点 | 广东省佛山市顺德区杏坛镇海凌村海赞路19号四层之二；地理坐标 | （ 113 度 6 分 28.298秒， 22 度 47 分 57.226 秒）；国民经济行业类别 | C3389其他金属制日用品制造 | 建设项目行业类别 | 三十、金属制品业33-66 金属制日用品制造338（其他）；建设性质 | 新建（迁建）改建技改技术改造 | 建设项目申报情形 | 首次申报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；...</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I2" s="7" t="b">
         <x:v>1</x:v>
@@ -448,7 +448,7 @@
       <x:c r="J2" s="11" t="str"/>
       <x:c r="K2" s="11" t="str"/>
     </x:row>
-    <x:row r="3" ht="82.5" customHeight="1">
+    <x:row r="3" ht="88.5" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>P001_Q02</x:v>
       </x:c>
@@ -456,22 +456,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>废水去向与冷却水</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废水去向与冷却水相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：烘干废水是否应该进入喷淋塔”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
-        <x:v>Word批注/修改意见（第12条）写明：雷兆宇：烘干废水是否应该进入喷淋塔</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 100 | 环保投资（万元） | 10；环保投资占比（%） | 10 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H3" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I3" s="7" t="b">
         <x:v>1</x:v>
@@ -479,7 +479,7 @@
       <x:c r="J3" s="11" t="str"/>
       <x:c r="K3" s="11" t="str"/>
     </x:row>
-    <x:row r="4" ht="82.5" customHeight="1">
+    <x:row r="4" ht="88.5" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>P001_Q03</x:v>
       </x:c>
@@ -487,22 +487,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C4" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：不建议过低，否则可能堵塞活性炭”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
-        <x:v>Word批注/修改意见（第17条）写明：雷兆宇：不建议过低，否则可能堵塞活性炭</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1、工程组成 项目租赁一栋4层高的工业厂房中的第4层作为生产经营场所，一层厂房高7.5米，二、三、四层高5.5米，厂房总高度为24米，项目工程组成见下表。表2-1 本项目工程组成项目内容备注主体工程生产车间用于检查、上挂、包装等工序，面积约500m2；喷漆线，用于除尘、喷纳米油、烘干等工序，总面积500m2，包括喷房4m2，除尘房3m2，烘烤线493m2仓储工程仓库约500m2，储存原料和产品辅助工程办公室约100m2，供日常办公使用公用工程给排水系统供水来源为市政自来水，依托厂房的三级化粪池预处理后...</x:v>
       </x:c>
       <x:c r="H4" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I4" s="7" t="b">
         <x:v>1</x:v>
@@ -510,7 +510,7 @@
       <x:c r="J4" s="11" t="str"/>
       <x:c r="K4" s="11" t="str"/>
     </x:row>
-    <x:row r="5" ht="82.5" customHeight="1">
+    <x:row r="5" ht="88.5" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>P001_Q04</x:v>
       </x:c>
@@ -518,22 +518,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：项目不是化工项目为什么要提这一句话”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：项目不是化工项目为什么要提这一句话</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1、大气环境质量现状根据《关于调整顺德区环境空气质量功能区划的复函》（佛府办函[2014]494号），项目所在区域为环境空气质量功能二类区，执行《环境空气质量标准》（GB3095-2012）及2018年修改单中的二级标准。（1）基本污染物环境质量现状为评价项目所在地环境空气质量现状，引用佛山市生态环境局顺德分局发布的《2022年度佛山市顺德区环境质量状况公报》中的数据，项目所在区域基本污染物环境质量现状评价如下：表3-1 2022年顺德区（国控测点）环境空气质量现状评价表污染物年评价指标现状浓度标...</x:v>
       </x:c>
       <x:c r="H5" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报</x:v>
       </x:c>
       <x:c r="I5" s="7" t="b">
         <x:v>1</x:v>
@@ -541,7 +541,7 @@
       <x:c r="J5" s="11" t="str"/>
       <x:c r="K5" s="11" t="str"/>
     </x:row>
-    <x:row r="6" ht="82.5" customHeight="1">
+    <x:row r="6" ht="88.5" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>P001_Q05</x:v>
       </x:c>
@@ -549,22 +549,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
         <x:v>表4-1 废气污染源源强核算结果及治理设施相关参数一览表（表格）写明：...2以及广东省关于贯彻落实《工业炉窑大气污染综合治理方案》的实施意见 （粤环函【2019】1112号）重点区域排放限值的较严值臭气浓度GB14554-933、废气源强核算：（1）漆雾项目喷纳米油工序会产生少量漆雾，污染因子为颗粒物，参考《广东省家具制造行业挥发性有机废气治理技术指南》，喷涂过程中会有漆雾产生。本项目喷涂采用低压环保型喷枪，可减少漆量损耗。项目喷纳米油工序年工作1700h/a。...</x:v>
       </x:c>
       <x:c r="H6" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I6" s="7" t="b">
         <x:v>1</x:v>
@@ -572,7 +572,7 @@
       <x:c r="J6" s="11" t="str"/>
       <x:c r="K6" s="11" t="str"/>
     </x:row>
-    <x:row r="7" ht="82.5" customHeight="1">
+    <x:row r="7" ht="88.5" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>P001_Q06</x:v>
       </x:c>
@@ -580,22 +580,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C7" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...对产品进行喷涂处理柜子拉手120335mm*25mm*17mm*6mm0.025门拉手50825mm*45*35mm*20mm0.116总计300/////3、原辅材料及能源消耗 表2-3 本项目原辅料消耗一览表类别名称单位用量性状包装规格最大储存量 原辅材料抽屉拉手万个/年130固体/15柜子拉手万个/年120固体/15门拉手万个/年50固体/5水性纳米油吨/年14.91液体25kg/桶1.4洗枪水（酒精）吨/年0.036液体10kg/桶0.01纳米油用量估算：根据《涂装工艺与设备》中公式（如下）核算涂料用...</x:v>
+        <x:v>表4-1 废气污染源源强核算结果及治理设施相关参数一览表（表格）写明：...半年一次DB44/27-2001NOXSO2臭气浓度GB14554-93房门窗或通风口、其他开口（孔）等排放口外1mNMHCDB442367-2022有组织废气排气筒DA001TVOC半年一次DB442367-2022NMHCNOX广东省关于贯彻落实《工业炉窑大气污染综合治理方案》的实施意见 （粤环函【2019】1112号）重点区域排放限值SO2颗粒物DB442367-2022以及广东省关于贯彻落实《工业炉窑大气污染综合治理方案》的实施意见 （粤环函【2019】1112号）重点区域排放限值的较严值臭气浓度GB14554-933、废气源强核算：（1）漆雾项目喷纳米油工序会产生少量漆雾，污染...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H7" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I7" s="7" t="b">
         <x:v>1</x:v>
@@ -603,7 +603,7 @@
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
     </x:row>
-    <x:row r="8" ht="82.5" customHeight="1">
+    <x:row r="8" ht="88.5" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>P001_Q07</x:v>
       </x:c>
@@ -611,22 +611,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>废气收集风量与设计风量核算</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的集气罩尺寸、控制风速、收集点数量和风量计算过程，判断设计风量是否具有可复核性。</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查风量计算是否可复核。报告应说明收集点数量、罩口尺寸、控制风速或换气次数，并形成可追溯的设计风量。建议核查计算公式、取值依据、风机风量裕量和治理设施处理风量是否匹配。</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
-        <x:v>表4-1 废气污染源源强核算结果及治理设施相关参数一览表（表格）写明：...11.202①废气收集和处理措施a.废气收集措施方案项目喷漆线设置为全封闭设计，由独立除尘房、喷房和烘烤线组成，设计换气次数为12 次/小时，工作时间内保持整体密闭且负压抽风。...</x:v>
+        <x:v>表4-1 废气污染源源强核算结果及治理设施相关参数一览表（表格）写明：... 100%0.0360.211 合计1.7211.202①废气收集和处理措施a.废气收集措施方案项目喷漆线设置为全封闭设计，由独立除尘房、喷房和烘烤线组成，设计换气次数为12 次/小时，工作时间内保持整体密闭且负压抽风。...</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集风量与设计风量核算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I8" s="7" t="b">
         <x:v>1</x:v>
@@ -634,7 +634,7 @@
       <x:c r="J8" s="11" t="str"/>
       <x:c r="K8" s="11" t="str"/>
     </x:row>
-    <x:row r="9" ht="82.5" customHeight="1">
+    <x:row r="9" ht="88.5" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>P001_Q08</x:v>
       </x:c>
@@ -642,22 +642,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
-        <x:v>表4-1 废气污染源源强核算结果及治理设施相关参数一览表（表格）写明：...物 | 污染物产生 | 治理措施 | 污染物排放 | 排放时间（h）；核算方法 | 产生废气量(m³/h) | 产生量（t/a） | 产生速率（kg/h) | 收集效率（%） | 治理设施/治理工艺 | 去除效率（%） | 是否为可行技术 | 废气排放量(m³/h) | 排放量t/a | 排放速率kg/h | 排放浓度(mg/m³)；...</x:v>
+        <x:v>表4-1 废气污染源源强核算结果及治理设施相关参数一览表（表格）写明：...算使用原料用量t/a附着率%固含量%漆雾产生量t/a水性纳米油14.915023.71.767合计1.767 喷纳米油产生的漆雾经“水帘柜+喷淋塔+干式过滤器+二级活性炭”处理系统处理后通过经一根28m高的排气筒DA001排放。漆雾的产排情况见表4-7。（2）VOCs项目喷纳米油、烘干工序会产生有机废气，主要污染因子为VOCs。根据东莞市北测标准技术服务有限公司对水性纳米油的VOC含量测定，纳米油的VOCs产生系数如表5-7所示。项目喷纳米油、烘干工序年工作1700h/a。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I9" s="7" t="b">
         <x:v>1</x:v>
@@ -665,7 +665,7 @@
       <x:c r="J9" s="11" t="str"/>
       <x:c r="K9" s="11" t="str"/>
     </x:row>
-    <x:row r="10" ht="82.5" customHeight="1">
+    <x:row r="10" ht="88.5" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>P001_Q09</x:v>
       </x:c>
@@ -673,22 +673,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...活污水依托厂房的三级化粪池预处理后排入杏坛污水处理厂，尾水排入顺德支流废气喷纳米油漆雾、有机废气通过密闭车间整室收集，收集后经“水帘柜+喷淋塔+干式过滤器+二级活性炭”装置处理后通过28m排气筒（DA001）高空排放烘干有机废气通过密闭车间整室收集，收集后经“喷淋塔+干式过滤器+二级活性炭”装置处理后通过28m排气筒（DA001）高空排放燃烧废气通过与烘干有机废气一同收集排放噪声设备噪声厂房隔声、风机消声、设备减振固废生活垃圾定期交由环卫部门清理一般工业固体废物定点收集后交由一般固废处置单位处置危险废物暂存点...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...5水性纳米油吨/年14.91液体25kg/桶1.4洗枪水（酒精）吨/年0.036液体10kg/桶0.01纳米油用量估算：根据《涂装工艺与设备》中公式（如下）核算涂料用量：公式中：A——涂料的消耗量，g；B——涂膜厚度，um；C——涂膜密度，g/cm3；E——各涂装方法的涂料利用率，%；F——原涂料固体分，%；G——涂装面积，m2。通过上述公式计算可得建设单位纳米油用量详见表2-4。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I10" s="7" t="b">
         <x:v>1</x:v>
@@ -696,7 +696,7 @@
       <x:c r="J10" s="11" t="str"/>
       <x:c r="K10" s="11" t="str"/>
     </x:row>
-    <x:row r="11" ht="82.5" customHeight="1">
+    <x:row r="11" ht="88.5" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>P001_Q10</x:v>
       </x:c>
@@ -704,22 +704,22 @@
         <x:v>202403061513437166乐鲸修改意见.docx</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
-        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个</x:v>
+        <x:v>佛山市顺德区乐鲸科技有限公司年产五金拉手300万个新建项目</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>图件、附件、敏感点识别完整性</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的项目位置、厂界范围、敏感目标识别和附图附件，判断敏感点识别及图件附件是否完整。</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查敏感点和图件附件完整性。报告应明确项目位置、厂界范围、四至关系、环境保护目标和相关附图附件。建议核查敏感目标识别范围是否充分，附图、附件是否能支撑位置、管控单元和保护目标判断。</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
-        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：...和周边环境地面已做好水泥面硬化防渗措施，大气污染物产生量不大，经收集处理后高空排放，经扩散、降解等作用后，沉降到周边土壤环境的污染物较小。项目车间地面进行及废水暂存储池防渗处理，对存放液体原辅料的仓库、危废暂存点区域进行围闭，防止液体原辅料泄和液体危险废物漏到外围。因此项目不存在土壤、地下水环境污染途径，可不开展土壤、地下水环境质量现状调查。；污染物 | 年评价指标 | 现状浓度 | 标准值 | 占标率/% | 达标情况；SO2（ug/m3） | 年平均质量浓度 | 5 | 60 | 8.3 | 达标；...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：...能区划图，项目属于3类声功能区，执行《声环境质量标准》（GB3096-2008）3类标准，即昼间≤65dB(A)，夜间≤55dB(A)。项目周边50米范围内无声环境保护目标，无需开展声环境现状调查。4.生态环境项目用地范围内无生态环境保护目标，无需开展生态现状调查。5、电磁辐射项目不涉及电磁辐射，无需开展电磁辐射现状调查。6、土壤、地下水环境项目厂房和周边环境地面已做好水泥面硬化防渗措施，大气污染物产生量不大，经收集处理后高空排放，经扩散、降解等作用后，沉降到周边土壤环境的污染物较小。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；报告表编制要求；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I11" s="7" t="b">
         <x:v>1</x:v>
@@ -727,7 +727,7 @@
       <x:c r="J11" s="11" t="str"/>
       <x:c r="K11" s="11" t="str"/>
     </x:row>
-    <x:row r="12" ht="82.5" customHeight="1">
+    <x:row r="12" ht="88.5" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>P002_Q01</x:v>
       </x:c>
@@ -738,19 +738,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>废水去向与冷却水</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废水去向与冷却水相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：请根据最新换水换碳要求去更换水帘柜废水”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
-        <x:v>Word批注/修改意见（第4条）写明：雷兆宇：请根据最新换水换碳要求去更换水帘柜废水</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...赞路21号首层之二、二层之一、三层之五、四层之一、五层之一；地理坐标 | （E 113 度 13 分 25.94 秒，N 22 度 44 分 19.79 秒）；国民经济行业类别 | C2641涂料制造 | 建设项目行业类别 | 44涂料、油墨、颜料及类似产品制造264（单纯物理分离、物理提纯、混合、分装的）；建设性质 | 新建（迁建）□改建□扩建□技术改造 | 建设项目申报情形 | 首次申报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；...</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I12" s="7" t="b">
         <x:v>1</x:v>
@@ -758,7 +758,7 @@
       <x:c r="J12" s="11" t="str"/>
       <x:c r="K12" s="11" t="str"/>
     </x:row>
-    <x:row r="13" ht="82.5" customHeight="1">
+    <x:row r="13" ht="88.5" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>P002_Q02</x:v>
       </x:c>
@@ -769,19 +769,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：应该与试喷工序合并，该系数是喷漆+烘干工序的VOCs产生值，由于有水帘柜，需要干式过滤后再进活性炭。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
-        <x:v>Word批注/修改意见（第7条）写明：雷兆宇：应该与试喷工序合并，该系数是喷漆+烘干工序的VOCs产生值，由于有水帘柜，需要干式过滤后再进活性炭。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 200 | 环保投资（万元） | 30；环保投资占比（%） | 15 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I13" s="7" t="b">
         <x:v>1</x:v>
@@ -789,7 +789,7 @@
       <x:c r="J13" s="11" t="str"/>
       <x:c r="K13" s="11" t="str"/>
     </x:row>
-    <x:row r="14" ht="82.5" customHeight="1">
+    <x:row r="14" ht="88.5" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>P002_Q03</x:v>
       </x:c>
@@ -800,19 +800,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：用途”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：用途</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1、工程组成及平面布置 项目租用一栋五层工业厂房作为生产经营场所，所在建筑每层高度约为5m。厂房占地300m2，租用的建筑面积合计为1440m2。厂房内一层为成品仓（240m2）、二层为办公室（300m2）、三层为实验室（300m2）、四层为原辅料仓（300m2）、五层为生产车间（300m2），具体平面布置图见附图4。项目工程组成见下表：表2-1 本项目工程组成项目内容备注主体工程生产车间位于5层，约300m2，用于水性涂料的生产，主要工序有投料、分散、研磨、调漆、包装等仓储工程原辅料仓位于4层，约3...</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I14" s="7" t="b">
         <x:v>1</x:v>
@@ -820,7 +820,7 @@
       <x:c r="J14" s="11" t="str"/>
       <x:c r="K14" s="11" t="str"/>
     </x:row>
-    <x:row r="15" ht="82.5" customHeight="1">
+    <x:row r="15" ht="88.5" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>P002_Q04</x:v>
       </x:c>
@@ -831,19 +831,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
-        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...OC、臭气浓度半年无组织排放监测点位监测指标监测频次厂界颗粒物、TVOC、臭气浓度半年房门窗或通风口、其他开口（孔）等排放口外1mNMHC半年2、废气污染物排放源强核算过程（1）颗粒物◇投料粉尘项目生产过程中的投料工序所加入的颜填料多数为粉末状固体，其投料过程会产生粉尘，主要污染因子为颗粒物。粉尘的产生系数参考《排放源统计调查产排污核算方法和系数手册》（生态环境部公告2021年第24号）的2641涂料制造行业系数手册-2641涂料制造行业系数表中的水性工业涂料颗粒物产污系数：0.1kg/t-产品。...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1、大气环境质量现状本项目选址位于佛山市顺德区杏坛镇，根据《顺德区生态环境保护规划（2021-2025年）》，顺德区全境为大气环境二类区，本项目所在地属环境空气质量二类功能区，区域的环境空气质量执行国家《环境空气质量标准》（GB3095-2012）及2018年修改单中的二级标准。（1）常规污染物环境质量现状根据《佛山市生态环境局顺德分局关于发布2021年度佛山市顺德区环境质量状况公报的通知》，该地区空气质量执行《环境空气质量标准》（GB3095-2012）及2018年修改单中的二级标准，基本污染物...</x:v>
       </x:c>
       <x:c r="H15" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报</x:v>
       </x:c>
       <x:c r="I15" s="7" t="b">
         <x:v>1</x:v>
@@ -851,7 +851,7 @@
       <x:c r="J15" s="11" t="str"/>
       <x:c r="K15" s="11" t="str"/>
     </x:row>
-    <x:row r="16" ht="82.5" customHeight="1">
+    <x:row r="16" ht="88.5" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>P002_Q05</x:v>
       </x:c>
@@ -862,19 +862,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F16" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
-        <x:v>五、环境保护措施监督检查清单（表格）写明：... 通过集气管道接入分散缸顶部设置的排气口进行收集，收集后与有机废气统一通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放 | 《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）；打样喷涂漆雾（有组织）（排气筒DA001） | 颗粒物 | 通过水帘柜进行打样室的整室收集，收集后与有机废气统一通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放 | 《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）；...</x:v>
+        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...◇投料粉尘项目生产过程中的投料工序所加入的颜填料多数为粉末状固体，其投料过程会产生粉尘，主要污染因子为颗粒物。粉尘的产生系数参考《排放源统计调查产排污核算方法和系数手册》（生态环境部公告2021年第24号）的2641涂料制造行业系数手册-2641涂料制造行业系数表中的水性工业涂料颗粒物产污系数：0.1kg/t-产品。项目水性涂料的产量为2400t/a；水性涂料测试量约为产量的0.05%，即为1.2t/a。项目生产车间投料工序年工作300小时；实验室投料工序年工作150小时。经计算，项目投料过程颗粒物的产生量为0.240t/a，产生速率为0.801kg/h。...</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I16" s="7" t="b">
         <x:v>1</x:v>
@@ -882,7 +882,7 @@
       <x:c r="J16" s="11" t="str"/>
       <x:c r="K16" s="11" t="str"/>
     </x:row>
-    <x:row r="17" ht="82.5" customHeight="1">
+    <x:row r="17" ht="88.5" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>P002_Q06</x:v>
       </x:c>
@@ -893,19 +893,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...过集气管道与废气处理系统连接，收集后的粉尘通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放打样喷涂漆雾、烘干有机废气打样间密闭设置，通过水帘柜进行整室收集，与生产车间收集的废气一起通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放分散、研磨和调漆有机废气研磨机为密闭设备，进出料管道与分散缸相连，分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的有机废气通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）...</x:v>
+        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...OC、臭气浓度半年无组织排放监测点位监测指标监测频次厂界颗粒物、TVOC、臭气浓度半年房门窗或通风口、其他开口（孔）等排放口外1mNMHC半年2、废气污染物排放源强核算过程（1）颗粒物◇投料粉尘项目生产过程中的投料工序所加入的颜填料多数为粉末状固体，其投料过程会产生粉尘，主要污染因子为颗粒物。粉尘的产生系数参考《排放源统计调查产排污核算方法和系数手册》（生态环境部公告2021年第24号）的2641涂料制造行业系数手册-2641涂料制造行业系数表中的水性工业涂料颗粒物产污系数：0.1kg/t-产品。项目水性涂料的产量为2400t/a；水性涂料测试量约为产量的0.05%，即为1.2t/a。...</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I17" s="7" t="b">
         <x:v>1</x:v>
@@ -913,7 +913,7 @@
       <x:c r="J17" s="11" t="str"/>
       <x:c r="K17" s="11" t="str"/>
     </x:row>
-    <x:row r="18" ht="82.5" customHeight="1">
+    <x:row r="18" ht="88.5" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>P002_Q07</x:v>
       </x:c>
@@ -924,19 +924,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E18" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F18" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
-        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...。经计算，项目投料过程颗粒物的产生量为0.240t/a，产生速率为0.801kg/h。要求项目正式生产的投料粉尘通过集气管道接入分散缸顶部设置的排气口进行收集，收集效率可达90%。收集后与有机废气统一通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放，其中“滤芯除尘器”对粉尘的处理效率可达99%。实验室的粉尘通过车间无组织排放。◇打样喷涂漆雾项目打样喷涂过程会产生少量漆雾，主要污染因子为颗粒物。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...收处理有限公司进行处理。废气投料粉尘分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的粉尘通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放打样喷涂漆雾、烘干有机废气打样间密闭设置，通过水帘柜进行整室收集，与生产车间收集的废气一起通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放分散、研磨和调漆有机废气研磨机为密闭设备，进出料管道与分散缸相连，分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的有机废气通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放噪声设备噪声...</x:v>
       </x:c>
       <x:c r="H18" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I18" s="7" t="b">
         <x:v>1</x:v>
@@ -944,7 +944,7 @@
       <x:c r="J18" s="11" t="str"/>
       <x:c r="K18" s="11" t="str"/>
     </x:row>
-    <x:row r="19" ht="82.5" customHeight="1">
+    <x:row r="19" ht="88.5" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>P002_Q08</x:v>
       </x:c>
@@ -955,19 +955,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D19" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>废气收集风量与设计风量核算</x:v>
       </x:c>
       <x:c r="E19" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的集气罩尺寸、控制风速、收集点数量和风量计算过程，判断设计风量是否具有可复核性。</x:v>
       </x:c>
       <x:c r="F19" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查风量计算是否可复核。报告应说明收集点数量、罩口尺寸、控制风速或换气次数，并形成可追溯的设计风量。建议核查计算公式、取值依据、风机风量裕量和治理设施处理风量是否匹配。</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...拟定期委托佛山市顺德区绿点废水回收处理有限公司进行处理。废气投料粉尘分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的粉尘通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放打样喷涂漆雾、烘干有机废气打样间密闭设置，通过水帘柜进行整室收集，与生产车间收集的废气一起通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放分散、研磨和调漆有机废气研磨机为密闭设备，进出料管道与分散缸相连，分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收...</x:v>
+        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：运营期环境影响和保护措施 | 表4-3 项目排气口基本情况表工序污染物排气筒参数排放口类型地理坐标编号废气量（m3/h）排放时间（h）高度（m）内径（m）温度（℃）投料、分散、研磨、调漆、打样喷涂和烘干颗粒物、TVOCDA001200002400300.825一般排放口X：113.224010Y：22.738813表4-4 废气污染源监测点位、监测指标及监测频次一览表有组织排放生产单元监测点位监测指标监测频次投料、分散、研磨、调漆、喷涂和烘干排气口DA001颗粒物、TVOC、臭气浓度半年无组织排放监测点位监测指标监测频次厂界颗粒物、TVOC、臭气浓度半年房门窗或通风口、其他开口（孔）等排放口外...</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集风量与设计风量核算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I19" s="7" t="b">
         <x:v>1</x:v>
@@ -975,7 +975,7 @@
       <x:c r="J19" s="11" t="str"/>
       <x:c r="K19" s="11" t="str"/>
     </x:row>
-    <x:row r="20" ht="82.5" customHeight="1">
+    <x:row r="20" ht="88.5" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>P002_Q09</x:v>
       </x:c>
@@ -986,19 +986,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E20" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F20" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...能力为2t/d，自建废水处理站拟采用“物化沉淀＋生化处理+过滤”的处理工艺，清洗废水经自建废水处理站处理后可全部回用作清洗用水，每半年更换一次清洗废水。清洗废水暂存于专用储水罐，拟定期委托佛山市顺德区绿点废水回收处理有限公司进行处理。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...罐，拟定期委托佛山市顺德区绿点废水回收处理有限公司进行处理。废气投料粉尘分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的粉尘通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放打样喷涂漆雾、烘干有机废气打样间密闭设置，通过水帘柜进行整室收集，与生产车间收集的废气一起通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放分散、研磨和调漆有机废气研磨机为密闭设备，进出料管道与分散缸相连，分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的有机废气通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H20" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I20" s="7" t="b">
         <x:v>1</x:v>
@@ -1006,7 +1006,7 @@
       <x:c r="J20" s="11" t="str"/>
       <x:c r="K20" s="11" t="str"/>
     </x:row>
-    <x:row r="21" ht="82.5" customHeight="1">
+    <x:row r="21" ht="88.5" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>P002_Q10</x:v>
       </x:c>
@@ -1017,19 +1017,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D21" s="6" t="str">
-        <x:v>总量控制</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E21" s="6" t="str">
-        <x:v>请根据报告中的VOCs总量控制指标和替代来源，判断总量控制论证是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F21" s="6" t="str">
-        <x:v>判断：需核查总量控制指标和替代来源。依据：报告涉及VOCs总量、替代来源或总量指标。审核意见：建议检查总量核算是否与源强排放量一致，替代来源或削减来源是否有明确证据。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
-        <x:v>六、结论（表格）写明：...= 3 \* GB3 \* MERGEFORMAT ③ | 本项目排放量（固体废物产生量） = 4 \* GB3 \* MERGEFORMAT ④ | 以新带老削减量（新建项目不填） = 5 \* GB3 \* MERGEFORMAT ⑤ | 本项目建成后全厂排放量（固体废物产生量） = 6 \* GB3 \* MERGEFORMAT ⑥ | 变化量 = 7 \* GB3 \* MERGEFORMAT ⑦；...</x:v>
+        <x:v>五、环境保护措施监督检查清单（表格）写明：... 通过集气管道接入分散缸顶部设置的排气口进行收集，收集后与有机废气统一通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放 | 《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）；打样喷涂漆雾（有组织）（排气筒DA001） | 颗粒物 | 通过水帘柜进行打样室的整室收集，收集后与有机废气统一通过“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放 | 《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）；...</x:v>
       </x:c>
       <x:c r="H21" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；地方政策库；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I21" s="7" t="b">
         <x:v>1</x:v>
@@ -1037,7 +1037,7 @@
       <x:c r="J21" s="11" t="str"/>
       <x:c r="K21" s="11" t="str"/>
     </x:row>
-    <x:row r="22" ht="82.5" customHeight="1">
+    <x:row r="22" ht="88.5" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>P003_Q01</x:v>
       </x:c>
@@ -1048,19 +1048,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D22" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E22" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F22" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：补充佛山市生态环境局关于印发《佛山市挥发性有机物排污总量指标精细化管理工作方案（试行）》的函相符性分析”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：补充佛山市生态环境局关于印发《佛山市挥发性有机物排污总量指标精细化管理工作方案（试行）》的函相符性分析</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...赞路21号首层之二、二层之一、三层之五、四层之一、五层之一；地理坐标 | （E 113 度 13 分 25.94 秒，N 22 度 44 分 19.79 秒）；国民经济行业类别 | C2641涂料制造 | 建设项目行业类别 | 44涂料、油墨、颜料及类似产品制造264（单纯物理分离、物理提纯、混合、分装的）；建设性质 | 新建（迁建）□改建□扩建□技术改造 | 建设项目申报情形 | 首次申报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；...</x:v>
       </x:c>
       <x:c r="H22" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I22" s="7" t="b">
         <x:v>1</x:v>
@@ -1068,7 +1068,7 @@
       <x:c r="J22" s="11" t="str"/>
       <x:c r="K22" s="11" t="str"/>
     </x:row>
-    <x:row r="23" ht="82.5" customHeight="1">
+    <x:row r="23" ht="88.5" customHeight="1">
       <x:c r="A23" s="6" t="str">
         <x:v>P003_Q02</x:v>
       </x:c>
@@ -1079,19 +1079,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E23" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集效率与处理效率相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F23" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：是否合理？先通过水帘柜，气体会粘到水汽，是否影响滤芯除尘器的处理效率”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
-        <x:v>Word批注/修改意见（第5条）写明：雷兆宇：是否合理？先通过水帘柜，气体会粘到水汽，是否影响滤芯除尘器的处理效率</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 200 | 环保投资（万元） | 30；环保投资占比（%） | 15 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H23" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I23" s="7" t="b">
         <x:v>1</x:v>
@@ -1099,7 +1099,7 @@
       <x:c r="J23" s="11" t="str"/>
       <x:c r="K23" s="11" t="str"/>
     </x:row>
-    <x:row r="24" ht="82.5" customHeight="1">
+    <x:row r="24" ht="88.5" customHeight="1">
       <x:c r="A24" s="6" t="str">
         <x:v>P003_Q03</x:v>
       </x:c>
@@ -1110,19 +1110,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D24" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E24" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F24" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：这不能处理喷涂废气吧？”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
-        <x:v>Word批注/修改意见（第2条）写明：雷兆宇：这不能处理喷涂废气吧？</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1、工程组成及平面布置 项目租用一栋五层工业厂房作为生产经营场所，所在建筑每层高度约为5m。厂房占地300m2，租用的建筑面积合计为1440m2。厂房内一层为成品仓（240m2）、二层为办公室（300m2）、三层为实验室（300m2）、四层为原辅料仓（300m2）、五层为生产车间（300m2），具体平面布置图见附图4。项目工程组成见下表：表2-1 本项目工程组成项目内容备注主体工程生产车间位于5层，约300m2，用于水性涂料的生产，主要工序有投料、分散、研磨、调漆、包装等仓储工程原辅料仓位于4层，约3...</x:v>
       </x:c>
       <x:c r="H24" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I24" s="7" t="b">
         <x:v>1</x:v>
@@ -1130,7 +1130,7 @@
       <x:c r="J24" s="11" t="str"/>
       <x:c r="K24" s="11" t="str"/>
     </x:row>
-    <x:row r="25" ht="82.5" customHeight="1">
+    <x:row r="25" ht="88.5" customHeight="1">
       <x:c r="A25" s="6" t="str">
         <x:v>P003_Q04</x:v>
       </x:c>
@@ -1141,19 +1141,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D25" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E25" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F25" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G25" s="6" t="str">
-        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...OC、臭气浓度半年无组织排放监测点位监测指标监测频次厂界颗粒物、TVOC、臭气浓度半年房门窗或通风口、其他开口（孔）等排放口外1mNMHC半年2、废气污染物排放源强核算过程（1）颗粒物◇投料粉尘项目生产过程中的投料工序所加入的颜填料多数为粉末状固体，其投料过程会产生粉尘，主要污染因子为颗粒物。粉尘的产生系数参考《排放源统计调查产排污核算方法和系数手册》（生态环境部公告2021年第24号）的2641涂料制造行业系数手册-2641涂料制造行业系数表中的水性工业涂料颗粒物产污系数：0.1kg/t-产品。...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1、大气环境质量现状本项目选址位于佛山市顺德区杏坛镇，根据《顺德区生态环境保护规划（2021-2025年）》，顺德区全境为大气环境二类区，本项目所在地属环境空气质量二类功能区，区域的环境空气质量执行国家《环境空气质量标准》（GB3095-2012）及2018年修改单中的二级标准。（1）常规污染物环境质量现状根据《佛山市生态环境局顺德分局关于发布2021年度佛山市顺德区环境质量状况公报的通知》，该地区空气质量执行《环境空气质量标准》（GB3095-2012）及2018年修改单中的二级标准，基本污染物...</x:v>
       </x:c>
       <x:c r="H25" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报</x:v>
       </x:c>
       <x:c r="I25" s="7" t="b">
         <x:v>1</x:v>
@@ -1161,7 +1161,7 @@
       <x:c r="J25" s="11" t="str"/>
       <x:c r="K25" s="11" t="str"/>
     </x:row>
-    <x:row r="26" ht="82.5" customHeight="1">
+    <x:row r="26" ht="88.5" customHeight="1">
       <x:c r="A26" s="6" t="str">
         <x:v>P003_Q05</x:v>
       </x:c>
@@ -1172,19 +1172,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D26" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E26" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F26" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G26" s="6" t="str">
-        <x:v>五、环境保护措施监督检查清单（表格）写明：... | 通过集气管道接入分散缸顶部设置的排气口进行收集，收集后通过“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放 | 《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）；打样喷涂漆雾（有组织）（排气筒DA001） | 颗粒物 | 通过水帘柜进行打样室的整室收集，收集后通过“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放 | 《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）；...</x:v>
+        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...◇投料粉尘项目生产过程中的投料工序所加入的颜填料多数为粉末状固体，其投料过程会产生粉尘，主要污染因子为颗粒物。粉尘的产生系数参考《排放源统计调查产排污核算方法和系数手册》（生态环境部公告2021年第24号）的2641涂料制造行业系数手册-2641涂料制造行业系数表中的水性工业涂料颗粒物产污系数：0.1kg/t-产品。项目水性涂料的产量为2400t/a；水性涂料测试量约为产量的0.05%，即为1.2t/a。项目生产车间投料工序年工作300小时；实验室投料工序年工作150小时。经计算，项目投料过程颗粒物的产生量为0.240t/a，产生速率为0.801kg/h。...</x:v>
       </x:c>
       <x:c r="H26" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I26" s="7" t="b">
         <x:v>1</x:v>
@@ -1192,7 +1192,7 @@
       <x:c r="J26" s="11" t="str"/>
       <x:c r="K26" s="11" t="str"/>
     </x:row>
-    <x:row r="27" ht="82.5" customHeight="1">
+    <x:row r="27" ht="88.5" customHeight="1">
       <x:c r="A27" s="6" t="str">
         <x:v>P003_Q06</x:v>
       </x:c>
@@ -1203,19 +1203,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D27" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E27" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F27" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G27" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...与废气处理系统连接，收集后的粉尘通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放打样喷涂漆雾和有机废气、烘干有机废气打样间密闭设置，通过水帘柜进行整室收集，与生产车间收集的废气一起通过“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放分散、研磨和调漆有机废气研磨机为密闭设备，进出料管道与分散缸相连，分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的有机废气通过一套“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m...</x:v>
+        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...OC、臭气浓度半年无组织排放监测点位监测指标监测频次厂界颗粒物、TVOC、臭气浓度半年房门窗或通风口、其他开口（孔）等排放口外1mNMHC半年2、废气污染物排放源强核算过程（1）颗粒物◇投料粉尘项目生产过程中的投料工序所加入的颜填料多数为粉末状固体，其投料过程会产生粉尘，主要污染因子为颗粒物。粉尘的产生系数参考《排放源统计调查产排污核算方法和系数手册》（生态环境部公告2021年第24号）的2641涂料制造行业系数手册-2641涂料制造行业系数表中的水性工业涂料颗粒物产污系数：0.1kg/t-产品。项目水性涂料的产量为2400t/a；水性涂料测试量约为产量的0.05%，即为1.2t/a。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H27" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I27" s="7" t="b">
         <x:v>1</x:v>
@@ -1223,7 +1223,7 @@
       <x:c r="J27" s="11" t="str"/>
       <x:c r="K27" s="11" t="str"/>
     </x:row>
-    <x:row r="28" ht="82.5" customHeight="1">
+    <x:row r="28" ht="88.5" customHeight="1">
       <x:c r="A28" s="6" t="str">
         <x:v>P003_Q07</x:v>
       </x:c>
@@ -1234,19 +1234,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D28" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E28" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F28" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G28" s="6" t="str">
-        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...。经计算，项目投料过程颗粒物的产生量为0.240t/a，产生速率为0.801kg/h。要求项目正式生产的投料粉尘通过集气管道接入分散缸顶部设置的排气口进行收集，收集效率可达90%。收集后通过“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放，其中“滤芯除尘器”对粉尘的处理效率可达99%。实验室的粉尘通过车间无组织排放。◇打样喷涂漆雾项目打样喷涂过程会产生少量漆雾，主要污染因子为颗粒物。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...收处理有限公司进行处理。废气投料粉尘分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的粉尘通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放打样喷涂漆雾和有机废气、烘干有机废气打样间密闭设置，通过水帘柜进行整室收集，与生产车间收集的废气一起通过“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放分散、研磨和调漆有机废气研磨机为密闭设备，进出料管道与分散缸相连，分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的有机废气通过一套“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（D...</x:v>
       </x:c>
       <x:c r="H28" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I28" s="7" t="b">
         <x:v>1</x:v>
@@ -1254,7 +1254,7 @@
       <x:c r="J28" s="11" t="str"/>
       <x:c r="K28" s="11" t="str"/>
     </x:row>
-    <x:row r="29" ht="82.5" customHeight="1">
+    <x:row r="29" ht="88.5" customHeight="1">
       <x:c r="A29" s="6" t="str">
         <x:v>P003_Q08</x:v>
       </x:c>
@@ -1265,19 +1265,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D29" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E29" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F29" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G29" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...拟定期委托佛山市顺德区绿点废水回收处理有限公司进行处理。废气投料粉尘分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的粉尘通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放打样喷涂漆雾和有机废气、烘干有机废气打样间密闭设置，通过水帘柜进行整室收集，与生产车间收集的废气一起通过“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放分散、研磨和调漆有机废气研磨机为密闭设备，进出料管道与分散缸相连，分散缸顶盖设置排气口，通过集气管道与...</x:v>
+        <x:v>表4-2 废气污染源源强核算结果及相关参数一览表（表格）写明：...染源监测点位、监测指标及监测频次一览表有组织排放生产单元监测点位监测指标监测频次投料、分散、研磨、调漆、喷涂和烘干排气口DA001颗粒物、TVOC、臭气浓度半年无组织排放监测点位监测指标监测频次厂界颗粒物、TVOC、臭气浓度半年房门窗或通风口、其他开口（孔）等排放口外1mNMHC半年2、废气污染物排放源强核算过程（1）颗粒物◇投料粉尘项目生产过程中的投料工序所加入的颜填料多数为粉末状固体，其投料过程会产生粉尘，主要污染因子为颗粒物。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H29" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I29" s="7" t="b">
         <x:v>1</x:v>
@@ -1285,7 +1285,7 @@
       <x:c r="J29" s="11" t="str"/>
       <x:c r="K29" s="11" t="str"/>
     </x:row>
-    <x:row r="30" ht="82.5" customHeight="1">
+    <x:row r="30" ht="88.5" customHeight="1">
       <x:c r="A30" s="6" t="str">
         <x:v>P003_Q09</x:v>
       </x:c>
@@ -1296,19 +1296,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D30" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E30" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F30" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G30" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...能力为2t/d，自建废水处理站拟采用“物化沉淀＋生化处理+过滤”的处理工艺，清洗废水经自建废水处理站处理后可全部回用作清洗用水，每半年更换一次清洗废水。清洗废水暂存于专用储水罐，拟定期委托佛山市顺德区绿点废水回收处理有限公司进行处理。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...罐，拟定期委托佛山市顺德区绿点废水回收处理有限公司进行处理。废气投料粉尘分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的粉尘通过一套“滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放打样喷涂漆雾和有机废气、烘干有机废气打样间密闭设置，通过水帘柜进行整室收集，与生产车间收集的废气一起通过“干式过滤+滤芯除尘器+二级活性炭吸附”装置处理后通过30m排气筒（DA001）高空排放分散、研磨和调漆有机废气研磨机为密闭设备，进出料管道与分散缸相连，分散缸顶盖设置排气口，通过集气管道与废气处理系统连接，收集后的有机废气通过一套“干式过滤+滤芯除尘器+二级活性炭...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H30" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I30" s="7" t="b">
         <x:v>1</x:v>
@@ -1316,7 +1316,7 @@
       <x:c r="J30" s="11" t="str"/>
       <x:c r="K30" s="11" t="str"/>
     </x:row>
-    <x:row r="31" ht="82.5" customHeight="1">
+    <x:row r="31" ht="88.5" customHeight="1">
       <x:c r="A31" s="6" t="str">
         <x:v>P003_Q10</x:v>
       </x:c>
@@ -1327,19 +1327,19 @@
         <x:v>广东云晟新材料有限公司年产水性涂料2400吨新建项目</x:v>
       </x:c>
       <x:c r="D31" s="6" t="str">
-        <x:v>总量控制</x:v>
+        <x:v>风险防范措施</x:v>
       </x:c>
       <x:c r="E31" s="6" t="str">
-        <x:v>请根据报告中的VOCs总量控制指标和替代来源，判断总量控制论证是否充分。</x:v>
+        <x:v>请根据报告中的风险物质、危废暂存、液态物料贮存和事故情景，判断风险防范措施是否完整。</x:v>
       </x:c>
       <x:c r="F31" s="6" t="str">
-        <x:v>判断：需核查总量控制指标和替代来源。依据：报告涉及VOCs总量、替代来源或总量指标。审核意见：建议检查总量核算是否与源强排放量一致，替代来源或削减来源是否有明确证据。</x:v>
+        <x:v>判断：需核查风险防范措施与风险源是否对应。报告应针对液态物料、危废暂存、废气治理设施和可能事故情景提出防渗、防泄漏、收集、应急处置等措施。建议核查措施是否具体、是否覆盖主要风险单元。</x:v>
       </x:c>
       <x:c r="G31" s="6" t="str">
-        <x:v>六、结论（表格）写明：...= 3 \* GB3 \* MERGEFORMAT ③ | 本项目排放量（固体废物产生量） = 4 \* GB3 \* MERGEFORMAT ④ | 以新带老削减量（新建项目不填） = 5 \* GB3 \* MERGEFORMAT ⑤ | 本项目建成后全厂排放量（固体废物产生量） = 6 \* GB3 \* MERGEFORMAT ⑥ | 变化量 = 7 \* GB3 \* MERGEFORMAT ⑦；...</x:v>
+        <x:v>五、环境保护措施监督检查清单（表格）写明：...根据废物特性设置符合《危险废物贮存污染控制标准》（GB18597-2001）及其2013年修改单要求的危险废物暂存场所，且在暂存场所上空设有防雨淋设施，地面采取防渗措施，危险废物收集后分别临时贮存于废物储罐内；根据生产需要合理设置贮存量，尽量减少厂区内的物料贮存量；严禁将危险废物混入生活垃圾；堆放危险废物的地方要有明显的标志，堆放点要防雨、防渗、防漏，按要求进行包装贮存。；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H31" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；地方政策库；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I31" s="7" t="b">
         <x:v>1</x:v>
@@ -1347,7 +1347,7 @@
       <x:c r="J31" s="11" t="str"/>
       <x:c r="K31" s="11" t="str"/>
     </x:row>
-    <x:row r="32" ht="82.5" customHeight="1">
+    <x:row r="32" ht="88.5" customHeight="1">
       <x:c r="A32" s="6" t="str">
         <x:v>P004_Q01</x:v>
       </x:c>
@@ -1355,22 +1355,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C32" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D32" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E32" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F32" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：收集效率按2022年主要污染物总量减排核算技术指南 （国家VOCs-2022年修订）取值。收集效率应取50”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G32" s="6" t="str">
-        <x:v>Word批注/修改意见（第7条）写明：雷兆宇：收集效率按2022年主要污染物总量减排核算技术指南 （国家VOCs-2022年修订）取值。收集效率应取50</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...会杏坛工业区科技二路2号威和新科园8栋101之六.102.201.202；地理坐标 | （北纬 22 度 47 分 7 秒，东经 113 度 10分 35秒）；国民经济行业类别 | C2641 涂料制造 | 建设项目行业类别 | “二十三、化学原料和化学制品制造业26”中的“44涂料、油墨、颜料及类似产品制造 264；”中的“单纯物理分离、物理提纯、混合、分装的（不产生废水或挥发性有机物的除外）”；建设性质 | 新建（迁建）改建扩建技术改造 | 建设项目申报情形 | 首次申报项目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H32" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I32" s="7" t="b">
         <x:v>1</x:v>
@@ -1378,7 +1378,7 @@
       <x:c r="J32" s="11" t="str"/>
       <x:c r="K32" s="11" t="str"/>
     </x:row>
-    <x:row r="33" ht="82.5" customHeight="1">
+    <x:row r="33" ht="88.5" customHeight="1">
       <x:c r="A33" s="6" t="str">
         <x:v>P004_Q02</x:v>
       </x:c>
@@ -1386,22 +1386,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C33" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D33" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E33" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F33" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：密度不可信，请环评单位核实原辅材料，绝大部分部密度均大于1.1，生产过程不涉及化学反应，密度应远大于1.1”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G33" s="6" t="str">
-        <x:v>Word批注/修改意见（第2条）写明：雷兆宇：密度不可信，请环评单位核实原辅材料，绝大部分部密度均大于1.1，生产过程不涉及化学反应，密度应远大于1.1</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；项目审批（核准/备案）部门（选填） | / | 项目审批（核准/备案）文号（选填） | /；总投资（万元） | 200 | 环保投资（万元） | 25；环保投资占比（%） | 12.5 | 施工工期 | 2个月</x:v>
       </x:c>
       <x:c r="H33" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I33" s="7" t="b">
         <x:v>1</x:v>
@@ -1409,7 +1409,7 @@
       <x:c r="J33" s="11" t="str"/>
       <x:c r="K33" s="11" t="str"/>
     </x:row>
-    <x:row r="34" ht="82.5" customHeight="1">
+    <x:row r="34" ht="88.5" customHeight="1">
       <x:c r="A34" s="6" t="str">
         <x:v>P004_Q03</x:v>
       </x:c>
@@ -1417,22 +1417,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C34" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D34" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E34" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集效率与处理效率相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F34" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：Xxx工艺可以有效处理SS、COD、BOD，处理效率，什么原理，最后得出结果基本可信”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G34" s="6" t="str">
-        <x:v>Word批注/修改意见（第10条）写明：雷兆宇：Xxx工艺可以有效处理SS、COD、BOD，处理效率，什么原理，最后得出结果基本可信</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1.项目工程组成佛山市顺德区亚马逊涂料有限公司原址位于佛山市顺德区杏坛镇昌教村委会中心公路6号（不含之一卓志塑料厂）。该厂于2016年3月17日以《佛山市顺德区亚马逊涂料有限公司建设项目》环评报告表报批，经佛山市顺德区环境运输和城市管理局杏坛分局的批复文号为顺环（杏）审〔2016〕18号。于2016年9月28日通过佛山市顺德区亚马逊涂料有限公司建设项目竣工环境保护验收，该次验收为阶段验收（验收规模：高速分散机4台）。现因发展需要，拟搬迁至广东省佛山市顺德区杏坛镇齐杏社区居民委员会杏坛工业区科技二路2号...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H34" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I34" s="7" t="b">
         <x:v>1</x:v>
@@ -1440,7 +1440,7 @@
       <x:c r="J34" s="11" t="str"/>
       <x:c r="K34" s="11" t="str"/>
     </x:row>
-    <x:row r="35" ht="82.5" customHeight="1">
+    <x:row r="35" ht="88.5" customHeight="1">
       <x:c r="A35" s="6" t="str">
         <x:v>P004_Q04</x:v>
       </x:c>
@@ -1448,22 +1448,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C35" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D35" s="6" t="str">
-        <x:v>排放标准适用</x:v>
+        <x:v>污染物排放标准适用性</x:v>
       </x:c>
       <x:c r="E35" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断排放标准适用相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据项目行业类别、生产工艺、污染因子和排放形式，判断废气、废水、噪声和固废相关排放标准选取是否合理。</x:v>
       </x:c>
       <x:c r="F35" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：应根据排放标准中典型大气污染物进行核对分析，是否存在特征污染物，按需定性分析或定量分析”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查排放标准适用性。报告应结合行业类别、生产工艺、污染因子、有组织和无组织排放形式选取标准。建议核查是否遗漏厂区内VOCs无组织限值、厂界限值、排气筒排放限值或噪声、废水相关标准。</x:v>
       </x:c>
       <x:c r="G35" s="6" t="str">
-        <x:v>Word批注/修改意见（第8条）写明：雷兆宇：应根据排放标准中典型大气污染物进行核对分析，是否存在特征污染物，按需定性分析或定量分析</x:v>
+        <x:v>表4-12项目废气排放口信息一览表（表格）写明：运营期环境影响和保护措施 | 1.2大气达标性分析 1）排气筒废气达标分析本项目共设置1个排气筒，高度约45m，排气筒污染物排放情况见下表。表4-11 项目排气筒污染物排放达标情况一览表污染源污染物排放浓度（mg/m3）排放速率（kg/h）执行标准浓度限值（mg/m3）速率限值（kg/h）达标情况排气筒FQ-03672颗粒物2.35780.04717《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）中表2特别排放限值要求和《大气污染物排放限值》（DB44/27-2001）第二时段二级标准的较严值20/达标有机废气25.33830.50677《涂料、...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H35" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#8_塑料制品业典型污染源及执行标准、GB_31572-2015、GB_37822-2019、DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I35" s="7" t="b">
         <x:v>1</x:v>
@@ -1471,7 +1471,7 @@
       <x:c r="J35" s="11" t="str"/>
       <x:c r="K35" s="11" t="str"/>
     </x:row>
-    <x:row r="36" ht="82.5" customHeight="1">
+    <x:row r="36" ht="88.5" customHeight="1">
       <x:c r="A36" s="6" t="str">
         <x:v>P004_Q05</x:v>
       </x:c>
@@ -1479,22 +1479,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C36" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D36" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E36" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F36" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：10000风量需要2.8立方米的活性炭碳箱，”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G36" s="6" t="str">
-        <x:v>Word批注/修改意见（第11条）写明：雷兆宇：10000风量需要2.8立方米的活性炭碳箱，</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...染物为颗粒物，产生的粉尘中不含重金属等有毒有害物质。由于项目研发新产品时，每次投料的数量极少，因此该部分投料粉尘忽略不计。 由于《排放源统计调查产排污核算方法和系数手册》（公告 2021 年第24号）涂料制造行业系数手册中，无 UV涂料的污染源产生系数，本环评 UV 涂料生产过程中粉尘产生情况，参考溶剂型涂料的粉尘产生系数 0.051kg/t－产品进行计算。本项目UV 涂料产品年产量为300t，则颗粒物产生量为 0.0153t/a。...</x:v>
       </x:c>
       <x:c r="H36" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I36" s="7" t="b">
         <x:v>1</x:v>
@@ -1502,7 +1502,7 @@
       <x:c r="J36" s="11" t="str"/>
       <x:c r="K36" s="11" t="str"/>
     </x:row>
-    <x:row r="37" ht="82.5" customHeight="1">
+    <x:row r="37" ht="88.5" customHeight="1">
       <x:c r="A37" s="6" t="str">
         <x:v>P004_Q06</x:v>
       </x:c>
@@ -1510,22 +1510,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C37" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D37" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E37" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F37" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：明确转缸专用，回用生产。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G37" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：明确转缸专用，回用生产。</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...，内设负压整室收集，收集效率为95%。表4-1本项目总风量计算一览表设备罩口长度（m）污染源至罩口距离（m）风速（m/s）单台设备风量（m3/h）设备数量（台）核算风量（m3/h）投粉料工位10.30.77561756分散机（型号1）1.60.30.71209.656048分散机（型号2）1.10.30.7831.686652.8研磨机1.10.30.7831.632494.8灌装机0.80.30.7604.81604.8污染源规格体积（m3）换气次数（m/s）数量（个）核算风量（m3/h）打磨、试喷、风干工序3m×4m×2m24151360实验台（8台实验研磨机）2m×4m×2m161...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H37" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I37" s="7" t="b">
         <x:v>1</x:v>
@@ -1533,7 +1533,7 @@
       <x:c r="J37" s="11" t="str"/>
       <x:c r="K37" s="11" t="str"/>
     </x:row>
-    <x:row r="38" ht="82.5" customHeight="1">
+    <x:row r="38" ht="88.5" customHeight="1">
       <x:c r="A38" s="6" t="str">
         <x:v>P004_Q07</x:v>
       </x:c>
@@ -1541,22 +1541,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C38" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D38" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E38" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F38" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G38" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...，内设负压整室收集，收集效率为95%。表4-1本项目总风量计算一览表设备罩口长度（m）污染源至罩口距离（m）风速（m/s）单台设备风量（m3/h）设备数量（台）核算风量（m3/h）投粉料工位10.30.77561756分散机（型号1）1.60.30.71209.656048分散机（型号2）1.10.30.7831.686652.8研磨机1.10.30.7831.632494.8灌装机0.80.30.7604.81604.8污染源规格体积（m3）换气次数（m/s）数量（个）核算风量（m3/h）打磨、试喷、风干工...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：... | 大气污染源1.1废气产污环节根据《废气处理工程技术手册》（王纯、张殿印主编，化学工业出版社，2013版），投粉料、分散机、研磨机、灌装机均采用上吸罩+四面垂帘方式的排气量Q1的计算公式如下：Q1=WH VxQ1：所需风量，m3/h；W：罩口长度，m；H：污染源至罩口距离，m；Vx：风速，m/s。根据《废气处理工程技术手册》（王纯、张殿印），打磨、试喷、风干工序和实验台位于独立的房间内，内设负压整室收集，收集效率为95%。...</x:v>
       </x:c>
       <x:c r="H38" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I38" s="7" t="b">
         <x:v>1</x:v>
@@ -1564,7 +1564,7 @@
       <x:c r="J38" s="11" t="str"/>
       <x:c r="K38" s="11" t="str"/>
     </x:row>
-    <x:row r="39" ht="82.5" customHeight="1">
+    <x:row r="39" ht="88.5" customHeight="1">
       <x:c r="A39" s="6" t="str">
         <x:v>P004_Q08</x:v>
       </x:c>
@@ -1572,22 +1572,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C39" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D39" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E39" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F39" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G39" s="6" t="str">
-        <x:v>表4-12项目废气排放口信息一览表（表格）写明：...染物排放浓度（mg/m3）排放速率（kg/h）执行标准浓度限值（mg/m3）速率限值（kg/h）达标情况排气筒FQ-03672颗粒物2.35780.04717《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）中表2特别排放限值要求和《大气污染物排放限值》（DB44/27-2001）第二时段二级标准的较严值20/达标有机废气25.33830.50677《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）中表2特别排放限值要求和《固定污染源挥发性有机物综合排放标准》（DB...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...m；H：污染源至罩口距离，m；Vx：风速，m/s。根据《废气处理工程技术手册》（王纯、张殿印），打磨、试喷、风干工序和实验台位于独立的房间内，内设负压整室收集，收集效率为95%。表4-1本项目总风量计算一览表设备罩口长度（m）污染源至罩口距离（m）风速（m/s）单台设备风量（m3/h）设备数量（台）核算风量（m3/h）投粉料工位10.30.77561756分散机（型号1）1.60.30.71209.656048分散机（型号2）1.10.30.7831.686652.8研磨机1.10.30.7831.632494.8灌装机0.80.30.7604.81604.8污染源规格体积（m3）换气次...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H39" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I39" s="7" t="b">
         <x:v>1</x:v>
@@ -1595,7 +1595,7 @@
       <x:c r="J39" s="11" t="str"/>
       <x:c r="K39" s="11" t="str"/>
     </x:row>
-    <x:row r="40" ht="82.5" customHeight="1">
+    <x:row r="40" ht="88.5" customHeight="1">
       <x:c r="A40" s="6" t="str">
         <x:v>P004_Q09</x:v>
       </x:c>
@@ -1603,22 +1603,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C40" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D40" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E40" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F40" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G40" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：... | 大气污染源1.1废气产污环节根据《废气处理工程技术手册》（王纯、张殿印主编，化学工业出版社，2013版），投粉料、分散机、研磨机、灌装机均采用上吸罩+四面垂帘方式的排气量Q1的计算公式如下：Q1=WH VxQ1：所需风量，m3/h；W：罩口长度，m；H：污染源至罩口距离，m；Vx：风速，m/s。根据《废气处理工程技术手册》（王纯、张殿印），打磨、试喷、风干工序和实验台位于独立的房间内，内设负压整室收集，收集效率为95%。...</x:v>
+        <x:v>表4-12项目废气排放口信息一览表（表格）写明：...别排放限值，对周围大气环境和附近敏感点影响不大。3）非正常工况下废气达标分析本项目生产设施开停机等非正常工况下无废气污染物产生。1.4 废气治理设施可行性分析 吸附法是用固体吸附剂吸附处理废气中有害气体的一种方法。选择吸附剂的原则是比表面积大，容易吸附和脱附再生，来源容易，价格较低。有机废气适宜采用活性炭作吸附剂。活性炭是一种由含碳材料制成的外观呈黑色，内部孔隙结构发达、比表面积大、吸附能力强的一类微晶质碳素材料。活性炭材料中有大量肉眼看不见的微孔，1g活性炭材料中微孔的总内表面积可高达700～2300m2。正是这些微孔使得活性炭能“捕捉”各种有毒有害气体和杂质。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H40" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I40" s="7" t="b">
         <x:v>1</x:v>
@@ -1626,7 +1626,7 @@
       <x:c r="J40" s="11" t="str"/>
       <x:c r="K40" s="11" t="str"/>
     </x:row>
-    <x:row r="41" ht="82.5" customHeight="1">
+    <x:row r="41" ht="88.5" customHeight="1">
       <x:c r="A41" s="6" t="str">
         <x:v>P004_Q10</x:v>
       </x:c>
@@ -1634,22 +1634,22 @@
         <x:v>（20230603第二次修改版）佛山市顺德区亚马逊涂料有限公司迁扩建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C41" s="6" t="str">
-        <x:v>| 佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
+        <x:v>佛山市顺德区亚马逊涂料有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D41" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E41" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F41" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G41" s="6" t="str">
-        <x:v>表4-12项目废气排放口信息一览表（表格）写明：...，比表面积 900～1500m2 /g，具有非常良好的吸附特性，其吸附量比活性炭颗粒一般大20～100倍，吸附容量为25wt%。采用活性炭进行有机尾气的净化，其去除效率会因二级活性炭吸附废气的饱和程度而不同，净化效率为50%～90%（本报告二级活性炭吸附净化效率取75%）。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1.项目工程组成佛山市顺德区亚马逊涂料有限公司原址位于佛山市顺德区杏坛镇昌教村委会中心公路6号（不含之一卓志塑料厂）。该厂于2016年3月17日以《佛山市顺德区亚马逊涂料有限公司建设项目》环评报告表报批，经佛山市顺德区环境运输和城市管理局杏坛分局的批复文号为顺环（杏）审〔2016〕18号。于2016年9月28日通过佛山市顺德区亚马逊涂料有限公司建设项目竣工环境保护验收，该次验收为阶段验收（验收规模：高速分散机4台）。现因发展需要，拟搬迁至广东省佛山市顺德区杏坛镇齐杏社区居民委员会杏坛工业区科技二路2号威和新科园8栋101之六.102.201.202...</x:v>
       </x:c>
       <x:c r="H41" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I41" s="7" t="b">
         <x:v>1</x:v>
@@ -1657,7 +1657,7 @@
       <x:c r="J41" s="11" t="str"/>
       <x:c r="K41" s="11" t="str"/>
     </x:row>
-    <x:row r="42" ht="82.5" customHeight="1">
+    <x:row r="42" ht="88.5" customHeight="1">
       <x:c r="A42" s="6" t="str">
         <x:v>P005_Q01</x:v>
       </x:c>
@@ -1665,22 +1665,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C42" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D42" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E42" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F42" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：熟化过程是相对复杂的过程，PE熔点温度高于熟化温度，但过程中理应存在少量的非甲烷总烃，可以不定量分析，但不能说非甲烷总烃产生”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G42" s="6" t="str">
-        <x:v>Word批注/修改意见（第10条）写明：雷兆宇：熟化过程是相对复杂的过程，PE熔点温度高于熟化温度，但过程中理应存在少量的非甲烷总烃，可以不定量分析，但不能说非甲烷总烃产生</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...手机号已脱敏]；建设地点 | 广东省佛山市顺德区杏坛镇龙潭村龙古路2号之一；地理坐标 | （东经113度07分24.310秒，北纬22度48分54.960秒）；国民经济行业类别 | C2223 加工纸制造C2921塑料薄膜制造 | 建设项目行业类别 | 十九、造纸和纸制品业22、37 造纸222*（含废纸造纸）、手工纸制造；有涂布、浸渍、印刷、粘胶工艺的加工纸制造二十六、橡胶和塑料制品业29、53 塑料制品业292-其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）；...</x:v>
       </x:c>
       <x:c r="H42" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I42" s="7" t="b">
         <x:v>1</x:v>
@@ -1688,7 +1688,7 @@
       <x:c r="J42" s="11" t="str"/>
       <x:c r="K42" s="11" t="str"/>
     </x:row>
-    <x:row r="43" ht="82.5" customHeight="1">
+    <x:row r="43" ht="88.5" customHeight="1">
       <x:c r="A43" s="6" t="str">
         <x:v>P005_Q02</x:v>
       </x:c>
@@ -1696,22 +1696,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C43" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D43" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E43" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F43" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：油墨中可挥发性有机化合物(VOCs)含量的限值（GB 38507-2020）比较确认是否为低VOCs油墨，在上文论述”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G43" s="6" t="str">
-        <x:v>Word批注/修改意见（第17条）写明：雷兆宇：油墨中可挥发性有机化合物(VOCs)含量的限值（GB 38507-2020）比较确认是否为低VOCs油墨，在上文论述</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 项目由来佛山市亮正新材料有限公司位于佛山市顺德区杏坛镇龙潭工业区齐龙路29号之二（中心地理位置为：东经113度07分24.310秒，北纬22度48分54.960秒），占地面积为1500m2，建筑面积为1200m2，主要从事纸制品制造，年产保护纸400万米、保护膜200万米。根据《建设项目环境影响评价分类管理名录（2021年版）》，本次项目属于“十九、造纸和纸制品业22、37 造纸222*（含废纸造纸）、手工纸制造；有涂布、浸渍、印刷、粘胶工艺的加工纸制造”类别和“二十六、橡胶和塑料制品业29、53 塑...</x:v>
       </x:c>
       <x:c r="H43" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I43" s="7" t="b">
         <x:v>1</x:v>
@@ -1719,7 +1719,7 @@
       <x:c r="J43" s="11" t="str"/>
       <x:c r="K43" s="11" t="str"/>
     </x:row>
-    <x:row r="44" ht="82.5" customHeight="1">
+    <x:row r="44" ht="88.5" customHeight="1">
       <x:c r="A44" s="6" t="str">
         <x:v>P005_Q03</x:v>
       </x:c>
@@ -1727,22 +1727,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C44" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D44" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E44" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F44" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：是否能做到，上面计算是集气罩计算方法，如果是单层密闭正压需写明一小时换气多少次，通过体积计算风量。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G44" s="6" t="str">
-        <x:v>Word批注/修改意见（第21条）写明：雷兆宇：是否能做到，上面计算是集气罩计算方法，如果是单层密闭正压需写明一小时换气多少次，通过体积计算风量。</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 大气环境根据《佛山市人民政府办公室关于调整顺德区环境空气质量功能区划的复函》（佛府办函[2014]494号，2014年8月）和《顺德区生态环境规划（2011~2020年）》，顺德区全境为大气环境二类区，因此本项目所在区域属二类环境空气质量功能区，执行《环境空气质量标准》（GB3095-2012）及2018年修改单二级标准。（1）空气质量达标区判定根据《佛山市生态环境局顺德分局关于发布2022年度佛山市顺德区生态环境状况公报的通知（佛环顺函〔2023〕26号）》，2022年顺德区空气质量综合指数为3...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H44" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I44" s="7" t="b">
         <x:v>1</x:v>
@@ -1750,7 +1750,7 @@
       <x:c r="J44" s="11" t="str"/>
       <x:c r="K44" s="11" t="str"/>
     </x:row>
-    <x:row r="45" ht="82.5" customHeight="1">
+    <x:row r="45" ht="88.5" customHeight="1">
       <x:c r="A45" s="6" t="str">
         <x:v>P005_Q04</x:v>
       </x:c>
@@ -1758,22 +1758,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C45" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D45" s="6" t="str">
-        <x:v>排放标准适用</x:v>
+        <x:v>污染物排放标准适用性</x:v>
       </x:c>
       <x:c r="E45" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断排放标准适用相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据项目行业类别、生产工艺、污染因子和排放形式，判断废气、废水、噪声和固废相关排放标准选取是否合理。</x:v>
       </x:c>
       <x:c r="F45" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：与印刷工业大气污染物排放标准GB 41616—2022较严值”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查排放标准适用性。报告应结合行业类别、生产工艺、污染因子、有组织和无组织排放形式选取标准。建议核查是否遗漏厂区内VOCs无组织限值、厂界限值、排气筒排放限值或噪声、废水相关标准。</x:v>
       </x:c>
       <x:c r="G45" s="6" t="str">
-        <x:v>Word批注/修改意见（第11条）写明：雷兆宇：与印刷工业大气污染物排放标准GB 41616—2022较严值</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：2）无组织达标分析项目胶水调配、上胶、复合、熟化工序产生的VOCs未被集气罩收集的以无组织的形式排放至大气环境，可达到广东省《固定污染源挥发性有机物综合排放标准》（DB44/2367-2022）表3厂区内VOCs无组织排放限值要求。印刷工位未收集的VOCs经空气流通稀释后，可达到广东省《印刷行业挥发性有机化合物排放标准》（DB44/815-2010）表3无组织排放监控点浓度限值要求。项目胶水调配、上胶、复合、熟化、印刷工序会产生少量的异味，无组织排放，可满足《恶臭污染物排放标准》（GB14554-93）表1恶臭污染物厂界标准值，厂界排放浓度≤20（无量纲）。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H45" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#8_塑料制品业典型污染源及执行标准、GB_31572-2015、GB_37822-2019、DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I45" s="7" t="b">
         <x:v>1</x:v>
@@ -1781,7 +1781,7 @@
       <x:c r="J45" s="11" t="str"/>
       <x:c r="K45" s="11" t="str"/>
     </x:row>
-    <x:row r="46" ht="82.5" customHeight="1">
+    <x:row r="46" ht="88.5" customHeight="1">
       <x:c r="A46" s="6" t="str">
         <x:v>P005_Q05</x:v>
       </x:c>
@@ -1789,22 +1789,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C46" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D46" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E46" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F46" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：附件附上涂布机的性状、型号”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G46" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：附件附上涂布机的性状、型号</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...、上胶、复合、熟化产生的有机废气项目在胶水调配、上胶、复合、熟化过程会产生有机废气，其主要污染因子为VOCs，本次环评核算中参考《排放源统计调查产排污核算方法和系数手册-22造纸和纸制品业系数手册》中造纸和纸制品业（22）加工纸制造（2223）行业系数表-加工纸-涂布法的挥发性有机物产污系数910g/t-产品，项目年产保护纸400万米/年（合约3125卷/年，293kg/卷，即915.625t/a）、保护膜200万米/年（合约1613卷/年，57.86kg/卷，即93.328t/a），则项目胶水调配、上胶、复合、熟化过程的VOCs产生量约为0.9181t/a。...</x:v>
       </x:c>
       <x:c r="H46" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I46" s="7" t="b">
         <x:v>1</x:v>
@@ -1812,7 +1812,7 @@
       <x:c r="J46" s="11" t="str"/>
       <x:c r="K46" s="11" t="str"/>
     </x:row>
-    <x:row r="47" ht="82.5" customHeight="1">
+    <x:row r="47" ht="88.5" customHeight="1">
       <x:c r="A47" s="6" t="str">
         <x:v>P005_Q06</x:v>
       </x:c>
@@ -1820,22 +1820,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C47" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D47" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E47" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F47" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G47" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：①胶水调配、上胶、复合、熟化产生的有机废气项目在胶水调配、上胶、复合、熟化过程会产生有机废气，其主要污染因子为VOCs，本次环评核算中参考《排放源统计调查产排污核算方法和系数手册-22造纸和纸制品业系数手册》中造纸和纸制品业（22）加工纸制造（2223）行业系数表-加工纸-涂布法的挥发性有机物产污系数910g/t-产品，项目年产保护纸400万米/年（合约3125卷/年，293kg/卷，即915.625t/a）、保护膜200万米/年（合约1613卷/年，57.86kg/卷，即93.328t/a），则项目胶水调配、上胶...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：①胶水调配、上胶、复合、熟化产生的有机废气项目在胶水调配、上胶、复合、熟化过程会产生有机废气，其主要污染因子为VOCs，本次环评核算中参考《排放源统计调查产排污核算方法和系数手册-22造纸和纸制品业系数手册》中造纸和纸制品业（22）加工纸制造（2223）行业系数表-加工纸-涂布法的挥发性有机物产污系数910g/t-产品，项目年产保护纸400万米/年（合约3125卷/年，293kg/卷，即915.625t/a）、保护膜200万米/年（合约1613卷/年，57.86kg/卷，即93.328t/a），则项目胶水调配、上胶、复合、熟化过程的VOCs产生量约为0.9181t/a。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H47" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I47" s="7" t="b">
         <x:v>1</x:v>
@@ -1843,7 +1843,7 @@
       <x:c r="J47" s="11" t="str"/>
       <x:c r="K47" s="11" t="str"/>
     </x:row>
-    <x:row r="48" ht="82.5" customHeight="1">
+    <x:row r="48" ht="88.5" customHeight="1">
       <x:c r="A48" s="6" t="str">
         <x:v>P005_Q07</x:v>
       </x:c>
@@ -1851,22 +1851,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C48" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D48" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E48" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F48" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G48" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...顺德区发布的有机污染物治理政策的相符性分析见表1-2。表1-2 项目与有机污染物治理政策的相符性分析序号政策本项目情况相符性1.《珠江三角洲地区严格控制工业企业挥发性有机物（VOCs）排放的意见》（粤环[2012]18号）1.1在自然保护区、水源保护区、风景名胜区、森林公园、重要湿地、生态敏感区和其他重生态功能区实行强制性保护，禁止新建VOCs污染企业。本项目选址不在禁止区域。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...Cs污染企业。本项目选址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。胶水调配、上胶、印刷废气经包围型集气罩收集后和经密闭收集的复合、熟化废气一同通过“二级活性炭吸附装置”处理后引至15m高排气筒G1高空排放。符合3.关于印发《重点行业挥发性有机物综合治理方案》的通知（环大气[2019]53 号）3.1含 VOCs 物料应储存于密闭容器、包装袋，高效密封储罐，封闭式储库、料仓等。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H48" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I48" s="7" t="b">
         <x:v>1</x:v>
@@ -1874,7 +1874,7 @@
       <x:c r="J48" s="11" t="str"/>
       <x:c r="K48" s="11" t="str"/>
     </x:row>
-    <x:row r="49" ht="82.5" customHeight="1">
+    <x:row r="49" ht="88.5" customHeight="1">
       <x:c r="A49" s="6" t="str">
         <x:v>P005_Q08</x:v>
       </x:c>
@@ -1882,22 +1882,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C49" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D49" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>废气收集风量与设计风量核算</x:v>
       </x:c>
       <x:c r="E49" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的集气罩尺寸、控制风速、收集点数量和风量计算过程，判断设计风量是否具有可复核性。</x:v>
       </x:c>
       <x:c r="F49" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查风量计算是否可复核。报告应说明收集点数量、罩口尺寸、控制风速或换气次数，并形成可追溯的设计风量。建议核查计算公式、取值依据、风机风量裕量和治理设施处理风量是否匹配。</x:v>
       </x:c>
       <x:c r="G49" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。胶水调配、上胶、印刷废气经包围型集气罩收集后和经密闭收集的复合、熟化废气一同通过“二级活性炭吸附装置”处理后引至15m高排气筒G1高空排放。符合3.关于印发《重点行业挥发性有机物综合治理方案》的通知（环大气[2019]53 号）3.1含 VOCs 物料应储存于密闭容器、包装袋，高效密封储罐，封闭式储库、料仓等。含VOCs物料生产和使用过程，应采取有效收集措施或在密闭空间中操作。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...用全密闭集气罩或密闭空间的，除行业有特殊要求外，应保持微负压状态，并根据相关规范合理设置通风量。采用局部集气罩的，距集气罩开口面最远处的VOCs无组织排放位置，控制风速应不低于0.3米/秒，有行业要求的按相关规定执行。胶水调配、上胶废气经包围型集气罩收集后和经密闭收集的复合、熟化废气一同通过“二级活性炭吸附装置”处理后引至15m高排气筒G1高空排放。包围型集气罩收集效率为50%，密闭收集效率为75%，二级活性炭处理效率为51%。...</x:v>
       </x:c>
       <x:c r="H49" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集风量与设计风量核算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I49" s="7" t="b">
         <x:v>1</x:v>
@@ -1905,7 +1905,7 @@
       <x:c r="J49" s="11" t="str"/>
       <x:c r="K49" s="11" t="str"/>
     </x:row>
-    <x:row r="50" ht="82.5" customHeight="1">
+    <x:row r="50" ht="88.5" customHeight="1">
       <x:c r="A50" s="6" t="str">
         <x:v>P005_Q09</x:v>
       </x:c>
@@ -1913,22 +1913,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C50" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D50" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E50" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F50" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G50" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。胶水调配、上胶、印刷废气经包围型集气罩收集后和经密闭收集的复合、熟化废气一同通过“二级活性炭吸附装置”处理后引至15m高排气筒G1高空排放。符合3.关于印发《重点行业挥发性有机物综合治理方案》的通知（环大气[2019]53 号）3.1含 VOCs 物料应储存于密闭容器、包装袋，高效密封储罐，封闭式储库、料仓等。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。胶水调配、上胶、印刷废气经包围型集气罩收集后和经密闭收集的复合、熟化废气一同通过“二级活性炭吸附装置”处理后引至15m高排气筒G1高空排放。符合3.关于印发《重点行业挥发性有机物综合治理方案》的通知（环大气[2019]53 号）3.1含 VOCs 物料应储存于密闭容器、包装袋，高效密封储罐，封闭式储库、料仓等。含VOCs物料生产和使用过程，应采取有效收集措施或在密闭空间中操作。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H50" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I50" s="7" t="b">
         <x:v>1</x:v>
@@ -1936,7 +1936,7 @@
       <x:c r="J50" s="11" t="str"/>
       <x:c r="K50" s="11" t="str"/>
     </x:row>
-    <x:row r="51" ht="82.5" customHeight="1">
+    <x:row r="51" ht="88.5" customHeight="1">
       <x:c r="A51" s="6" t="str">
         <x:v>P005_Q10</x:v>
       </x:c>
@@ -1944,22 +1944,22 @@
         <x:v>202307051138439441.佛山市亮正新材料有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C51" s="6" t="str">
-        <x:v>| 佛山市亮正新材料有限公司新建项目</x:v>
+        <x:v>佛山市亮正新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D51" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E51" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F51" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G51" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...染物排放标准》（GB14554-93）表1恶臭污染物厂界标准值，厂界排放浓度≤20（无量纲）。（3）废气治理设施可行性分析项目生产过程中产生的有机废气收集后二级活性炭吸附废气处理设施进行处理，处理达标后通过26m排气筒（G1）排放。吸附法是用固体吸附剂吸附处理废气中有害气体的一种方法。选择吸附剂的原则是比表面积大，容易吸附和脱附再生，来源容易，价格较低。有机废气适宜采用活性炭作吸附剂。活性炭是一种由含碳材料制成的外观呈黑色，内部孔隙结构发达、比表面积大、吸附能力强的一类微晶质碳素材料。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...废纸造纸）、手工纸制造；有涂布、浸渍、印刷、粘胶工艺的加工纸制造”类别和“二十六、橡胶和塑料制品业29、53 塑料制品业292-其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）”，需编制建设项目环境影响报告表。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H51" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I51" s="7" t="b">
         <x:v>1</x:v>
@@ -1967,7 +1967,7 @@
       <x:c r="J51" s="11" t="str"/>
       <x:c r="K51" s="11" t="str"/>
     </x:row>
-    <x:row r="52" ht="82.5" customHeight="1">
+    <x:row r="52" ht="88.5" customHeight="1">
       <x:c r="A52" s="6" t="str">
         <x:v>P006_Q01</x:v>
       </x:c>
@@ -1975,22 +1975,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C52" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D52" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E52" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F52" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：是否合理？按最新核算方法核算。对原项目进行归真。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G52" s="6" t="str">
-        <x:v>Word批注/修改意见（第6条）写明：雷兆宇：是否合理？按最新核算方法核算。对原项目进行归真。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...建设地点 | 佛山市顺德区杏坛镇顺业西路15号中集智能制造中心22栋101；地理坐标 | （东经113度11分58.650秒，北纬22度45分20.510秒）；国民经济行业类别 | C2929 塑料零件及其他塑料制品制造 | 建设项目行业类别 | 二十六、橡胶和塑料制品业29、53塑料制品业-292、其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）改建扩建技术改造 | 建设项目申报情形 | 首次申报项目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H52" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I52" s="7" t="b">
         <x:v>1</x:v>
@@ -1998,7 +1998,7 @@
       <x:c r="J52" s="11" t="str"/>
       <x:c r="K52" s="11" t="str"/>
     </x:row>
-    <x:row r="53" ht="82.5" customHeight="1">
+    <x:row r="53" ht="88.5" customHeight="1">
       <x:c r="A53" s="6" t="str">
         <x:v>P006_Q02</x:v>
       </x:c>
@@ -2006,22 +2006,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C53" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D53" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E53" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F53" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：补充佛山市生态环境局关于印发《佛山市挥发性有机物排污总量指标精细化管理工作方案（试行）》的函相符性分析”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G53" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：补充佛山市生态环境局关于印发《佛山市挥发性有机物排污总量指标精细化管理工作方案（试行）》的函相符性分析</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；项目审批（核准/备案）部门（选填） | / | 项目审批（核准/备案）文号（选填） | /；总投资（万元） | 150 | 环保投资（万元） | 15；环保投资占比（%） | 10 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H53" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I53" s="7" t="b">
         <x:v>1</x:v>
@@ -2029,7 +2029,7 @@
       <x:c r="J53" s="11" t="str"/>
       <x:c r="K53" s="11" t="str"/>
     </x:row>
-    <x:row r="54" ht="82.5" customHeight="1">
+    <x:row r="54" ht="88.5" customHeight="1">
       <x:c r="A54" s="6" t="str">
         <x:v>P006_Q03</x:v>
       </x:c>
@@ -2037,22 +2037,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C54" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D54" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>三线一单管控内容一致性</x:v>
       </x:c>
       <x:c r="E54" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集效率与处理效率相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的项目位置、经纬度、环境管控单元和项目排污特征，判断三线一单符合性分析是否充分。</x:v>
       </x:c>
       <x:c r="F54" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：危险废物还有废旧灯管、以及水喷淋废水”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查三线一单分析是否逐项对应。报告应明确项目所在管控单元、准入要求和项目排污特征，并说明与空间布局、污染物排放、环境风险和资源利用要求的对应关系。建议核查是否存在只作概括性符合结论、未结合项目工艺和污染物特征的问题。</x:v>
       </x:c>
       <x:c r="G54" s="6" t="str">
-        <x:v>Word批注/修改意见（第9条）写明：雷兆宇：危险废物还有废旧灯管、以及水喷淋废水</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...区2018-2020年村级工业园升级改造三年行动计划项目》，本项目不在“三旧”改造和村级工业园改造范围，因此本项目的选址符合佛山市顺德区总体规划的要求。项目与“三线一单”符合性分析1、广东省“三线一单”符合性分析①生态保护红线佛山市顺德区启卓工程塑料实业有限公司位于广佛山市顺德区杏坛镇顺业西路15号中集智能制造中心22栋101，根据《广东省人民政府关于印发广东省“三线一单”生态环境分区管控方案的通知》（粤府[2020]71号），项目所在地不属于生态优先保护区、水环境优先保护区、大气环境优先保护区等优先保护单元，因此项目不涉及生态保护红线。...</x:v>
       </x:c>
       <x:c r="H54" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#4_三线一单、顺德管控单元准入清单</x:v>
       </x:c>
       <x:c r="I54" s="7" t="b">
         <x:v>1</x:v>
@@ -2060,7 +2060,7 @@
       <x:c r="J54" s="11" t="str"/>
       <x:c r="K54" s="11" t="str"/>
     </x:row>
-    <x:row r="55" ht="82.5" customHeight="1">
+    <x:row r="55" ht="88.5" customHeight="1">
       <x:c r="A55" s="6" t="str">
         <x:v>P006_Q04</x:v>
       </x:c>
@@ -2068,22 +2068,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C55" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D55" s="6" t="str">
-        <x:v>废水去向与冷却水</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E55" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废水去向与冷却水相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F55" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：不需要定期更换吗？冷却水重复使用其硬度会不断增加，对设备具有一定影响。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G55" s="6" t="str">
-        <x:v>Word批注/修改意见（第3条）写明：雷兆宇：不需要定期更换吗？冷却水重复使用其硬度会不断增加，对设备具有一定影响。</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 项目由来佛山市顺德区启卓工程塑料实业有限公司原名为佛山市顺德区杏坛镇启卓塑料五金厂，成立于2004年6月23日，位于顺德区杏坛镇七滘工业园光华区二路3号，占地面积为2500m2，建筑面积为2000m2，主要从事废旧塑料粒的生产，年产废旧塑料粒（PE、PP）1500吨，已于2005年已取得环保批准证（编号：20051004）。于2016年变更法人及项目名称为佛山市顺德区启卓工程塑料实业有限公司，并于2017年3月15日通过环保验收，并取得顺德区环境运输和城市管理局杏坛分局出具的《验收组意见》（顺环杏[2...</x:v>
       </x:c>
       <x:c r="H55" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I55" s="7" t="b">
         <x:v>1</x:v>
@@ -2091,7 +2091,7 @@
       <x:c r="J55" s="11" t="str"/>
       <x:c r="K55" s="11" t="str"/>
     </x:row>
-    <x:row r="56" ht="82.5" customHeight="1">
+    <x:row r="56" ht="88.5" customHeight="1">
       <x:c r="A56" s="6" t="str">
         <x:v>P006_Q05</x:v>
       </x:c>
@@ -2099,22 +2099,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C56" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D56" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E56" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F56" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：这里写现项目，并非原项目”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G56" s="6" t="str">
-        <x:v>Word批注/修改意见（第2条）写明：雷兆宇：这里写现项目，并非原项目</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：③挤出、抽检废气搬迁后项目挤出、抽检工序期间会产生有机废气，以非甲烷总烃表征。挤出过程非甲烷总烃产生系数参考《排放源统计调查产排污核算方法和系数手册-292塑料制品行业系数手册》2929塑料零件及其他塑料制品制造行业系数表-改性粒料-树脂、助剂-造粒中挥发性有机物产生系数为4.6kg/t-产品。本项目改性塑料粒年产量为3500t/a，由此可得，挤出、抽检工序非甲烷总烃产生量为16.1000t/a。挤出、抽检废气经包围型集气罩收集后通过“二级活性炭吸附装置”处理，尾气通过30m高的G1排气筒排放。...</x:v>
       </x:c>
       <x:c r="H56" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I56" s="7" t="b">
         <x:v>1</x:v>
@@ -2122,7 +2122,7 @@
       <x:c r="J56" s="11" t="str"/>
       <x:c r="K56" s="11" t="str"/>
     </x:row>
-    <x:row r="57" ht="82.5" customHeight="1">
+    <x:row r="57" ht="88.5" customHeight="1">
       <x:c r="A57" s="6" t="str">
         <x:v>P006_Q06</x:v>
       </x:c>
@@ -2130,22 +2130,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C57" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D57" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E57" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F57" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G57" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | （1）废气源强核算项目废气产生、排放情况详见下表：表4-1 项目废气产生、排放情况一览表产品排气筒编号/车间名称产排污环节污染物种类污染物产生排放形式/治理设施污染物排放产生量（t/a）产生浓度（mg/m3）处理能力（m3/h）收集效率（%）治理工艺去除率（%）是否为可行技术可行性技术依据排放量（t/a）排放速率（kg/h）排放浓度（mg/m3）改性塑料粒生产车间混料颗粒物少量≤1.0无组织/////少量/≤1.0破碎颗粒物0.0186≤1.0/...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：③挤出、抽检废气搬迁后项目挤出、抽检工序期间会产生有机废气，以非甲烷总烃表征。挤出过程非甲烷总烃产生系数参考《排放源统计调查产排污核算方法和系数手册-292塑料制品行业系数手册》2929塑料零件及其他塑料制品制造行业系数表-改性粒料-树脂、助剂-造粒中挥发性有机物产生系数为4.6kg/t-产品。本项目改性塑料粒年产量为3500t/a，由此可得，挤出、抽检工序非甲烷总烃产生量为16.1000t/a。挤出、抽检废气经包围型集气罩收集后通过“二级活性炭吸附装置”处理，尾气通过30m高的G1排气筒排放。风量计算：项目拟在拉粒机、注塑检测机、挤出检测机的出料口设置包围型集气罩正压排风收...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H57" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I57" s="7" t="b">
         <x:v>1</x:v>
@@ -2153,7 +2153,7 @@
       <x:c r="J57" s="11" t="str"/>
       <x:c r="K57" s="11" t="str"/>
     </x:row>
-    <x:row r="58" ht="82.5" customHeight="1">
+    <x:row r="58" ht="88.5" customHeight="1">
       <x:c r="A58" s="6" t="str">
         <x:v>P006_Q07</x:v>
       </x:c>
@@ -2161,22 +2161,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C58" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D58" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E58" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F58" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G58" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...源消耗等达到或优于国家下达的总量和强度符合控制目标。本项目不属于高耗能、污染资源型企业，用水来自市政管网，用电来自市政供电。本项目建成后通过内部管理、设备选择、原辅材料的选用和管理、废物回收利用、污染治理等方面采取可行的防治措施，以“节能、降耗、减污”为目标，有效的控制污染。项目的水、电等资源利用不会突破区域上线。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。挤出、抽检工序废气经集气罩收集后通过二级活性炭吸附废气处理设施进行处理，处理达标后通过排气筒G1（30m）引至楼顶排放符合3.关于印发《重点行业挥发性有机物综合治理方案》的通知（环大气[2019]53 号）3.1含 VOCs 物料应储存于密闭容器、包装袋，高效密封储罐，封闭式储库、料仓等。含VOCs物料生产和使用过程，应采取有效收集措施或在密闭空间中操作。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H58" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I58" s="7" t="b">
         <x:v>1</x:v>
@@ -2184,7 +2184,7 @@
       <x:c r="J58" s="11" t="str"/>
       <x:c r="K58" s="11" t="str"/>
     </x:row>
-    <x:row r="59" ht="82.5" customHeight="1">
+    <x:row r="59" ht="88.5" customHeight="1">
       <x:c r="A59" s="6" t="str">
         <x:v>P006_Q08</x:v>
       </x:c>
@@ -2192,22 +2192,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C59" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D59" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>废水排放及生活污水基本情况</x:v>
       </x:c>
       <x:c r="E59" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的生活污水、生产废水、冷却水去向和基本情况表，判断废水排放内容是否准确、一致。</x:v>
       </x:c>
       <x:c r="F59" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查废水类别和去向一致性。报告应明确生活污水、生产废水、冷却水或喷淋废水的产生、处理、回用和排放路径。建议核查正文、基本情况表、排放标准和纳污去向是否一致。</x:v>
       </x:c>
       <x:c r="G59" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...物产生系数为4.6kg/t-产品。本项目改性塑料粒年产量为3500t/a，由此可得，挤出、抽检工序非甲烷总烃产生量为16.1000t/a。挤出、抽检废气经包围型集气罩收集后通过“二级活性炭吸附装置”处理，尾气通过30m高的G1排气筒排放。风量计算：项目拟在拉粒机、注塑检测机、挤出检测机的出料口设置包围型集气罩正压排风收集产生的非甲烷总烃，集气罩尺寸均约为长0.5m*宽0.5m，收集后经二级活性炭处理后通过30米排气筒G1排放。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...扩建项目不得新增水污染物。本项目不在饮用水源准保护区内。符合4.禁止引入达不到清洁生产国际先进水平的企业。本项目为搬迁项目。符合5.在污水管网建设滞后或所依托的污水处理厂处理能力不能满足废水处理需求的区域，不应引入废水排放量较大的项目。扩区南片区在纳污水体水质稳定达标前，应合理控制涉水排放企业规模，优先引入无生产废水或生产废水排放量较小的项目；扩区东北组团应控制废水排放量较大企业的引入，引入涉水排放企业的规模应与区域污水处理厂处理能力相匹配，严格控制废水排放量较大的项目及新增一类水污染物排放项目的引入，避免对下游饮用水源保护区产生不良影响；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H59" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：地表水与废水执行标准；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I59" s="7" t="b">
         <x:v>1</x:v>
@@ -2215,7 +2215,7 @@
       <x:c r="J59" s="11" t="str"/>
       <x:c r="K59" s="11" t="str"/>
     </x:row>
-    <x:row r="60" ht="82.5" customHeight="1">
+    <x:row r="60" ht="88.5" customHeight="1">
       <x:c r="A60" s="6" t="str">
         <x:v>P006_Q09</x:v>
       </x:c>
@@ -2223,22 +2223,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C60" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D60" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>危险废物识别和危废代码</x:v>
       </x:c>
       <x:c r="E60" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的原辅材料、生产工艺、治理设施和固废清单，判断危险废物识别及危废代码是否完整、准确。</x:v>
       </x:c>
       <x:c r="F60" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查危险废物识别完整性。报告应结合原辅材料、生产工艺、废气治理设施和固废清单识别危险废物类别、代码和产生量。建议核查废包装物、废活性炭、废过滤材料、废抹布等是否遗漏，危废暂存能力是否匹配。</x:v>
       </x:c>
       <x:c r="G60" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。挤出、抽检工序废气经集气罩收集后通过二级活性炭吸附废气处理设施进行处理，处理达标后通过排气筒G1（30m）引至楼顶排放符合3.关于印发《重点行业挥发性有机物综合治理方案》的通知（环大气[2019]53 号）3.1含 VOCs 物料应储存于密闭容器、包装袋，高效密封储罐，封闭式储库、料仓等。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措 | 项目产生的一般工业固废分类收集，存储于一般固废暂存间内，一般固废暂存间的建设应满足《广东省固体废物污染环境防治条例》、《一般工业固体废物贮存和填埋污染控制标准》（GB18599-2020）以及《关于发布〈一般工业固体废物贮存、处置场污染控制标准〉（GB18599-2001）相关要求，加盖雨棚，地面采取水泥面硬化防渗措施等。项目一般固废产生量为20.3167t/a。员工生活垃圾收集后送交环卫部门集中处理，次品及水口料破碎后回用于生产过程，废塑料碎渣、废包装材料，收集后外卖给回收商。根据《危险废物产生单位危险废物规范化管理工作指引》：“贮存设施和场所，产生的危险废...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H60" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；标准条款；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I60" s="7" t="b">
         <x:v>1</x:v>
@@ -2246,7 +2246,7 @@
       <x:c r="J60" s="11" t="str"/>
       <x:c r="K60" s="11" t="str"/>
     </x:row>
-    <x:row r="61" ht="82.5" customHeight="1">
+    <x:row r="61" ht="88.5" customHeight="1">
       <x:c r="A61" s="6" t="str">
         <x:v>P006_Q10</x:v>
       </x:c>
@@ -2254,22 +2254,22 @@
         <x:v>202303061051125381佛山市顺德区启卓工程塑料实业有限公司搬迁项目(修改意见).docx</x:v>
       </x:c>
       <x:c r="C61" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D61" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E61" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F61" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G61" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...生产需要合理置贮存量，尽量减少厂内的物料贮存量；严禁将危险废物混入生活垃圾；堆放危险废物的地 方要有明显的标志，堆放点要防雨、防渗、防漏，应按要求进行包装贮存6废活性炭环保设施69.7296HW49类其他废物900-039-49固态有机物T防渗袋69.72967废含油桶罐生产过程0.0040HW08 废矿物油与含矿物油废物900-249-08固态矿物油T/In桶装0.00408含油废抹布设备维护0.02HW49类其他废物900-041-49固态矿物油T/In防渗袋0.02危险废物小计——69.8536————...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...次，暂存间贮存能力可满足危险废物的存储需求。表4-18 项目危险废物贮存场所（设施）基本情况序号贮存场所名称类别代码位置占地面积（m2）贮存方式能力（t）周期1危废暂存间废机油HW08废矿物油与含矿物油废物900-214-08生产车间东南侧10桶装101年2废活性炭HW49类其他废物900-039-49防渗袋1个月3废含油桶罐HW08 废矿物油与含矿物油废物900-249-08桶装1年4含油废抹布HW49类其他废物900-041-49防渗袋1年建设单位拟将危险废物交有危废处置资质单位处理。...</x:v>
       </x:c>
       <x:c r="H61" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I61" s="7" t="b">
         <x:v>1</x:v>
@@ -2277,7 +2277,7 @@
       <x:c r="J61" s="11" t="str"/>
       <x:c r="K61" s="11" t="str"/>
     </x:row>
-    <x:row r="62" ht="82.5" customHeight="1">
+    <x:row r="62" ht="88.5" customHeight="1">
       <x:c r="A62" s="6" t="str">
         <x:v>P007_Q01</x:v>
       </x:c>
@@ -2285,22 +2285,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C62" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D62" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E62" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F62" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：抽检工序产生的非甲烷总烃需要计算”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G62" s="6" t="str">
-        <x:v>Word批注/修改意见（第11条）写明：雷兆宇：抽检工序产生的非甲烷总烃需要计算</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...建设地点 | 佛山市顺德区杏坛镇顺业西路15号中集智能制造中心22栋101；地理坐标 | （东经113度11分58.650秒，北纬22度45分20.510秒）；国民经济行业类别 | C2929 塑料零件及其他塑料制品制造 | 建设项目行业类别 | 二十六、橡胶和塑料制品业29、53塑料制品业-292、其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）改建扩建技术改造 | 建设项目申报情形 | 首次申报项目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H62" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I62" s="7" t="b">
         <x:v>1</x:v>
@@ -2308,7 +2308,7 @@
       <x:c r="J62" s="11" t="str"/>
       <x:c r="K62" s="11" t="str"/>
     </x:row>
-    <x:row r="63" ht="82.5" customHeight="1">
+    <x:row r="63" ht="88.5" customHeight="1">
       <x:c r="A63" s="6" t="str">
         <x:v>P007_Q02</x:v>
       </x:c>
@@ -2316,22 +2316,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C63" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D63" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E63" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F63" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：产品2000吨，原辅材料才1940吨？”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G63" s="6" t="str">
-        <x:v>Word批注/修改意见（第3条）写明：雷兆宇：产品2000吨，原辅材料才1940吨？</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；项目审批（核准/备案）部门（选填） | / | 项目审批（核准/备案）文号（选填） | /；总投资（万元） | 150 | 环保投资（万元） | 15；环保投资占比（%） | 10 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H63" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I63" s="7" t="b">
         <x:v>1</x:v>
@@ -2339,7 +2339,7 @@
       <x:c r="J63" s="11" t="str"/>
       <x:c r="K63" s="11" t="str"/>
     </x:row>
-    <x:row r="64" ht="82.5" customHeight="1">
+    <x:row r="64" ht="88.5" customHeight="1">
       <x:c r="A64" s="6" t="str">
         <x:v>P007_Q03</x:v>
       </x:c>
@@ -2347,22 +2347,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C64" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D64" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E64" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F64" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：包围型集气罩收集效率应该为60%，保留10%余量，进行计算。原项目分析需要修改”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G64" s="6" t="str">
-        <x:v>Word批注/修改意见（第12条）写明：雷兆宇：包围型集气罩收集效率应该为60%，保留10%余量，进行计算。原项目分析需要修改</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 项目由来佛山市顺德区启卓工程塑料实业有限公司原名为佛山市顺德区杏坛镇启卓塑料五金厂，成立于2004年6月23日，位于顺德区杏坛镇七滘工业园光华区二路3号，占地面积为2500m2，建筑面积为2000m2，主要从事废旧塑料粒的生产，年产废旧塑料粒（PE、PP）1500吨，已于2005年已取得环保批准证（编号：20051004）。于2016年变更法人及项目名称为佛山市顺德区启卓工程塑料实业有限公司，并于2017年3月15日通过环保验收，并取得顺德区环境运输和城市管理局杏坛分局出具的《验收组意见》（顺环杏[2...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H64" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I64" s="7" t="b">
         <x:v>1</x:v>
@@ -2370,7 +2370,7 @@
       <x:c r="J64" s="11" t="str"/>
       <x:c r="K64" s="11" t="str"/>
     </x:row>
-    <x:row r="65" ht="82.5" customHeight="1">
+    <x:row r="65" ht="88.5" customHeight="1">
       <x:c r="A65" s="6" t="str">
         <x:v>P007_Q04</x:v>
       </x:c>
@@ -2378,22 +2378,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C65" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D65" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>污染物排放标准适用性</x:v>
       </x:c>
       <x:c r="E65" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据项目行业类别、生产工艺、污染因子和排放形式，判断废气、废水、噪声和固废相关排放标准选取是否合理。</x:v>
       </x:c>
       <x:c r="F65" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：是否合理？过滤风速计算错误。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查排放标准适用性。报告应结合行业类别、生产工艺、污染因子、有组织和无组织排放形式选取标准。建议核查是否遗漏厂区内VOCs无组织限值、厂界限值、排气筒排放限值或噪声、废水相关标准。</x:v>
       </x:c>
       <x:c r="G65" s="6" t="str">
-        <x:v>Word批注/修改意见（第17条）写明：雷兆宇：是否合理？过滤风速计算错误。</x:v>
+        <x:v>五、环境保护措施监督检查清单（表格）写明：内容要素 | 排放口(编号、名称)/污染源 | 污染物项目 | 环境保护措施 | 执行标准；大气环境 | 排气筒（G1） | 非甲烷总烃 | 挤出、抽检废气经包围型集气罩收集后通过“二级活性炭吸附装置”处理，尾气通过30m高的G1排气筒排放 | 《合成树脂工业污染物排放标准》（GB31572-2015）表5大气污染物特别排放限值；臭气浓度 | 《恶臭污染物排放标准》（GB14554-93）中表2中15m高排气筒排放标准值；生产车间 | 颗粒物 | 加强车间内通风换气 | 《合成树脂工业污染物排放标准》（GB31572-2015）表9企业边界大气污染物浓度限值要求；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H65" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#8_塑料制品业典型污染源及执行标准、GB_31572-2015、GB_37822-2019、DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I65" s="7" t="b">
         <x:v>1</x:v>
@@ -2401,7 +2401,7 @@
       <x:c r="J65" s="11" t="str"/>
       <x:c r="K65" s="11" t="str"/>
     </x:row>
-    <x:row r="66" ht="82.5" customHeight="1">
+    <x:row r="66" ht="88.5" customHeight="1">
       <x:c r="A66" s="6" t="str">
         <x:v>P007_Q05</x:v>
       </x:c>
@@ -2409,22 +2409,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C66" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D66" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E66" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F66" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：增加高新区区域环评相符性分析”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G66" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：增加高新区区域环评相符性分析</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：③挤出、抽检废气搬迁后项目挤出、抽检工序期间会产生有机废气，以非甲烷总烃表征。挤出过程非甲烷总烃产生系数参考《排放源统计调查产排污核算方法和系数手册-292塑料制品行业系数手册》2929塑料零件及其他塑料制品制造行业系数表-改性粒料-树脂、助剂-造粒中挥发性有机物产生系数为4.6kg/t-产品。本项目改性塑料粒年产量为2000t/a，由此可得，挤出、抽检工序非甲烷总烃产生量为9.2t/a。挤出、抽检废气经包围型集气罩收集后通过“二级活性炭吸附装置”处理，尾气通过30m高的G1排气筒排放。...</x:v>
       </x:c>
       <x:c r="H66" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I66" s="7" t="b">
         <x:v>1</x:v>
@@ -2432,7 +2432,7 @@
       <x:c r="J66" s="11" t="str"/>
       <x:c r="K66" s="11" t="str"/>
     </x:row>
-    <x:row r="67" ht="82.5" customHeight="1">
+    <x:row r="67" ht="88.5" customHeight="1">
       <x:c r="A67" s="6" t="str">
         <x:v>P007_Q06</x:v>
       </x:c>
@@ -2440,22 +2440,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C67" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D67" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E67" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F67" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G67" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | （1）废气源强核算项目废气产生、排放情况详见下表：表4-1 项目废气产生、排放情况一览表产品排气筒编号/车间名称产排污环节污染物种类污染物产生排放形式/治理设施污染物排放产生量（t/a）产生浓度（mg/m3）处理能力（m3/h）收集效率（%）治理工艺去除率（%）是否为可行技术可行性技术依据排放量（t/a）排放速率（kg/h）排放浓度（mg/m3）改性塑料粒生产车间混料颗粒物少量≤1.0无组织/////少量/≤1.0破碎颗粒物0.0106≤1.0/...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：③挤出、抽检废气搬迁后项目挤出、抽检工序期间会产生有机废气，以非甲烷总烃表征。挤出过程非甲烷总烃产生系数参考《排放源统计调查产排污核算方法和系数手册-292塑料制品行业系数手册》2929塑料零件及其他塑料制品制造行业系数表-改性粒料-树脂、助剂-造粒中挥发性有机物产生系数为4.6kg/t-产品。本项目改性塑料粒年产量为2000t/a，由此可得，挤出、抽检工序非甲烷总烃产生量为9.2t/a。挤出、抽检废气经包围型集气罩收集后通过“二级活性炭吸附装置”处理，尾气通过30m高的G1排气筒排放。风量计算：项目拟在拉粒机、注塑检测机、挤出检测机的出料口设置包围型集气罩正压排风收集产生的...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H67" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I67" s="7" t="b">
         <x:v>1</x:v>
@@ -2463,7 +2463,7 @@
       <x:c r="J67" s="11" t="str"/>
       <x:c r="K67" s="11" t="str"/>
     </x:row>
-    <x:row r="68" ht="82.5" customHeight="1">
+    <x:row r="68" ht="88.5" customHeight="1">
       <x:c r="A68" s="6" t="str">
         <x:v>P007_Q07</x:v>
       </x:c>
@@ -2471,22 +2471,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C68" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D68" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E68" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F68" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G68" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...源消耗等达到或优于国家下达的总量和强度符合控制目标。本项目不属于高耗能、污染资源型企业，用水来自市政管网，用电来自市政供电。本项目建成后通过内部管理、设备选择、原辅材料的选用和管理、废物回收利用、污染治理等方面采取可行的防治措施，以“节能、降耗、减污”为目标，有效的控制污染。项目的水、电等资源利用不会突破区域上线。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...发性有机物产生系数为4.6kg/t-产品。本项目改性塑料粒年产量为2000t/a，由此可得，挤出、抽检工序非甲烷总烃产生量为9.2t/a。挤出、抽检废气经包围型集气罩收集后通过“二级活性炭吸附装置”处理，尾气通过30m高的G1排气筒排放。风量计算：项目拟在拉粒机、注塑检测机、挤出检测机的出料口设置包围型集气罩正压排风收集产生的非甲烷总烃，集气罩尺寸均约为长0.6m*宽0.6m，收集后经二级活性炭处理后通过30米排气筒G1排放。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H68" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I68" s="7" t="b">
         <x:v>1</x:v>
@@ -2494,7 +2494,7 @@
       <x:c r="J68" s="11" t="str"/>
       <x:c r="K68" s="11" t="str"/>
     </x:row>
-    <x:row r="69" ht="82.5" customHeight="1">
+    <x:row r="69" ht="88.5" customHeight="1">
       <x:c r="A69" s="6" t="str">
         <x:v>P007_Q08</x:v>
       </x:c>
@@ -2502,22 +2502,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C69" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D69" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E69" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F69" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G69" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...发性有机物产生系数为4.6kg/t-产品。本项目改性塑料粒年产量为2000t/a，由此可得，挤出、抽检工序非甲烷总烃产生量为9.2t/a。挤出、抽检废气经包围型集气罩收集后通过“二级活性炭吸附装置”处理，尾气通过30m高的G1排气筒排放。风量计算：项目拟在拉粒机、注塑检测机、挤出检测机的出料口设置包围型集气罩正压排风收集产生的非甲烷总烃，集气罩尺寸均约为长0.6m*宽0.6m，收集后经二级活性炭处理后通过30米排气筒G1排放。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。挤出、抽检工序废气经集气罩收集后通过二级活性炭吸附废气处理设施进行处理，处理达标后通过排气筒G1（30m）引至楼顶排放符合3.关于印发《重点行业挥发性有机物综合治理方案》的通知（环大气[2019]53 号）3.1含 VOCs 物料应储存于密闭容器、包装袋，高效密封储罐，封闭式储库、料仓等。含VOCs物料生产和使用过程，应采取有效收集措施或在密闭空间中操作。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H69" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I69" s="7" t="b">
         <x:v>1</x:v>
@@ -2525,7 +2525,7 @@
       <x:c r="J69" s="11" t="str"/>
       <x:c r="K69" s="11" t="str"/>
     </x:row>
-    <x:row r="70" ht="82.5" customHeight="1">
+    <x:row r="70" ht="88.5" customHeight="1">
       <x:c r="A70" s="6" t="str">
         <x:v>P007_Q09</x:v>
       </x:c>
@@ -2533,22 +2533,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C70" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D70" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E70" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F70" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G70" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。挤出、抽检工序废气经集气罩收集后通过二级活性炭吸附废气处理设施进行处理，处理达标后通过排气筒G1（30m）引至楼顶排放符合3.关于印发《重点行业挥发性有机物综合治理方案》的通知（环大气[2019]53 号）3.1含 VOCs 物料应储存于密闭容器、包装袋，高效密封储罐，封闭式储库、料仓等。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...，除臭氧浓度不达标外，其余污染物指标浓度均达到《环境空气质量标准》（GB3095-2012）二级标准限值及2018年修改单。本项目产生的有机废气经集气罩收集通过二级活性炭吸附装置处理后引至30m高排气筒G1高空排放，对周边环境影响较小；生活污水经三级化粪池预处理达标后，通过市政污水管网排入杏坛生活污水处理厂处理，尾水排至顺德支流，对周围环境影响较小，本项目排放的污染物不会导致区域环境质量超标，符合环境质量底线要求。③资源利用上线强化节约集约利用，持续提升资源能源利用效率，水资源、土地资源、岸线资源、能源消耗等达到或优于国家下达的总量和强度符合控制目标。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H70" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I70" s="7" t="b">
         <x:v>1</x:v>
@@ -2556,7 +2556,7 @@
       <x:c r="J70" s="11" t="str"/>
       <x:c r="K70" s="11" t="str"/>
     </x:row>
-    <x:row r="71" ht="82.5" customHeight="1">
+    <x:row r="71" ht="88.5" customHeight="1">
       <x:c r="A71" s="6" t="str">
         <x:v>P007_Q10</x:v>
       </x:c>
@@ -2564,22 +2564,22 @@
         <x:v>20230406116394523佛山市顺德区启卓工程塑料实业有限公司搬迁项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C71" s="6" t="str">
-        <x:v>| 佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
+        <x:v>佛山市顺德区启卓工程塑料实业有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D71" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E71" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F71" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G71" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...生产需要合理置贮存量，尽量减少厂内的物料贮存量；严禁将危险废物混入生活垃圾；堆放危险废物的地 方要有明显的标志，堆放点要防雨、防渗、防漏，应按要求进行包装贮存6废活性炭环保设施63.15HW49类其他废物900-039-49固态有机物T防渗袋63.157废含油桶罐生产过程0.0040HW08 废矿物油与含矿物油废物900-249-08固态矿物油T/In桶装0.00408含油废抹布设备维护0.02HW49类其他废物900-041-49固态矿物油T/In防渗袋0.02危险废物小计——63.274—————————...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...次，暂存间贮存能力可满足危险废物的存储需求。表4-18 项目危险废物贮存场所（设施）基本情况序号贮存场所名称类别代码位置占地面积（m2）贮存方式能力（t）周期1危废暂存间废机油HW08废矿物油与含矿物油废物900-214-08生产车间东南侧10桶装101年2废活性炭HW49类其他废物900-039-49防渗袋1个月3废含油桶罐HW08 废矿物油与含矿物油废物900-249-08桶装1年4含油废抹布HW49类其他废物900-041-49防渗袋1年建设单位拟将危险废物交有危废处置资质单位处理。...</x:v>
       </x:c>
       <x:c r="H71" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I71" s="7" t="b">
         <x:v>1</x:v>
@@ -2587,7 +2587,7 @@
       <x:c r="J71" s="11" t="str"/>
       <x:c r="K71" s="11" t="str"/>
     </x:row>
-    <x:row r="72" ht="82.5" customHeight="1">
+    <x:row r="72" ht="88.5" customHeight="1">
       <x:c r="A72" s="6" t="str">
         <x:v>P008_Q01</x:v>
       </x:c>
@@ -2595,22 +2595,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C72" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D72" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E72" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F72" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：非甲烷总烃”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G72" s="6" t="str">
-        <x:v>Word批注/修改意见（第17条）写明：雷兆宇：非甲烷总烃</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...区杏坛镇齐杏社区杏坛工业区科技二路2号威和新科园6栋；地理坐标 | （北纬 22 度 47 分 11.7871秒，东经 113 度 10分 35.3206秒）；国民经济行业类别 | C3852家用空气调节器制造C3853家用通风电器具制造 | 建设项目行业类别 | “三十五、电气机械和器材制造业38”中的“77家用电力器具制造385；”中的“其他（仅分割、焊接、组装的除外；年用非溶剂型低VOCs含量涂料10吨以下的除外）”；建设性质 | 新建（迁建）改建扩建技术改造 | 建设项目申报情形 | 首次申报项目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H72" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I72" s="7" t="b">
         <x:v>1</x:v>
@@ -2618,7 +2618,7 @@
       <x:c r="J72" s="11" t="str"/>
       <x:c r="K72" s="11" t="str"/>
     </x:row>
-    <x:row r="73" ht="82.5" customHeight="1">
+    <x:row r="73" ht="88.5" customHeight="1">
       <x:c r="A73" s="6" t="str">
         <x:v>P008_Q02</x:v>
       </x:c>
@@ -2626,22 +2626,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C73" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D73" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E73" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F73" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：油墨和涂料计算方式不一样，油墨应该根据单位面积产品油墨用量（有推荐标准）倒推”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G73" s="6" t="str">
-        <x:v>Word批注/修改意见（第9条）写明：雷兆宇：油墨和涂料计算方式不一样，油墨应该根据单位面积产品油墨用量（有推荐标准）倒推</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；项目审批（核准/备案）部门（选填） | / | 项目审批（核准/备案）文号（选填） | /；总投资（万元） | 502 | 环保投资（万元） | 50；环保投资占比（%） | 9.96 | 施工工期 | 2个月</x:v>
       </x:c>
       <x:c r="H73" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I73" s="7" t="b">
         <x:v>1</x:v>
@@ -2649,7 +2649,7 @@
       <x:c r="J73" s="11" t="str"/>
       <x:c r="K73" s="11" t="str"/>
     </x:row>
-    <x:row r="74" ht="82.5" customHeight="1">
+    <x:row r="74" ht="88.5" customHeight="1">
       <x:c r="A74" s="6" t="str">
         <x:v>P008_Q03</x:v>
       </x:c>
@@ -2657,22 +2657,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C74" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D74" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E74" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F74" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：活性炭碳箱大小，过滤面积、停留时间等”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G74" s="6" t="str">
-        <x:v>Word批注/修改意见（第28条）写明：雷兆宇：活性炭碳箱大小，过滤面积、停留时间等</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1.项目工程组成广东威诺高科技股份有限公司原址位于佛山市顺德区罗水社区居民委员会杏龙路罗水工业区大道 1 号之五。该厂于2020年8月5日以《广东威诺高科技股份有限公司建设项目》环评报告表报批，经佛山市顺德区环境运输和城市管理局杏坛分局的批复文号为顺环0310环审〔2020〕第0236号。现因发展需要，拟搬迁至广东省佛山市顺德区杏坛镇齐杏社区杏坛工业区科技二路2号威和新科园6栋，6栋所在楼栋为9层建筑，首层高7米、2~5层高6米、6~7层高5米、8~9层高4.5米，合计建筑高度为50m。项目占地面积1...</x:v>
       </x:c>
       <x:c r="H74" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I74" s="7" t="b">
         <x:v>1</x:v>
@@ -2680,7 +2680,7 @@
       <x:c r="J74" s="11" t="str"/>
       <x:c r="K74" s="11" t="str"/>
     </x:row>
-    <x:row r="75" ht="82.5" customHeight="1">
+    <x:row r="75" ht="88.5" customHeight="1">
       <x:c r="A75" s="6" t="str">
         <x:v>P008_Q04</x:v>
       </x:c>
@@ -2688,22 +2688,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C75" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D75" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>污染物排放标准适用性</x:v>
       </x:c>
       <x:c r="E75" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据项目行业类别、生产工艺、污染因子和排放形式，判断废气、废水、噪声和固废相关排放标准选取是否合理。</x:v>
       </x:c>
       <x:c r="F75" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：确认是否为负压？”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查排放标准适用性。报告应结合行业类别、生产工艺、污染因子、有组织和无组织排放形式选取标准。建议核查是否遗漏厂区内VOCs无组织限值、厂界限值、排气筒排放限值或噪声、废水相关标准。</x:v>
       </x:c>
       <x:c r="G75" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：确认是否为负压？</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | 表4-10项目废气排放口信息一览表排放口编号及名称排放口基本情况地理坐标高度m内径m烟气流速m/s温度℃类型排气筒DA001530.621.6225一般排放口E113.1712°，N22.7865°注：根据《大气污染治理工程技术导则》HJ2000-2010之5.3污染气体的排放之5.3.5排气筒的出口直径应根据出口流速确定，流速宜取15m/s左右。当采用钢管烟囱且高度较高时或烟气量较大时，可适当提高出口流速至20～25m/s。本项目排气筒烟气流速为21.62m/s，排气筒的设置合理。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H75" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#8_塑料制品业典型污染源及执行标准、GB_31572-2015、GB_37822-2019、DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I75" s="7" t="b">
         <x:v>1</x:v>
@@ -2711,7 +2711,7 @@
       <x:c r="J75" s="11" t="str"/>
       <x:c r="K75" s="11" t="str"/>
     </x:row>
-    <x:row r="76" ht="82.5" customHeight="1">
+    <x:row r="76" ht="88.5" customHeight="1">
       <x:c r="A76" s="6" t="str">
         <x:v>P008_Q05</x:v>
       </x:c>
@@ -2719,22 +2719,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C76" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D76" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E76" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F76" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G76" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...烘干、丝印和烘干均位于独立的房间内。表4-1本项目风机风量计算一览表设备罩口长度（m）污染源至罩口距离（m）风速（m/s）单台设备风量（m3/h）设备数量（台）核算风量（m3/h）注塑机（型号1）0.60.41.086486912注塑机（型号2）0.50.41.072064320污染源罩内容积（m3）换气次数（次/h）换气次数（次/h）数量（个）核算风量（m3/h）浸漆房 5.0m×7.3m×3.6m131.43013942丝印房4.8m×5.7m×3.6m98.[电话已脱敏].88合计18128.88备注：...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...）的表2-3，活性炭吸附的处理效率为30%，则两级活性炭吸附的综合处理效率为1-（1-30%）×（1-30%）=51%。项目采用《排放源统计调查产排污核算方法和系数手册》、《污染源源强核算技术指南 准则HJ884—2018》、《排污单位自行监测技术指南总则（HJ 819-2017）》。（1）浸漆、烘干有机废气（排气筒DA001）本项目浸漆、烘干过程会产生有机废气，污染因子以NMHC表征。根据建设单位提供的成分报告，项目所用原料均不含苯、甲苯、二甲苯。根据VOCs含量报告（详见附件6），水性绝缘漆的VOCs含量为12g/L（密度为1.018g/cm3)。...</x:v>
       </x:c>
       <x:c r="H76" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I76" s="7" t="b">
         <x:v>1</x:v>
@@ -2742,7 +2742,7 @@
       <x:c r="J76" s="11" t="str"/>
       <x:c r="K76" s="11" t="str"/>
     </x:row>
-    <x:row r="77" ht="82.5" customHeight="1">
+    <x:row r="77" ht="88.5" customHeight="1">
       <x:c r="A77" s="6" t="str">
         <x:v>P008_Q06</x:v>
       </x:c>
@@ -2750,22 +2750,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C77" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D77" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E77" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F77" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G77" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...+垂帘收集的方式，污染物产生点（或生产设施）四周及上下有围挡设施，符合以下情况：通过软质垂帘四周围挡（偶有部分敞开），以此提高废气的收集效率。根据《广东省工业源挥发性有机物减排量核算方法（试行）》（2021年12月27日）中表4.5-1废气收集集气效率参考值，本项目废气收集方式为包围型集气设备，敞开面控制风速不小于0.5m/s，则收集效率可取60%。环评报告收集效率应当预留（10%以上）余量，不宜取理论最高值，因此本报告取50%。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...烘干、丝印和烘干均位于独立的房间内。表4-1本项目风机风量计算一览表设备罩口长度（m）污染源至罩口距离（m）风速（m/s）单台设备风量（m3/h）设备数量（台）核算风量（m3/h）注塑机（型号1）0.60.41.086486912注塑机（型号2）0.50.41.072064320污染源罩内容积（m3）换气次数（次/h）换气次数（次/h）数量（个）核算风量（m3/h）浸漆房 5.0m×7.3m×3.6m131.43013942丝印房4.8m×5.7m×3.6m98.[电话已脱敏].88合计18128.88备注：搬迁后项目注塑机共14台，具体型号如表2-5。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H77" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I77" s="7" t="b">
         <x:v>1</x:v>
@@ -2773,7 +2773,7 @@
       <x:c r="J77" s="11" t="str"/>
       <x:c r="K77" s="11" t="str"/>
     </x:row>
-    <x:row r="78" ht="82.5" customHeight="1">
+    <x:row r="78" ht="88.5" customHeight="1">
       <x:c r="A78" s="6" t="str">
         <x:v>P008_Q07</x:v>
       </x:c>
@@ -2781,22 +2781,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C78" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D78" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E78" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F78" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G78" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...；运营期环境影响和保护措施 | 大气污染源1.1废气产污环节根据《废气处理工程技术手册》（王纯、张殿印主编，化学工业出版社，2013版），注塑机上方的点对点局部集气罩+垂帘的排气量Q1的计算公式如下：Q1 =WHvxQ1：所需风量，m3/h；W：罩口长度，m；F：污染源至罩口距离，m2；v：0.25～2.5m/s。根据《废气处理工程技术手册》（王纯、张殿印主编，化学工业出版社，2013版），浸漆和烘干、丝印和烘干均位于独立的房间内。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...；运营期环境影响和保护措施 | 大气污染源1.1废气产污环节根据《废气处理工程技术手册》（王纯、张殿印主编，化学工业出版社，2013版），注塑机上方的点对点局部集气罩+垂帘的排气量Q1的计算公式如下：Q1 =WHvxQ1：所需风量，m3/h；W：罩口长度，m；F：污染源至罩口距离，m2；v：0.25～2.5m/s。根据《废气处理工程技术手册》（王纯、张殿印主编，化学工业出版社，2013版），浸漆和烘干、丝印和烘干均位于独立的房间内。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H78" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I78" s="7" t="b">
         <x:v>1</x:v>
@@ -2804,7 +2804,7 @@
       <x:c r="J78" s="11" t="str"/>
       <x:c r="K78" s="11" t="str"/>
     </x:row>
-    <x:row r="79" ht="82.5" customHeight="1">
+    <x:row r="79" ht="88.5" customHeight="1">
       <x:c r="A79" s="6" t="str">
         <x:v>P008_Q08</x:v>
       </x:c>
@@ -2812,22 +2812,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C79" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D79" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集风量与设计风量核算</x:v>
       </x:c>
       <x:c r="E79" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的集气罩尺寸、控制风速、收集点数量和风量计算过程，判断设计风量是否具有可复核性。</x:v>
       </x:c>
       <x:c r="F79" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查风量计算是否可复核。报告应说明收集点数量、罩口尺寸、控制风速或换气次数，并形成可追溯的设计风量。建议核查计算公式、取值依据、风机风量裕量和治理设施处理风量是否匹配。</x:v>
       </x:c>
       <x:c r="G79" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...污染防治推荐可行技术产排污环节污染物种类可行技术项目治理设施名称依据来源注塑、丝印、固化、清洁、浸漆、烘干非甲烷总烃喷淋、吸附、吸附浓缩+热力燃烧/催化燃烧两级活性炭吸附《排污许可证申请与核发技术规范 橡胶和塑料制品工业（HJ 1122-2020）》中的表A.2臭气浓度喷淋、吸附、低温等离子体、UV光氧化/光催化、生物法、以上组合技术由上表可知，项目采取“两级活性炭吸附”技术去处理项目注塑产生的非甲烷总烃是可行的。吸附法是用固体吸附剂吸附处理废气中有害气体的一种方法。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...响和保护措施 | 大气污染源1.1废气产污环节根据《废气处理工程技术手册》（王纯、张殿印主编，化学工业出版社，2013版），注塑机上方的点对点局部集气罩+垂帘的排气量Q1的计算公式如下：Q1 =WHvxQ1：所需风量，m3/h；W：罩口长度，m；F：污染源至罩口距离，m2；v：0.25～2.5m/s。根据《废气处理工程技术手册》（王纯、张殿印主编，化学工业出版社，2013版），浸漆和烘干、丝印和烘干均位于独立的房间内。...</x:v>
       </x:c>
       <x:c r="H79" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集风量与设计风量核算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I79" s="7" t="b">
         <x:v>1</x:v>
@@ -2835,7 +2835,7 @@
       <x:c r="J79" s="11" t="str"/>
       <x:c r="K79" s="11" t="str"/>
     </x:row>
-    <x:row r="80" ht="82.5" customHeight="1">
+    <x:row r="80" ht="88.5" customHeight="1">
       <x:c r="A80" s="6" t="str">
         <x:v>P008_Q09</x:v>
       </x:c>
@@ -2843,22 +2843,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C80" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D80" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E80" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F80" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G80" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...污染防治推荐可行技术产排污环节污染物种类可行技术项目治理设施名称依据来源注塑、丝印、固化、清洁、浸漆、烘干非甲烷总烃喷淋、吸附、吸附浓缩+热力燃烧/催化燃烧两级活性炭吸附《排污许可证申请与核发技术规范 橡胶和塑料制品工业（HJ 1122-2020）》中的表A.2臭气浓度喷淋、吸附、低温等离子体、UV光氧化/光催化、生物法、以上组合技术由上表可知，项目采取“两级活性炭吸附”技术去处理项目注塑产生的非甲烷总烃是可行的。吸附法是用固体吸附剂吸附处理废气中有害气体的一种方法。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...施可行性分析 表4-12 相关文件废气污染防治推荐可行技术产排污环节污染物种类可行技术项目治理设施名称依据来源注塑、丝印、固化、清洁、浸漆、烘干非甲烷总烃喷淋、吸附、吸附浓缩+热力燃烧/催化燃烧两级活性炭吸附《排污许可证申请与核发技术规范 橡胶和塑料制品工业（HJ 1122-2020）》中的表A.2臭气浓度喷淋、吸附、低温等离子体、UV光氧化/光催化、生物法、以上组合技术由上表可知，项目采取“两级活性炭吸附”技术去处理项目注塑产生的非甲烷总烃是可行的。吸附法是用固体吸附剂吸附处理废气中有害气体的一种方法。选择吸附剂的原则是比表面积大，容易吸附和脱附再生，来源容易，价格较低。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H80" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I80" s="7" t="b">
         <x:v>1</x:v>
@@ -2866,7 +2866,7 @@
       <x:c r="J80" s="11" t="str"/>
       <x:c r="K80" s="11" t="str"/>
     </x:row>
-    <x:row r="81" ht="82.5" customHeight="1">
+    <x:row r="81" ht="88.5" customHeight="1">
       <x:c r="A81" s="6" t="str">
         <x:v>P008_Q10</x:v>
       </x:c>
@@ -2874,22 +2874,22 @@
         <x:v>202307319405849广东威诺高科技股份有限公司搬迁项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C81" s="6" t="str">
-        <x:v>| 广东威诺高科技股份有限公司搬迁项目</x:v>
+        <x:v>广东威诺高科技股份有限公司搬迁项目</x:v>
       </x:c>
       <x:c r="D81" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E81" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F81" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G81" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...转仓。储运工程2楼仓库1756.76m2层高6m，设有呆滞物资仓、成品仓。3楼仓库1756.76m2层高6m，设有待发展区、废品回收放置区、固废仓（50m2）、危废仓（10m2）辅助工程8楼车间（实验室）1756.76m2层高4.5m，用于原料的测试，属于验货房，设有实验室、呆滞物资区。9楼车间（办公区）1756.76m2层高4.5m，用于人员办公和接待客人的场所。设有卫生间、办公区、会议室、待客区、展厅等。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...转仓。储运工程2楼仓库1756.76m2层高6m，设有呆滞物资仓、成品仓。3楼仓库1756.76m2层高6m，设有待发展区、废品回收放置区、固废仓（50m2）、危废仓（10m2）辅助工程8楼车间（实验室）1756.76m2层高4.5m，用于原料的测试，属于验货房，设有实验室、呆滞物资区。9楼车间（办公区）1756.76m2层高4.5m，用于人员办公和接待客人的场所。设有卫生间、办公区、会议室、待客区、展厅等。公用工程供电系统1套由市政电网供应，项目内不设置备用发电机给水系统1套由市政供水管网供给排水系统1套生活污水经三级化粪池处理后排入杏坛污水处理厂，尾水排入顺德支流；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H81" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I81" s="7" t="b">
         <x:v>1</x:v>
@@ -2897,7 +2897,7 @@
       <x:c r="J81" s="11" t="str"/>
       <x:c r="K81" s="11" t="str"/>
     </x:row>
-    <x:row r="82" ht="82.5" customHeight="1">
+    <x:row r="82" ht="88.5" customHeight="1">
       <x:c r="A82" s="6" t="str">
         <x:v>P009_Q01</x:v>
       </x:c>
@@ -2908,19 +2908,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D82" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E82" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F82" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：罩口速度0.5 控制面风速多少是否能达到最低要求0.3.减排文件风速是控制面风速，请根据罩口到控制面距离，计算控制面风速。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G82" s="6" t="str">
-        <x:v>Word批注/修改意见（第18条）写明：雷兆宇：罩口速度0.5 控制面风速多少是否能达到最低要求0.3.减排文件风速是控制面风速，请根据罩口到控制面距离，计算控制面风速。</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...m2，总建筑面积约为1900m2，从事塑料薄膜的加工生产，年产塑料薄膜242.368吨，主要用作保护膜用途。现申请办理相关环保手续。表2-1 项目所属行业分析表行业类别类别项目情况《国民经济行业分类》（GB/T 4754-2017）（2019年修订）项目主要从事塑料薄膜的加工生产，属于C2921塑料薄膜制造行业。C制造业大类中类小类29橡胶和塑料制品业292塑料制品业2921塑料薄膜制造《建设项目环境影响评价分类管理名录》（2021年版）项目主要从事塑料薄膜的加工生产，本项目设有混料、吹膜、涂布、烘干、分切、复卷、检验。本项目使用的保护胶涂布胶属于低VOCs含量胶水，故应编制报告表。...</x:v>
       </x:c>
       <x:c r="H82" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I82" s="7" t="b">
         <x:v>1</x:v>
@@ -2928,7 +2928,7 @@
       <x:c r="J82" s="11" t="str"/>
       <x:c r="K82" s="11" t="str"/>
     </x:row>
-    <x:row r="83" ht="82.5" customHeight="1">
+    <x:row r="83" ht="88.5" customHeight="1">
       <x:c r="A83" s="6" t="str">
         <x:v>P009_Q02</x:v>
       </x:c>
@@ -2939,19 +2939,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D83" s="6" t="str">
-        <x:v>废水去向与冷却水</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E83" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废水去向与冷却水相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F83" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：是否为间接冷却水，间接冷却水直接排入雨水管即可。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G83" s="6" t="str">
-        <x:v>Word批注/修改意见（第13条）写明：雷兆宇：是否为间接冷却水，间接冷却水直接排入雨水管即可。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...批准后再次申报项目 □超五年重新审核项目□重大变动重新报批项目；项目审批（核准/ 备案）部门（选填） | / | 项目审批（核准/ 备案）文号（选填） | /；总投资（万元） | 100.00 | 环保投资（万元） | 15.00；环保投资占比（%） | 15.00 | 施工工期 | 2个月</x:v>
       </x:c>
       <x:c r="H83" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I83" s="7" t="b">
         <x:v>1</x:v>
@@ -2959,7 +2959,7 @@
       <x:c r="J83" s="11" t="str"/>
       <x:c r="K83" s="11" t="str"/>
     </x:row>
-    <x:row r="84" ht="82.5" customHeight="1">
+    <x:row r="84" ht="88.5" customHeight="1">
       <x:c r="A84" s="6" t="str">
         <x:v>P009_Q03</x:v>
       </x:c>
@@ -2970,19 +2970,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D84" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>三线一单管控内容一致性</x:v>
       </x:c>
       <x:c r="E84" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的项目位置、经纬度、环境管控单元和项目排污特征，判断三线一单符合性分析是否充分。</x:v>
       </x:c>
       <x:c r="F84" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：重点区域 2kg/h”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查三线一单分析是否逐项对应。报告应明确项目所在管控单元、准入要求和项目排污特征，并说明与空间布局、污染物排放、环境风险和资源利用要求的对应关系。建议核查是否存在只作概括性符合结论、未结合项目工艺和污染物特征的问题。</x:v>
       </x:c>
       <x:c r="G84" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：重点区域 2kg/h</x:v>
+        <x:v>六、结论（正文）写明：附图11 广东省“三线一单”应用平台——陆域重点管控单元</x:v>
       </x:c>
       <x:c r="H84" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#4_三线一单、顺德管控单元准入清单</x:v>
       </x:c>
       <x:c r="I84" s="7" t="b">
         <x:v>1</x:v>
@@ -2990,7 +2990,7 @@
       <x:c r="J84" s="11" t="str"/>
       <x:c r="K84" s="11" t="str"/>
     </x:row>
-    <x:row r="85" ht="82.5" customHeight="1">
+    <x:row r="85" ht="88.5" customHeight="1">
       <x:c r="A85" s="6" t="str">
         <x:v>P009_Q04</x:v>
       </x:c>
@@ -3001,19 +3001,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D85" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E85" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F85" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G85" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | 1.3正常排放情况根据《广东省工业源挥发性有机物减排量核算方法（2023年修订）》，采用全过程物料衡算法进行计算，物料衡算法中VOCs产生量与去除量之差值核定为VOCs排放量，VOCs产生量为VOCs投用量与VOCs回收量之差，计算公式如下：E排放 = E投用 - E回收 - E去除式中：E排放—减排期内VOCs排放量，吨； E投用—减排期内使用物料中VOCs量之和，吨； E回收—减排期内各种VOCs溶剂与废弃物回收物中不用于循环使用的VOCs量之和，吨；...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1.项目概况及任务来源佛山市顺德区康明新材料厂新建项目（以下简称“项目”）选址位于广东省佛山市顺德区杏坛镇吉祐工业区三路2号（地理位置详见附图1），营业执照的统一社会信用代码为91440606MAD0EWB20F，属于新建项目。厂址在卫星影像图上的经纬度为：北纬：22°50′26.033″，东经：113°6′45.284″。经营范围：一般项目：新材料技术研发；塑料制品制造。（除依法须经批准的项目外，凭营业执照依法自主开展经营活动）项目总投资100万元，其中环保投资15万元，总占地面积约为1900m2，...</x:v>
       </x:c>
       <x:c r="H85" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I85" s="7" t="b">
         <x:v>1</x:v>
@@ -3021,7 +3021,7 @@
       <x:c r="J85" s="11" t="str"/>
       <x:c r="K85" s="11" t="str"/>
     </x:row>
-    <x:row r="86" ht="82.5" customHeight="1">
+    <x:row r="86" ht="88.5" customHeight="1">
       <x:c r="A86" s="6" t="str">
         <x:v>P009_Q05</x:v>
       </x:c>
@@ -3032,19 +3032,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D86" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E86" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F86" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G86" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | 1.3正常排放情况根据《广东省工业源挥发性有机物减排量核算方法（2023年修订）》，采用全过程物料衡算法进行计算，物料衡算法中VOCs产生量与去除量之差值核定为VOCs排放量，VOCs产生量为VOCs投用量与VOCs回收量之差，计算公式如下：E排放 = E投用 - E回收 - E去除式中：E排放—减排期内VOCs排放量，吨； E投用—减排期内使用物料中VOCs量之和，吨； E回收—减排期内各种VOCs溶剂与废弃物回收物中不用于循环使用的VOCs量之和，吨； E去除—减排期...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...塑胶粒分解温度约为300℃。项目吹膜成型工序工作温度约为PE塑胶为140℃（电能加热），低于其分解温度，会产生少量有机废气，主要成分为非甲烷总烃。项目非甲烷总烃产污系数根据《排放源统计调查产排污核算方法和系数手册》（公告2021年第24号）中“292塑料制品行业系数手册”中“2921塑料薄膜制造行业系数表”的排污系数，详见下表4-5：表4-5 塑料薄膜制造行业系数一览表行业类别核算环节产品名称原料名称工艺名称规模等级污染物类别污染物指标系数单位产污系数2921/塑料薄膜树脂、助剂配料－混合－挤出所有规模废气挥发性有机物（以非甲烷总烃计）千克/吨－产品2.5根据建设单位提供的资料，本项目吹...</x:v>
       </x:c>
       <x:c r="H86" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I86" s="7" t="b">
         <x:v>1</x:v>
@@ -3052,7 +3052,7 @@
       <x:c r="J86" s="11" t="str"/>
       <x:c r="K86" s="11" t="str"/>
     </x:row>
-    <x:row r="87" ht="82.5" customHeight="1">
+    <x:row r="87" ht="88.5" customHeight="1">
       <x:c r="A87" s="6" t="str">
         <x:v>P009_Q06</x:v>
       </x:c>
@@ -3063,19 +3063,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D87" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E87" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F87" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G87" s="6" t="str">
-        <x:v>五、环境保护措施监督检查清单（表格）写明：...排放口（编号、名称）/污染源 | 污染物项目 | 环境保护措施 | 执行标准；大气环境 | 吹膜、涂布、烘干 | 排气筒DA001 | 非甲烷总烃 | 项目利用集气罩+垂帘收集后利用二级活性炭吸附装置处理后引至15m排气筒DA001高空排放 | 《合成树脂工业污染物排放标准》（GB31572-2015）表5大气污染物特别排放限值和广东省《固定污染源挥发性有机物综合排放标准》（DB44/2367-2022）表1大气污染物排放限值的较严值；...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...性分析内容参照《排污许可证申请与核发技术规范 橡胶和塑料制品工业》（HJ1122-2020）进行分析。一、大气污染源1.1大气污染物产排情况汇总本项目废气污染源源强核算结果及相关参数一览表详见表4-1所示：表4-1 废气污染源源强核算结果及相关参数一览表工序/生产线污染源污染物污染物产生治理措施污染物排放排放时间/h核算方法废气产生量/（m3/h）收集效率%产生浓度/（mg/m3）产生速率/（kg/h）产生量/（t/a）工艺效率%核算方法废气排放量/（m3/h）排放浓度/（mg/m3）排放速率/（kg/h）排放量/（t/a）吹膜、涂布、烘干DA001非甲烷总烃系数核算法80005015....</x:v>
       </x:c>
       <x:c r="H87" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I87" s="7" t="b">
         <x:v>1</x:v>
@@ -3083,7 +3083,7 @@
       <x:c r="J87" s="11" t="str"/>
       <x:c r="K87" s="11" t="str"/>
     </x:row>
-    <x:row r="88" ht="82.5" customHeight="1">
+    <x:row r="88" ht="88.5" customHeight="1">
       <x:c r="A88" s="6" t="str">
         <x:v>P009_Q07</x:v>
       </x:c>
@@ -3094,19 +3094,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D88" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E88" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F88" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G88" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...见表4-1所示：表4-1 废气污染源源强核算结果及相关参数一览表工序/生产线污染源污染物污染物产生治理措施污染物排放排放时间/h核算方法废气产生量/（m3/h）收集效率%产生浓度/（mg/m3）产生速率/（kg/h）产生量/（t/a）工艺效率%核算方法废气排放量/（m3/h）排放浓度/（mg/m3）排放速率/（kg/h）排放量/（t/a）吹膜、涂布、烘干DA001非甲烷总烃系数核算法80005015.750.1260.302二级活性炭吸附装置51系数核算法80007.750.0620.1482400臭气浓度/...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...外，相应的会伴有明显的异味，需要作为恶臭进行管理和控制。本次评价统一以臭气浓度进行表征。该类异味覆盖范围仅限于生产设备至生产车间边界，对外环境影响较小。异味通过废气收集系统和“二级活性炭吸附装置”治理后与有机废气一同排放， 少部分未能被收集的异味以无组织形式在车间排放，通过加强车间通风，该类异味对周边环境的影响不大，能够满足《恶臭污染物排放标准》（GB14554-93）中臭气浓度排放标准的要求，即臭气浓度有组织排放浓度小于2000（无量纲），无组织排放浓度小于20（无量纲）。1.3.1.2非甲烷总烃项目吹膜过程中需要对PE塑胶粒进行加热熔融再吹膜成型，其中PE塑胶粒分解温度约为300℃。...</x:v>
       </x:c>
       <x:c r="H88" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I88" s="7" t="b">
         <x:v>1</x:v>
@@ -3114,7 +3114,7 @@
       <x:c r="J88" s="11" t="str"/>
       <x:c r="K88" s="11" t="str"/>
     </x:row>
-    <x:row r="89" ht="82.5" customHeight="1">
+    <x:row r="89" ht="88.5" customHeight="1">
       <x:c r="A89" s="6" t="str">
         <x:v>P009_Q08</x:v>
       </x:c>
@@ -3125,19 +3125,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D89" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>废气收集风量与设计风量核算</x:v>
       </x:c>
       <x:c r="E89" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的集气罩尺寸、控制风速、收集点数量和风量计算过程，判断设计风量是否具有可复核性。</x:v>
       </x:c>
       <x:c r="F89" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查风量计算是否可复核。报告应说明收集点数量、罩口尺寸、控制风速或换气次数，并形成可追溯的设计风量。建议核查计算公式、取值依据、风机风量裕量和治理设施处理风量是否匹配。</x:v>
       </x:c>
       <x:c r="G89" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...厂界环境噪声排放标准》（GB 12348-2008）3类标准4、固废项目在营运过程中产生的固体废物主要有两大类，一类为危险废物，主要包括废机油、废抹布、废油桶、废活性炭和废包装桶；另一类为一般废物，主要包括生活垃圾、废包装袋、边角料、次品和泥垢。本项目生活垃圾、一般工业固体废物以及危险废物的源强核实详见下表4-24所示，固体废物相关参数详见表4-25所示。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...数一览表详见表4-1所示：表4-1 废气污染源源强核算结果及相关参数一览表工序/生产线污染源污染物污染物产生治理措施污染物排放排放时间/h核算方法废气产生量/（m3/h）收集效率%产生浓度/（mg/m3）产生速率/（kg/h）产生量/（t/a）工艺效率%核算方法废气排放量/（m3/h）排放浓度/（mg/m3）排放速率/（kg/h）排放量/（t/a）吹膜、涂布、烘干DA001非甲烷总烃系数核算法80005015.750.1260.302二级活性炭吸附装置51系数核算法80007.750.0620.1482400臭气浓度//2000（无量纲）//2000（无量纲）涂布、烘干总VOCs0.36...</x:v>
       </x:c>
       <x:c r="H89" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集风量与设计风量核算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I89" s="7" t="b">
         <x:v>1</x:v>
@@ -3145,7 +3145,7 @@
       <x:c r="J89" s="11" t="str"/>
       <x:c r="K89" s="11" t="str"/>
     </x:row>
-    <x:row r="90" ht="82.5" customHeight="1">
+    <x:row r="90" ht="88.5" customHeight="1">
       <x:c r="A90" s="6" t="str">
         <x:v>P009_Q09</x:v>
       </x:c>
@@ -3156,19 +3156,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D90" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>废水排放及生活污水基本情况</x:v>
       </x:c>
       <x:c r="E90" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的生活污水、生产废水、冷却水去向和基本情况表，判断废水排放内容是否准确、一致。</x:v>
       </x:c>
       <x:c r="F90" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查废水类别和去向一致性。报告应明确生活污水、生产废水、冷却水或喷淋废水的产生、处理、回用和排放路径。建议核查正文、基本情况表、排放标准和纳污去向是否一致。</x:v>
       </x:c>
       <x:c r="G90" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...周外1米外等效连续A声级1次/季《工业企业厂界环境噪声排放标准》（GB 12348-2008）3类标准4、固废项目在营运过程中产生的固体废物主要有两大类，一类为危险废物，主要包括废机油、废抹布、废油桶、废活性炭和废包装桶；另一类为一般废物，主要包括生活垃圾、废包装袋、边角料、次品和泥垢。本项目生活垃圾、一般工业固体废物以及危险废物的源强核实详见下表4-24所示，固体废物相关参数详见表4-25所示。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | 2.3冷却用水项目吹膜机配有2台5t/h冷却塔，冷却塔冷却系统下方有一个0.5m2的沉淀池。项目冷却系统冷却水是为了保证原材料处于工艺要求的温度范围，冷却方式为间接冷却，冷却用水均为普通的自来水，无需添加矿物油、乳化液等冷却剂。间接冷却用水不直接接触塑胶料，对水质、盐度、硬度等要求均不高，故冷却用水可循环使用，但由于蒸发导致水中盐度、硬度变高，需要定期补充损耗水以及定期排放冷却浓水。由于蒸发等原因会有少量的损耗需定期补充新鲜水，冷却系统进水温度约为30℃，出水温度为25℃，温差为5℃。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H90" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：地表水与废水执行标准；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I90" s="7" t="b">
         <x:v>1</x:v>
@@ -3176,7 +3176,7 @@
       <x:c r="J90" s="11" t="str"/>
       <x:c r="K90" s="11" t="str"/>
     </x:row>
-    <x:row r="91" ht="82.5" customHeight="1">
+    <x:row r="91" ht="88.5" customHeight="1">
       <x:c r="A91" s="6" t="str">
         <x:v>P009_Q10</x:v>
       </x:c>
@@ -3187,19 +3187,19 @@
         <x:v>佛山市顺德区康明新材料厂新建项目</x:v>
       </x:c>
       <x:c r="D91" s="6" t="str">
-        <x:v>总量控制</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E91" s="6" t="str">
-        <x:v>请根据报告中的VOCs总量控制指标和替代来源，判断总量控制论证是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F91" s="6" t="str">
-        <x:v>判断：需核查总量控制指标和替代来源。依据：报告涉及VOCs总量、替代来源或总量指标。审核意见：建议检查总量核算是否与源强排放量一致，替代来源或削减来源是否有明确证据。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G91" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...用状况，尽量采用密闭形式，少开门窗，防止噪声对外传播，其中靠厂界的厂房其一侧墙壁应避免打开门窗；厂房内使用隔声材料进行降噪，并在其表面铺覆一层吸声材料，可进一步削减噪声强度。③加强管理建立设备定期维护、保养的管理制度，以防止设备故障形成的非生产噪声，同时确保环保措施发挥最有效的功能；加强职工环保意识教育，提倡文明生产，防止人为噪声；对于厂区内流动声源（汽车），应强化行车管理制度，严禁鸣号，进入厂区低速行驶，最大限度减少流动噪声源。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...评价分类管理名录》（2021年版）项目主要从事塑料薄膜的加工生产，本项目设有混料、吹膜、涂布、烘干、分切、复卷、检验。本项目使用的保护胶涂布胶属于低VOCs含量胶水，故应编制报告表。二十六、橡胶和塑料制品业2953塑料制品业292报告书报告表登记表以再生塑料为原料生产的；有电镀工艺的；年用溶剂型胶粘剂10吨及以上的；年用溶剂型涂料（含稀释剂）10吨及以上的其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）/《固定污染源排污许可分类管理名录（2019年版）》本项目主要从事塑料薄膜的加工生产，项目行业类别为2921塑料薄膜制造，年产量少于1万吨，故本项目应进行登记管理。...</x:v>
       </x:c>
       <x:c r="H91" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；地方政策库；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I91" s="7" t="b">
         <x:v>1</x:v>
@@ -3207,7 +3207,7 @@
       <x:c r="J91" s="11" t="str"/>
       <x:c r="K91" s="11" t="str"/>
     </x:row>
-    <x:row r="92" ht="82.5" customHeight="1">
+    <x:row r="92" ht="88.5" customHeight="1">
       <x:c r="A92" s="6" t="str">
         <x:v>P010_Q01</x:v>
       </x:c>
@@ -3215,22 +3215,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C92" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D92" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E92" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F92" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：涂料、胶粘剂、清洗剂才需要分析是否为低VOCs”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G92" s="6" t="str">
-        <x:v>Word批注/修改意见（第2条）写明：雷兆宇：涂料、胶粘剂、清洗剂才需要分析是否为低VOCs</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...地点 | 佛山市顺德区杏坛镇齐杏社区杏坛工业区科技五路1号华康楼11栋204；地理坐标 | （东经113度10分50.451秒，北纬22度47分2.508秒）；国民经济行业类别 | C2929 塑料零件及其他塑料制品制造 | 建设项目行业类别 | 二十六、橡胶和塑料制品业29、53塑料制品业-292、其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）改建扩建技术改造 | 建设项目申报情形 | 首次申报项目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H92" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I92" s="7" t="b">
         <x:v>1</x:v>
@@ -3238,7 +3238,7 @@
       <x:c r="J92" s="11" t="str"/>
       <x:c r="K92" s="11" t="str"/>
     </x:row>
-    <x:row r="93" ht="82.5" customHeight="1">
+    <x:row r="93" ht="88.5" customHeight="1">
       <x:c r="A93" s="6" t="str">
         <x:v>P010_Q02</x:v>
       </x:c>
@@ -3246,22 +3246,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C93" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D93" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E93" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集效率与处理效率相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F93" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：提高收集效率，附近有敏感点，改性塑料粒恶臭较为严重，请更改。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G93" s="6" t="str">
-        <x:v>Word批注/修改意见（第15条）写明：雷兆宇：提高收集效率，附近有敏感点，改性塑料粒恶臭较为严重，请更改。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；项目审批（核准/备案）部门（选填） | / | 项目审批（核准/备案）文号（选填） | /；总投资（万元） | 100 | 环保投资（万元） | 10；环保投资占比（%） | 10 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H93" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I93" s="7" t="b">
         <x:v>1</x:v>
@@ -3269,7 +3269,7 @@
       <x:c r="J93" s="11" t="str"/>
       <x:c r="K93" s="11" t="str"/>
     </x:row>
-    <x:row r="94" ht="82.5" customHeight="1">
+    <x:row r="94" ht="88.5" customHeight="1">
       <x:c r="A94" s="6" t="str">
         <x:v>P010_Q03</x:v>
       </x:c>
@@ -3277,22 +3277,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C94" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D94" s="6" t="str">
-        <x:v>废水去向与冷却水</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E94" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废水去向与冷却水相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F94" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：明确是否为间接冷却水”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G94" s="6" t="str">
-        <x:v>Word批注/修改意见（第6条）写明：雷兆宇：明确是否为间接冷却水</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 项目由来恒励新材料科技 (佛山) 有限公司选址于佛山市顺德区杏坛镇齐杏社区杏坛工业区科技五路1号华康楼11栋204，占地面积为931.68m2，中心地理坐标为东经113度10分50.451秒，北纬22度47分2.508秒，建筑面积为931.68m2，主要从事改性SEBS塑料的生产，预计投产后年产改性SEBS塑料720吨。根据《建设项目环境影响评价分类管理名录（2021年版）》，本次项目属于“二十六、橡胶和塑料制品业29、53塑料制品业-292、其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）”类...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H94" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I94" s="7" t="b">
         <x:v>1</x:v>
@@ -3300,7 +3300,7 @@
       <x:c r="J94" s="11" t="str"/>
       <x:c r="K94" s="11" t="str"/>
     </x:row>
-    <x:row r="95" ht="82.5" customHeight="1">
+    <x:row r="95" ht="88.5" customHeight="1">
       <x:c r="A95" s="6" t="str">
         <x:v>P010_Q04</x:v>
       </x:c>
@@ -3308,22 +3308,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C95" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D95" s="6" t="str">
-        <x:v>排放标准适用</x:v>
+        <x:v>污染物排放标准适用性</x:v>
       </x:c>
       <x:c r="E95" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断排放标准适用相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据项目行业类别、生产工艺、污染因子和排放形式，判断废气、废水、噪声和固废相关排放标准选取是否合理。</x:v>
       </x:c>
       <x:c r="F95" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：根据sebs特性结合合成树脂排放标准综合分析是否还有其它特征污染物。挤出温度是多少，是否会存在分解的情况。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查排放标准适用性。报告应结合行业类别、生产工艺、污染因子、有组织和无组织排放形式选取标准。建议核查是否遗漏厂区内VOCs无组织限值、厂界限值、排气筒排放限值或噪声、废水相关标准。</x:v>
       </x:c>
       <x:c r="G95" s="6" t="str">
-        <x:v>Word批注/修改意见（第14条）写明：雷兆宇：根据sebs特性结合合成树脂排放标准综合分析是否还有其它特征污染物。挤出温度是多少，是否会存在分解的情况。</x:v>
+        <x:v>五、环境保护措施监督检查清单（表格）写明：内容要素 | 排放口(编号、名称)/污染源 | 污染物项目 | 环境保护措施 | 执行标准；大气环境 | 排气筒（G1） | 非甲烷总烃 | 挤出过程产生的非甲烷总烃使用包围型集气罩（通过软质垂帘四周围挡，偶有部分敞开）收集后经“二级活性炭吸附装置”后引至55m排气筒(G1)高空排放 | 《合成树脂工业污染物排放标准》（GB31572-2015）表4大气污染物排放限值；臭气浓度 | 《恶臭污染物排放标准》（GB14554-93）中表2中15m高排气筒排放标准值；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H95" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#8_塑料制品业典型污染源及执行标准、GB_31572-2015、GB_37822-2019、DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I95" s="7" t="b">
         <x:v>1</x:v>
@@ -3331,7 +3331,7 @@
       <x:c r="J95" s="11" t="str"/>
       <x:c r="K95" s="11" t="str"/>
     </x:row>
-    <x:row r="96" ht="82.5" customHeight="1">
+    <x:row r="96" ht="88.5" customHeight="1">
       <x:c r="A96" s="6" t="str">
         <x:v>P010_Q05</x:v>
       </x:c>
@@ -3339,22 +3339,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C96" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D96" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E96" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F96" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：上文补充废气治理设施的可行性分析，明确碘值。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G96" s="6" t="str">
-        <x:v>Word批注/修改意见（第19条）写明：雷兆宇：上文补充废气治理设施的可行性分析，明确碘值。</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...系统在车间内无组织排放，预计投料混色工序产生的粉尘无组织排放厂界监控浓度限值≤1.0mg/m3，对周围环境影响不大。②挤出废气项目挤出工序期间会产生有机废气，以非甲烷总烃表征。挤出过程非甲烷总烃产生系数参考《广东省塑料制品与制造业、人造石制造业、电子元件制造业挥发性有机化合物排放系数使用指南》（广东省生态环境厅，2022年6月）表4-1塑料制品与制造业成型工序VOCs排放系数，收集效率和处理效率均为0%时的排放系数2.368kg/t-塑料原料。本项目SEBS、增粘树脂总使用量为720t/a，则挤出工序非甲烷总烃产生量为1.705t/a；...</x:v>
       </x:c>
       <x:c r="H96" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I96" s="7" t="b">
         <x:v>1</x:v>
@@ -3362,7 +3362,7 @@
       <x:c r="J96" s="11" t="str"/>
       <x:c r="K96" s="11" t="str"/>
     </x:row>
-    <x:row r="97" ht="82.5" customHeight="1">
+    <x:row r="97" ht="88.5" customHeight="1">
       <x:c r="A97" s="6" t="str">
         <x:v>P010_Q06</x:v>
       </x:c>
@@ -3370,22 +3370,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C97" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D97" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E97" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F97" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：氧化气氛，”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G97" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：氧化气氛，</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。挤出工序废气经包围型集气罩（通过软质垂帘四周围挡，偶有部分敞开）收集后通过二级活性炭吸附废气处理设施进行处理，处理达标后通过排气筒G1（55m）引至楼顶排放。符合3.佛山市生态环境局关于印发《佛山市重点行业VOCs治理提升工作方案》的通知（环大气〔2019〕53 号）3.12021年底前淘汰光氧化、光催化、低温等离子等低效治理设施。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H97" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I97" s="7" t="b">
         <x:v>1</x:v>
@@ -3393,7 +3393,7 @@
       <x:c r="J97" s="11" t="str"/>
       <x:c r="K97" s="11" t="str"/>
     </x:row>
-    <x:row r="98" ht="82.5" customHeight="1">
+    <x:row r="98" ht="88.5" customHeight="1">
       <x:c r="A98" s="6" t="str">
         <x:v>P010_Q07</x:v>
       </x:c>
@@ -3401,22 +3401,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C98" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D98" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E98" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F98" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G98" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...系统在车间内无组织排放，预计投料混色工序产生的粉尘无组织排放厂界监控浓度限值≤1.0mg/m3，对周围环境影响不大。②挤出废气项目挤出工序期间会产生有机废气，以非甲烷总烃表征。挤出过程非甲烷总烃产生系数参考《广东省塑料制品与制造业、人造石制造业、电子元件制造业挥发性有机化合物排放系数使用指南》（广东省生态环境厅，2022年6月）表4-1塑料制品与制造业成型工序VOCs排放系数，收集效率和处理效率均为0%时的排放系数2.368kg/t-塑料原料。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...项目所在区域大气环境属于不达标区，不达标因子为臭氧。本项目排放不涉及臭氧，生产过程产生的有机废气经包围型集气罩（通过软质垂帘四周围挡，偶有部分敞开）收集后通过“二级活性炭吸附装置”处理后通过55m排气筒G1排放，对周边环境影响较小；生活污水经三级化粪池预处理达标后排入杏坛污水处理厂，对周围环境影响较小，本项目排放的污染物不会导致区域环境质量超标，符合环境质量底线要求。③资源利用上线强化节约集约利用，持续提升资源能源利用效率，水资源、土地资源、岸线资源、能源消耗等达到或优于国家下达的总量和强度符合控制目标。本项目不属于高耗能、污染资源型企业，用水来自市政管网，用电来自市政供电。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H98" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I98" s="7" t="b">
         <x:v>1</x:v>
@@ -3424,7 +3424,7 @@
       <x:c r="J98" s="11" t="str"/>
       <x:c r="K98" s="11" t="str"/>
     </x:row>
-    <x:row r="99" ht="82.5" customHeight="1">
+    <x:row r="99" ht="88.5" customHeight="1">
       <x:c r="A99" s="6" t="str">
         <x:v>P010_Q08</x:v>
       </x:c>
@@ -3432,22 +3432,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C99" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D99" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>废水排放及生活污水基本情况</x:v>
       </x:c>
       <x:c r="E99" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的生活污水、生产废水、冷却水去向和基本情况表，判断废水排放内容是否准确、一致。</x:v>
       </x:c>
       <x:c r="F99" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查废水类别和去向一致性。报告应明确生活污水、生产废水、冷却水或喷淋废水的产生、处理、回用和排放路径。建议核查正文、基本情况表、排放标准和纳污去向是否一致。</x:v>
       </x:c>
       <x:c r="G99" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...顺德区发布的有机污染物治理政策的相符性分析见表1-4。表1-4 项目与有机污染物治理政策的相符性分析序号政策本项目情况相符性1.《珠江三角洲地区严格控制工业企业挥发性有机物（VOCs）排放的意见》（粤环[2012]18号）1.1在自然保护区、水源保护区、风景名胜区、森林公园、重要湿地、生态敏感区和其他重生态功能区实行强制性保护，禁止新建VOCs污染企业。本项目选址不在禁止区域。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：◇生活污水项目工作定员为5人，年工作300天，厂内不设置员工宿舍和饭堂，生活用水量参照广东省地方标准《用水定额 第3部分：生活》（DB44/T1461.3-2021），国家行政机构办公楼（无食堂和浴室）中的先进值计算，即10m3/人·a，则员工生活用水量为50m3/a。参考《社会区域类环境影响评价》环境影响评价工程师职业资格登记培训教材，城市生活污水排水系数0.85~0.95，污水排放量按用水量的90%算，则生活污水排放量约45m3/a，这部分污水主要含CODcr、BOD5、SS、NH3-N等污染物。生活废水经三级化...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H99" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：地表水与废水执行标准；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I99" s="7" t="b">
         <x:v>1</x:v>
@@ -3455,7 +3455,7 @@
       <x:c r="J99" s="11" t="str"/>
       <x:c r="K99" s="11" t="str"/>
     </x:row>
-    <x:row r="100" ht="82.5" customHeight="1">
+    <x:row r="100" ht="88.5" customHeight="1">
       <x:c r="A100" s="6" t="str">
         <x:v>P010_Q09</x:v>
       </x:c>
@@ -3463,22 +3463,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C100" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D100" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E100" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F100" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G100" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：①投料混料粉尘项目投料混料过程时在密闭式混料机中进行，在设备开盖时会产生少量粉尘，其主要污染因子为颗粒物，其产生的粉尘通过通风系统在车间内无组织排放，预计投料混色工序产生的粉尘无组织排放厂界监控浓度限值≤1.0mg/m3，对周围环境影响不大。②挤出废气项目挤出工序期间会产生有机废气，以非甲烷总烃表征。挤出过程非甲烷总烃产生系数参考《广东省塑料制品与制造业、人造石制造业、电子元件制造业挥发性有机化合物排放系数使用指南》（广东省生态环境厅，2022年6月）表4-1塑料制品与...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...次，暂存间贮存能力可满足危险废物的存储需求。表4-21 项目危险废物贮存场所（设施）基本情况序号贮存场所名称类别代码位置占地面积（m2）贮存方式能力（t）周期1危废暂存间废机油HW08废矿物油与含矿物油废物900-214-08生产车间东南侧10桶装101年2废活性炭HW49类其他废物900-039-49防渗袋1个月3废油包装桶HW08 废矿物油与含矿物油废物900-249-08桶装1年4含油废抹布HW49类其他废物900-041-49防渗袋1年建设单位拟将危险废物交有危废处置资质单位处理。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H100" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I100" s="7" t="b">
         <x:v>1</x:v>
@@ -3486,7 +3486,7 @@
       <x:c r="J100" s="11" t="str"/>
       <x:c r="K100" s="11" t="str"/>
     </x:row>
-    <x:row r="101" ht="82.5" customHeight="1">
+    <x:row r="101" ht="88.5" customHeight="1">
       <x:c r="A101" s="6" t="str">
         <x:v>P010_Q10</x:v>
       </x:c>
@@ -3494,22 +3494,22 @@
         <x:v>恒励新材料科技（佛山）有限公司新建项目-修改意见.docx</x:v>
       </x:c>
       <x:c r="C101" s="6" t="str">
-        <x:v>| 恒励新材料科技(佛山)有限公司新建项目</x:v>
+        <x:v>恒励新材料科技(佛山)有限公司新建项目</x:v>
       </x:c>
       <x:c r="D101" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>图件、附件、敏感点识别完整性</x:v>
       </x:c>
       <x:c r="E101" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的项目位置、厂界范围、敏感目标识别和附图附件，判断敏感点识别及图件附件是否完整。</x:v>
       </x:c>
       <x:c r="F101" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查敏感点和图件附件完整性。报告应明确项目位置、厂界范围、四至关系、环境保护目标和相关附图附件。建议核查敏感目标识别范围是否充分，附图、附件是否能支撑位置、管控单元和保护目标判断。</x:v>
       </x:c>
       <x:c r="G101" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...址不在禁止区域。符合2.《挥发性有机物（VOCs）污染防治技术政策》（环保部公告2013第31号）2.1含VOCs产品的使用过程中，应采取废气收集措施，提高废气收集效率，减少废气的无组织排放与逸散。挤出工序废气经包围型集气罩（通过软质垂帘四周围挡，偶有部分敞开）收集后通过二级活性炭吸附废气处理设施进行处理，处理达标后通过排气筒G1（55m）引至楼顶排放。...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...非甲烷总烃、臭气浓度，不属于新增排放重点防控重金属污染物(铅(Pb)、汞(Hg)、镉(Cd)、铬(Cr)和类金属砷(As))、持久性有机污染物的项目。符合 3、饮用水源准保护区内不得新建、扩建对水体污染严重、排放一类水污染物和持久性有机污染物的项目，改扩建项目不得新增水污染物。 项目不在饮用水源准保护区内。符合 4、禁止引入达不到清洁生产国际先进水平的企业。 本项目不涉及。符合 5、在污水管网建设滞后或所依托的污水处理厂处理能力不能满足废水处理需求的区域，不应引入废水排放量较大的项目。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H101" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；报告表编制要求；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I101" s="7" t="b">
         <x:v>1</x:v>
@@ -3517,7 +3517,7 @@
       <x:c r="J101" s="11" t="str"/>
       <x:c r="K101" s="11" t="str"/>
     </x:row>
-    <x:row r="102" ht="82.5" customHeight="1">
+    <x:row r="102" ht="88.5" customHeight="1">
       <x:c r="A102" s="6" t="str">
         <x:v>P011_Q01</x:v>
       </x:c>
@@ -3525,22 +3525,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C102" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D102" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E102" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F102" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：排放量的由来，该数据如何获得，需要提供实际生产的废水排放量，建议根据药剂使用量倒推废水产生量。或者监测数据。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G102" s="6" t="str">
-        <x:v>Word批注/修改意见（第9条）写明：雷兆宇：排放量的由来，该数据如何获得，需要提供实际生产的废水排放量，建议根据药剂使用量倒推废水产生量。或者监测数据。</x:v>
+        <x:v>建设项目工程分析（表格）写明：...限公司功能拉篮车间搬迁扩建项目”（下称“本项目”）。搬迁扩建后，本项目年产功能拉篮由100万个/年增加至132万个/年，并新增“除油、陶化、喷粉、固化、贴膜”等生产工艺。本项目拟租用已建设完成的厂房进行生产建设，项目占地面积7746.48m2，建筑面积15492.96m2。本项目所在建筑共7层，一层高度约7.9m，其余楼层约5.9m。工程具体内容按主体工程、公用工程、辅助工程、环保工程等内容细化见下表。...</x:v>
       </x:c>
       <x:c r="H102" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I102" s="7" t="b">
         <x:v>1</x:v>
@@ -3548,7 +3548,7 @@
       <x:c r="J102" s="11" t="str"/>
       <x:c r="K102" s="11" t="str"/>
     </x:row>
-    <x:row r="103" ht="82.5" customHeight="1">
+    <x:row r="103" ht="88.5" customHeight="1">
       <x:c r="A103" s="6" t="str">
         <x:v>P011_Q02</x:v>
       </x:c>
@@ -3556,22 +3556,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C103" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D103" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E103" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F103" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：是否为无溶剂涂料，执行60”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G103" s="6" t="str">
-        <x:v>Word批注/修改意见（第2条）写明：雷兆宇：是否为无溶剂涂料，执行60</x:v>
+        <x:v>建设项目工程分析（表格）写明：建设内容 | 1.项目内容佛山市顺德区悍高五金制品有限公司新建项目（以下简称“原项目”），建设于顺德区西部生态产业区启动区D-06-4地块和D-06-3地块（现地址为佛山市顺德区杏坛镇顺业东路36号之一），中心地理坐标：北纬22.750567°，东经113.210208°），主要从事金属家具用品、厨具等制造，项目租赁广东俊嘉汽车配件实业有限公司厂房和佛山市顺德区伟高展示科技有限公司已建成厂房进行生产，租赁厂房占地面积约15654.79m2，租赁厂房建筑面积为77789.21m2，主要建筑物2栋4层的厂房、1栋6层生...</x:v>
       </x:c>
       <x:c r="H103" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I103" s="7" t="b">
         <x:v>1</x:v>
@@ -3579,7 +3579,7 @@
       <x:c r="J103" s="11" t="str"/>
       <x:c r="K103" s="11" t="str"/>
     </x:row>
-    <x:row r="104" ht="82.5" customHeight="1">
+    <x:row r="104" ht="88.5" customHeight="1">
       <x:c r="A104" s="6" t="str">
         <x:v>P011_Q03</x:v>
       </x:c>
@@ -3587,22 +3587,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C104" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D104" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E104" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F104" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：请描述集气罩的样子”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G104" s="6" t="str">
-        <x:v>Word批注/修改意见（第21条）写明：雷兆宇：请描述集气罩的样子</x:v>
+        <x:v>区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1.环境空气质量现状根据《佛山市人民政府办公室关于调整顺德区环境空气质量功能区划的复函》（佛府办函[2014]494号，2014年8月）和《顺德区生态环境规划（2011~2020年）》，顺德区全境为大气环境二类区，因此本项目所在区域属二类环境空气质量功能区，执行《环境空气质量标准》（GB3095-2012）及2018年修改单二级标准。为评价本次环评的环境空气质量现状，引用《佛山市生态环境局顺德分局关于发布2022年度佛山市顺德区环境质量状况公报的通知》（佛环顺函〔2023〕26号）中的数据和结论如...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H104" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I104" s="7" t="b">
         <x:v>1</x:v>
@@ -3610,7 +3610,7 @@
       <x:c r="J104" s="11" t="str"/>
       <x:c r="K104" s="11" t="str"/>
     </x:row>
-    <x:row r="105" ht="82.5" customHeight="1">
+    <x:row r="105" ht="88.5" customHeight="1">
       <x:c r="A105" s="6" t="str">
         <x:v>P011_Q04</x:v>
       </x:c>
@@ -3618,22 +3618,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C105" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D105" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>污染物排放标准适用性</x:v>
       </x:c>
       <x:c r="E105" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集效率与处理效率相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据项目行业类别、生产工艺、污染因子和排放形式，判断废气、废水、噪声和固废相关排放标准选取是否合理。</x:v>
       </x:c>
       <x:c r="F105" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：处理效率太高，导致BOD浓度过低，不符合入污水处理厂的要求”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查排放标准适用性。报告应结合行业类别、生产工艺、污染因子、有组织和无组织排放形式选取标准。建议核查是否遗漏厂区内VOCs无组织限值、厂界限值、排气筒排放限值或噪声、废水相关标准。</x:v>
       </x:c>
       <x:c r="G105" s="6" t="str">
-        <x:v>Word批注/修改意见（第18条）写明：雷兆宇：处理效率太高，导致BOD浓度过低，不符合入污水处理厂的要求</x:v>
+        <x:v>环境保护措施监督清单（表格）写明：内容要素 | 排放口(编号、名称)/污染源 | 污染物项目 | 环境保护措施 | 执行标准；大气环境 | DA001排气筒 | 喷粉 | 颗粒物 | 喷粉颗粒物整室收集、抛光打磨颗粒物经集气罩一并收集后，通过旋风除尘+滤筒除尘装置处理，引至50m高排气筒（DA001）排放。 | 广东省地方标准《大气污染物排放限值》（DB44/27-2001）第二时段二级标准；抛光打磨 | 颗粒物；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H105" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#8_塑料制品业典型污染源及执行标准、GB_31572-2015、GB_37822-2019、DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I105" s="7" t="b">
         <x:v>1</x:v>
@@ -3641,7 +3641,7 @@
       <x:c r="J105" s="11" t="str"/>
       <x:c r="K105" s="11" t="str"/>
     </x:row>
-    <x:row r="106" ht="82.5" customHeight="1">
+    <x:row r="106" ht="88.5" customHeight="1">
       <x:c r="A106" s="6" t="str">
         <x:v>P011_Q05</x:v>
       </x:c>
@@ -3649,22 +3649,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C106" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D106" s="6" t="str">
-        <x:v>废水去向与冷却水</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E106" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废水去向与冷却水相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F106" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：请对该废水进行可行性分析，分别分析每一工艺对某种污染物的去除率，计算最终是否可以达到排放标准。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G106" s="6" t="str">
-        <x:v>Word批注/修改意见（第16条）写明：雷兆宇：请对该废水进行可行性分析，分别分析每一工艺对某种污染物的去除率，计算最终是否可以达到排放标准。</x:v>
+        <x:v>区域环境质量现状、环境保护目标及评价标准（表格）写明：...建厂房，因此，项目没有土建施工工程，主要是设备的安装与调试，施工期较短，故对周围环境造成的影响较小。；运营期环境影响和保护措施 | 1.废水污染源1.1生活污水核算本项目有175名工作人员，不设饭堂和宿舍，生活用水系数采用《用水定额 第3部分：生活》（DB44/T 1461.3-2021）“国家行政机构办公楼，无食堂和浴室”的先进值为10m3/人·年，年工作300d，则生活用水量1750t/a。污水排放量按用水量的90%算，则生活污水排放量约1575t/a，这部分污水主要含COD、BOD5、SS、NH3-N等污染物，生活污水污染物浓度采用顺德地区的生活污水源强调查数据。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H106" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I106" s="7" t="b">
         <x:v>1</x:v>
@@ -3672,7 +3672,7 @@
       <x:c r="J106" s="11" t="str"/>
       <x:c r="K106" s="11" t="str"/>
     </x:row>
-    <x:row r="107" ht="82.5" customHeight="1">
+    <x:row r="107" ht="88.5" customHeight="1">
       <x:c r="A107" s="6" t="str">
         <x:v>P011_Q06</x:v>
       </x:c>
@@ -3680,22 +3680,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C107" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D107" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E107" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F107" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：更换周期如何确定，请写出依据。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G107" s="6" t="str">
-        <x:v>Word批注/修改意见（第7条）写明：雷兆宇：更换周期如何确定，请写出依据。</x:v>
+        <x:v>建设项目工程分析（表格）写明：...污水处理站处理后排入杏坛污水处理厂。供气系统/供气系统通过天然气管道引入厂区通入车间。环保工程废气处理焊接焊材、打磨抛光粉尘收集后经布袋除尘器处理达标后经30m排气筒高空排放。喷粉废气喷粉废气经整室收集，抛光打磨废气经集气罩收集，两股废气一并进入“旋风除尘+滤筒除尘装置”处理达标后经50m排气筒（DA001）高空排放烘干燃烧废气烘干燃烧废气、固化废气分别经集气罩收集，脱附废气经固定排放管收集后一并进入“水喷淋降温＋干式过滤+二级活性炭吸附装置”处理达标后经50m排气筒（DA002）高空排放。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H107" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I107" s="7" t="b">
         <x:v>1</x:v>
@@ -3703,7 +3703,7 @@
       <x:c r="J107" s="11" t="str"/>
       <x:c r="K107" s="11" t="str"/>
     </x:row>
-    <x:row r="108" ht="82.5" customHeight="1">
+    <x:row r="108" ht="88.5" customHeight="1">
       <x:c r="A108" s="6" t="str">
         <x:v>P011_Q07</x:v>
       </x:c>
@@ -3711,22 +3711,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C108" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D108" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E108" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F108" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：可走保密审查，但不可以不列明有害物质成分。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G108" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：可走保密审查，但不可以不列明有害物质成分。</x:v>
+        <x:v>表4- SEQ 表4- \* ARABIC 26 废气污染物排放情况一览表（表格）写明：... 生产单元 | 污染物种类 | 污染物产生情况 | 排放形式 | 治理措施 | 污染物排放情况；产生量t/a | 产生浓度mg/m3 | 处理能力m3/h | 收集效率 | 处理工艺 | 去除率 | 是否可行性技术 | 排放浓度mg/m3 | 排放速率kg/h | 排放量t/a | 排放时间；开料、冲压、机械加工 | 冲床、车床、攻牙机等 | 颗粒物 | 10.577 | / | 无组织 | / | / | / | / | / | / | 0.106 | 0.254 | 2400h/a；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H108" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I108" s="7" t="b">
         <x:v>1</x:v>
@@ -3734,7 +3734,7 @@
       <x:c r="J108" s="11" t="str"/>
       <x:c r="K108" s="11" t="str"/>
     </x:row>
-    <x:row r="109" ht="82.5" customHeight="1">
+    <x:row r="109" ht="88.5" customHeight="1">
       <x:c r="A109" s="6" t="str">
         <x:v>P011_Q08</x:v>
       </x:c>
@@ -3742,22 +3742,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C109" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D109" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>废活性炭产生量、填充量和更换量</x:v>
       </x:c>
       <x:c r="E109" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的活性炭填充量、更换频次、VOCs吸附量和危废清单，判断废活性炭产生量核算是否前后一致。</x:v>
       </x:c>
       <x:c r="F109" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查废活性炭核算闭合性。报告应使活性炭填充量、更换频次、VOCs吸附量、废活性炭产生量和危废清单相互一致。建议核查更换周期是否偏长、吸附容量取值是否有依据、危废产生量是否覆盖吸附污染物和更换量。</x:v>
       </x:c>
       <x:c r="G109" s="6" t="str">
-        <x:v>表1- SEQ 表1- \* ARABIC 10 本项目与《佛山市生态环境局 佛山市水利局关于进一步加强工业企业废水污染防治的函》相符性分析（表格）写明：...“三线一单”管控要求应当入园集聚的建设项目违反准入要求在园区外围落地建设。加强废水排放指标管理，对于园区生产废水纳入集中处理的，应结合园区入驻企业建设进展和废水排放量实际，优化园区废水排放指标管理，最大限度发挥排水指标经济效益。（市生态环境局各分局负责）。 | 本项目位于广东省佛山市顺德区杏坛镇光华村，属于佛山市顺德区智慧家居园区范围内，本次环评对照《佛山市顺德区人民政府关于印发佛山市顺德区“三线一单”生态环境分区管控方案的通知》（顺府发[2021]11号）等文件相符性分析；目前，园区未配套集中处理设施。...</x:v>
+        <x:v>区域环境质量现状、环境保护目标及评价标准（表格）写明：...的公司回收处理。除油、清洗和陶化废水产排情况如下。表4- SEQ 表4- \* ARABIC 2 除油、清洗、陶化水量核算表池体名称有效容积m3用水类型清洗方式更换频次单次更换量m3年更换量m3/a溢流速度m3/h溢流水量m3/a废水产生量小计m3/a除油池12.5脱脂剂喷淋25d2.530//30除油池27.5脱脂剂喷淋25d7.590//90清洗池12逆流水喷淋25d224496009624清洗池22逆流水喷淋25d2244/24清洗池32逆流水喷淋25d2244/24清洗池42新鲜水喷淋25d2244/24陶化池8陶化剂喷淋25d896//96清洗池52逆流水喷淋25d224496...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H109" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I109" s="7" t="b">
         <x:v>1</x:v>
@@ -3765,7 +3765,7 @@
       <x:c r="J109" s="11" t="str"/>
       <x:c r="K109" s="11" t="str"/>
     </x:row>
-    <x:row r="110" ht="82.5" customHeight="1">
+    <x:row r="110" ht="88.5" customHeight="1">
       <x:c r="A110" s="6" t="str">
         <x:v>P011_Q09</x:v>
       </x:c>
@@ -3773,22 +3773,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C110" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D110" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E110" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F110" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G110" s="6" t="str">
-        <x:v>表1- SEQ 表1- \* ARABIC 9 本项目与所在的陆域环境管控单元相符性分析（表格）写明：...”规划（2021-2025）》的通知》相符性分析《佛山市顺德区生态环境保护“十四五”规划（2021-2025）》提出：1）持续推进重点行业VOCs整治。持续开展挥发性有机物专项整治，继续推进重点行业企业开展销号式综合整治，建立VOC重点监管企业名单并动态更新，督促企业建立VOCs管控台账清单；持续探寻高效节能的VOCs治理技术，对采用低温等离子、光氧化、光催化等低效治理工艺的企业在臭氧污染天气应对期间实施停限产或错峰生产，并推动企业逐步淘汰低效治理工艺。2）加强VOCs源头替代和无组织排放管控。...</x:v>
+        <x:v>表1- SEQ 表1- \* ARABIC 9 本项目与所在的陆域环境管控单元相符性分析（表格）写明：...低 VOCs含量原辅材料的企业纳入正面清单和政府绿色采购清单。鼓励重点行业企业开展生产工艺和设备水性化改造，推广使用水性、高固体分、无溶剂、粉末等低VOCs含量涂料。严格落实《挥发性有机物无组织排放控制标准》，开展厂区内无组织排放浓度监测，加强对含VOCs物料储存、转移和运输、设备与管线组件泄漏、敞开页面逸散以及工艺过程等五类排放源的管控。相符性分析：1）本项目不使用溶剂型油墨、涂料、清洗剂、胶黏剂等高挥发性有机物原辅材料。项目使用的粉末涂料为低挥发性有机物涂料。项目有机废气经活性炭吸附处理，不使用低温等离子、光氧化、光催化等低效治理工艺。2）项目有机废气经收集处理后可达标排放。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H110" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I110" s="7" t="b">
         <x:v>1</x:v>
@@ -3796,7 +3796,7 @@
       <x:c r="J110" s="11" t="str"/>
       <x:c r="K110" s="11" t="str"/>
     </x:row>
-    <x:row r="111" ht="82.5" customHeight="1">
+    <x:row r="111" ht="88.5" customHeight="1">
       <x:c r="A111" s="6" t="str">
         <x:v>P011_Q10</x:v>
       </x:c>
@@ -3804,22 +3804,22 @@
         <x:v>2023101914551665922.悍高集团股份有限公司功能拉篮车间搬迁扩建项目（修改意见).docx</x:v>
       </x:c>
       <x:c r="C111" s="6" t="str">
-        <x:v>| 悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
+        <x:v>悍高集团股份有限公司功能拉篮车间搬迁扩建项目</x:v>
       </x:c>
       <x:c r="D111" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>附表、总量、正文前后一致性</x:v>
       </x:c>
       <x:c r="E111" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告正文、污染物排放汇总表、总量控制指标和监督检查清单，判断附表数据与正文内容是否一致。</x:v>
       </x:c>
       <x:c r="F111" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查正文、附表和总量指标一致性。报告中的源强核算、排放汇总、总量控制和监督检查清单应使用同一套污染因子、排放口编号和排放量数据。建议核查是否存在正文与附表数据不一致、总量指标缺少来源或监督检查清单遗漏因子的情况。</x:v>
       </x:c>
       <x:c r="G111" s="6" t="str">
-        <x:v>表4- SEQ 表4- \* ARABIC 26 废气污染物排放情况一览表（表格）写明：运营期环境影响和保护措施 | 表4- SEQ 表4- \* ARABIC 27 本项目排气筒基本情况编号及名称类型地理坐标/°高度/m内径/m温度/℃设计风量/m3/h烟气流速m/s东经北纬DA001排气筒一般排放口113.13328722.787465501.[电话已脱敏].70DA002排气筒一般排放口113.13309922.787615500.[电话已脱敏].79表4- SEQ 表4- \* ARABIC 28 项目废气排放基本信息一览表产污环节污染物种类生产设备污染防治设施排放方式排放口类型工艺类型是否为...</x:v>
+        <x:v>表1- SEQ 表1- \* ARABIC 9 本项目与所在的陆域环境管控单元相符性分析（表格）写明：...合《广东省人民政府办公厅关于印发广东省2021年大气、水、土壤污染防治工作方案的通知》的相关规定。（4）与《广东省生态环境厅关于做好重点行业建设项目挥发性有机物总量指标管理工作的通知》（粤环发〔2019〕2号）相符性分析《广东省生态环境厅关于做好重点行业建设项目挥发性有机物总量指标管理工作的通知》提出：“对VOCs排放量大于300公斤/年的新、改、扩建项目，进行总量替代，按照附表1填报VOCs指标来源说明。其他排放量规模需要总量替代的，由本级生态环境主管部门自行确定范围，并按照要求审核总量指标来源，填写VOCs总量指标来源说明。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H111" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；QA测试集；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I111" s="7" t="b">
         <x:v>1</x:v>
@@ -3827,7 +3827,7 @@
       <x:c r="J111" s="11" t="str"/>
       <x:c r="K111" s="11" t="str"/>
     </x:row>
-    <x:row r="112" ht="82.5" customHeight="1">
+    <x:row r="112" ht="88.5" customHeight="1">
       <x:c r="A112" s="6" t="str">
         <x:v>P012_Q01</x:v>
       </x:c>
@@ -3835,22 +3835,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C112" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D112" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E112" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F112" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：过滤风速 不正确。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G112" s="6" t="str">
-        <x:v>Word批注/修改意见（第6条）写明：雷兆宇：过滤风速 不正确。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...式 | [手机号已脱敏]；建设地点 | 佛山市顺德区杏坛镇海凌村海赞路26号之三；地理坐标 | （东经113°13′48.58″，北纬22°44′5.51″）；国民经济行业类别 | C2927日用塑料制品制造 | 建设项目行业类别 | 二十六、塑胶和塑料制品业 29-53 塑料制品业292-其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | ☑新建（迁建）□改建□扩建□技术改造 | 建设项目申报情形 | ☑首次申报项目 □不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H112" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I112" s="7" t="b">
         <x:v>1</x:v>
@@ -3858,7 +3858,7 @@
       <x:c r="J112" s="11" t="str"/>
       <x:c r="K112" s="11" t="str"/>
     </x:row>
-    <x:row r="113" ht="82.5" customHeight="1">
+    <x:row r="113" ht="88.5" customHeight="1">
       <x:c r="A113" s="6" t="str">
         <x:v>P012_Q02</x:v>
       </x:c>
@@ -3866,22 +3866,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C113" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D113" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E113" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F113" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：需明确如何收集，附件补充调节池位置。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G113" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：需明确如何收集，附件补充调节池位置。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 20 | 环保投资（万元） | 5；环保投资占比（%） | 25% | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H113" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I113" s="7" t="b">
         <x:v>1</x:v>
@@ -3889,7 +3889,7 @@
       <x:c r="J113" s="11" t="str"/>
       <x:c r="K113" s="11" t="str"/>
     </x:row>
-    <x:row r="114" ht="82.5" customHeight="1">
+    <x:row r="114" ht="88.5" customHeight="1">
       <x:c r="A114" s="6" t="str">
         <x:v>P012_Q03</x:v>
       </x:c>
@@ -3897,22 +3897,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C114" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D114" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E114" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F114" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G114" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...m排气筒出口内径/m烟气流速/（m/s）烟气温度/℃年排放小时数/h经度纬度G1排气筒113.23000022.734751150.611304800（1）废气源强核算①有机废气项目切丝前需对生产的丝状半成品进行烘干，主要目的为去除多余的水分，该工序烘干时间较短，且工作温度较低达不到熔融温度，产生的有机废气较少，故将烘干工艺产生的污染物量并入到挤出产生的的有机废气中计算。...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1、项目概况佛山市润特龙清洁用品有限公司新建项目位于佛山市顺德区杏坛镇海凌村海赞路26号之三。本项目租赁一栋2层厂房中的第2层，层高6m（建筑总高度14m）。项目占地面积为1800平方米，建筑面积为1800平方米。主要从事日用塑料制品的生产，计划年产扫把丝1380吨、刷丝20吨、清洁扫把20万把、清洁刷2万把，项目组成详见下表。表2-1 项目工程组成表工程类别项目名称数量/建筑规模主要用途主体工程生产车间本项目车间位于一栋2层厂房的第2层其余楼层为其他项目车间。厂房总高14m（第一层高8m，第2层高6...</x:v>
       </x:c>
       <x:c r="H114" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I114" s="7" t="b">
         <x:v>1</x:v>
@@ -3920,7 +3920,7 @@
       <x:c r="J114" s="11" t="str"/>
       <x:c r="K114" s="11" t="str"/>
     </x:row>
-    <x:row r="115" ht="82.5" customHeight="1">
+    <x:row r="115" ht="88.5" customHeight="1">
       <x:c r="A115" s="6" t="str">
         <x:v>P012_Q04</x:v>
       </x:c>
@@ -3928,22 +3928,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C115" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D115" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E115" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F115" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G115" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...1″）；国民经济行业类别 | C2927日用塑料制品制造 | 建设项目行业类别 | 二十六、塑胶和塑料制品业 29-53 塑料制品业292-其他（年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | ☑新建（迁建）□改建□扩建□技术改造 | 建设项目申报情形 | ☑首次申报项目 □不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1、评价区域环境功能属性本项目所在区域环境功能属性见下表3-1：表3-1 本项目所在区域环境功能属性编号功能区名称功能区确定依据功能区类别及属性1水环境功能区《佛山市顺德区生态环境保护“十四五”规划（2021-2025）》顺德支流为Ⅲ类水体2环境空气质量功能区《佛山市顺德区生态环境保护“十四五”规划（2021-2025）》大气环境为二类功能区3声环境功能区《佛山市声环境功能区划》的通知（佛环〔2024〕1号）3类声环境功能区（编号：3322）4基本农田保护区《顺德区土地利用总体规划（2010-20...</x:v>
       </x:c>
       <x:c r="H115" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报</x:v>
       </x:c>
       <x:c r="I115" s="7" t="b">
         <x:v>1</x:v>
@@ -3951,7 +3951,7 @@
       <x:c r="J115" s="11" t="str"/>
       <x:c r="K115" s="11" t="str"/>
     </x:row>
-    <x:row r="116" ht="82.5" customHeight="1">
+    <x:row r="116" ht="88.5" customHeight="1">
       <x:c r="A116" s="6" t="str">
         <x:v>P012_Q05</x:v>
       </x:c>
@@ -3959,22 +3959,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C116" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D116" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E116" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F116" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G116" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...00天，日均工作时长16小时，则非甲烷总烃的产生速率为0.765kg/h。有组织及无组织排放情况表4-6。②颗粒物项目混料过程的原料均为塑料新粒料，且混料过程为密闭状态，基本不会有粉尘的产生，项目塑料粉尘的产生主要为边角料和次品破碎过程会产生的粉尘，污染因子为颗粒物。项目破碎过程中加盖，塑料粉尘产生量较少，在车间无组织排放。 根据建设单位提供资料可知，边角料、次品产生量约占原料使用的5%，即边角料、次品产生量为70吨/年。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...生单体废气，不会产生相应的其他特征污染物，因此挤出、烘干定型工序产生的废气主要为挥发出少量的异味气体，污染因子为非甲烷总烃。参考《排放源统计调查产排污核算方法和系数手册》-292塑料制品行业系数手册内“2929塑料零件及其他塑料制品制造行业系数表（续表1）”，“配料—混合—挤出/注塑”生产工艺，挥发性有机物（以非甲烷总烃计）的产污系数，按2.7kg/t-产品计算。项目次品和边角料破碎后全部回用于生产，塑料产品量为1400t/a，则非甲烷总烃的产生量为3.780t/a，年工作300天，日均工作时长16小时，则非甲烷总烃的产生速率为0.765kg/h。有组织及无组织排放情况表4-6。...</x:v>
       </x:c>
       <x:c r="H116" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I116" s="7" t="b">
         <x:v>1</x:v>
@@ -3982,7 +3982,7 @@
       <x:c r="J116" s="11" t="str"/>
       <x:c r="K116" s="11" t="str"/>
     </x:row>
-    <x:row r="117" ht="82.5" customHeight="1">
+    <x:row r="117" ht="88.5" customHeight="1">
       <x:c r="A117" s="6" t="str">
         <x:v>P012_Q06</x:v>
       </x:c>
@@ -3990,22 +3990,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C117" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D117" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E117" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F117" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G117" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...水处理厂处理，尾水排入顺德支流。/冷却水处理冷却水循环使用，定期经静置沉淀后，用作如厕冲水。/废气处理设施项目挤出、烘干定型产生的废气经集气罩+帘幕收集后引入“二级活性炭吸附”处理达标后引至15米G1排气筒排放/噪声治理合理调整设备布置，设备定期维护与保养，采用墙体隔声、距离衰减等治理措施/一般固体废物暂存房1个4平方米/危险废物暂存房1个4平方米/2、主要产品及产能项目主要产品及产能见下表：表2-2 项目产品方案序号名称单位产量备注1扫把丝吨/年1380φ1.5-2mm2刷丝吨/年20φ1.5-2mm3清洁...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...m排气筒出口内径/m烟气流速/（m/s）烟气温度/℃年排放小时数/h经度纬度G1排气筒113.23000022.734751150.611304800（1）废气源强核算①有机废气项目切丝前需对生产的丝状半成品进行烘干，主要目的为去除多余的水分，该工序烘干时间较短，且工作温度较低达不到熔融温度，产生的有机废气较少，故将烘干工艺产生的污染物量并入到挤出产生的的有机废气中计算。...</x:v>
       </x:c>
       <x:c r="H117" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I117" s="7" t="b">
         <x:v>1</x:v>
@@ -4013,7 +4013,7 @@
       <x:c r="J117" s="11" t="str"/>
       <x:c r="K117" s="11" t="str"/>
     </x:row>
-    <x:row r="118" ht="82.5" customHeight="1">
+    <x:row r="118" ht="88.5" customHeight="1">
       <x:c r="A118" s="6" t="str">
         <x:v>P012_Q07</x:v>
       </x:c>
@@ -4021,22 +4021,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C118" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D118" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E118" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F118" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G118" s="6" t="str">
-        <x:v>表4-20 项目固体废物产生及处置情况一览表（表格）写明：...49-08厂房西南面4平方米25kg/铁桶4t/a半年2废机油桶HW08900-249-08堆放3含油废抹布和手套HW49900-041-4925kg/塑料桶4废活性炭HW49900-039-491t/塑料袋从上表可知，项目危险废物暂存间选址可行，场所贮存能力满足要求。根据《关于发布《危险废物规范化管理指标体系》的通知》（环办【2015】99号）、《危险废物贮存污染控制标准》（GB18597-2023）。②转移建设单位拟将危险废物拟交由有危废处置资质单位处理。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | 表4-2 废气排放口基本情况点源名称坐标排气筒高度/m排气筒出口内径/m烟气流速/（m/s）烟气温度/℃年排放小时数/h经度纬度G1排气筒113.23000022.734751150.611304800（1）废气源强核算①有机废气项目切丝前需对生产的丝状半成品进行烘干，主要目的为去除多余的水分，该工序烘干时间较短，且工作温度较低达不到熔融温度，产生的有机废气较少，故将烘干工艺产生的污染物量并入到挤出产生的的有机废气中计算。挤出、烘干定型工序使用的原料为PET、PP、改性PET、尼龙、PS、EVA、PBT塑料粒和色母粒，本项目挤出工序的加工温度为200℃-...</x:v>
       </x:c>
       <x:c r="H118" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I118" s="7" t="b">
         <x:v>1</x:v>
@@ -4044,7 +4044,7 @@
       <x:c r="J118" s="11" t="str"/>
       <x:c r="K118" s="11" t="str"/>
     </x:row>
-    <x:row r="119" ht="82.5" customHeight="1">
+    <x:row r="119" ht="88.5" customHeight="1">
       <x:c r="A119" s="6" t="str">
         <x:v>P012_Q08</x:v>
       </x:c>
@@ -4052,22 +4052,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C119" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D119" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>废气收集风量与设计风量核算</x:v>
       </x:c>
       <x:c r="E119" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的集气罩尺寸、控制风速、收集点数量和风量计算过程，判断设计风量是否具有可复核性。</x:v>
       </x:c>
       <x:c r="F119" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查风量计算是否可复核。报告应说明收集点数量、罩口尺寸、控制风速或换气次数，并形成可追溯的设计风量。建议核查计算公式、取值依据、风机风量裕量和治理设施处理风量是否匹配。</x:v>
       </x:c>
       <x:c r="G119" s="6" t="str">
-        <x:v>表4-20 项目固体废物产生及处置情况一览表（表格）写明：运营期环境影响和保护措施 | （3）固废管理：①收集、贮存项目产生的一般工业固废分类收集，存储于一般固废暂存间内（约4平方米），一般固废暂存间的建设应满足防渗漏、防雨淋、防扬尘相关要求，加盖雨棚，地面采取水泥面硬化防渗措施等。项目一般固废产生量为3.5t/a。其中生活垃圾交由环卫部门处理，其他一般固体废物定期交由回收商回收利用，项目建设一个面积约为4平方米的危险废物暂存间，项目拟每半年委外处置1次，暂存间贮存能力可满足危险废物的存储需求。表4-21项目危险废物贮存场所（设施）基本情况序号贮...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...二级活性炭吸附”处理，根据《环境工程设计手册（修订版）》（湖南科学技术出版社），外部吸气罩排风量的计算得出项目集气罩风量：L=3600KPHVxL—集气罩风量，m3/h；K—风险系数1.4；P—罩口周长，m；集气罩边长0.5m*4=2m；H—污染源至罩口距离，m；取0.15mVx—控制风速，0.5m/s~1.0m/s。本项目风速取0.7m/s。...</x:v>
       </x:c>
       <x:c r="H119" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集风量与设计风量核算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I119" s="7" t="b">
         <x:v>1</x:v>
@@ -4075,7 +4075,7 @@
       <x:c r="J119" s="11" t="str"/>
       <x:c r="K119" s="11" t="str"/>
     </x:row>
-    <x:row r="120" ht="82.5" customHeight="1">
+    <x:row r="120" ht="88.5" customHeight="1">
       <x:c r="A120" s="6" t="str">
         <x:v>P012_Q09</x:v>
       </x:c>
@@ -4083,22 +4083,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C120" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D120" s="6" t="str">
-        <x:v>总量控制</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E120" s="6" t="str">
-        <x:v>请根据报告中的VOCs总量控制指标和替代来源，判断总量控制论证是否充分。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F120" s="6" t="str">
-        <x:v>判断：需核查总量控制指标和替代来源。依据：报告涉及VOCs总量、替代来源或总量指标。审核意见：建议检查总量核算是否与源强排放量一致，替代来源或削减来源是否有明确证据。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G120" s="6" t="str">
-        <x:v>六、结论（表格）写明：...= 3 \* GB3 \* MERGEFORMAT ③ | 本项目排放量（固体废物产生量） = 4 \* GB3 \* MERGEFORMAT ④ | 以新带老削减量（新建项目不填） = 5 \* GB3 \* MERGEFORMAT ⑤ | 本项目建成后全厂排放量（固体废物产生量） = 6 \* GB3 \* MERGEFORMAT ⑥ | 变化量 = 7 \* GB3 \* MERGEFORMAT ⑦；...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...水处理厂处理，尾水排入顺德支流。/冷却水处理冷却水循环使用，定期经静置沉淀后，用作如厕冲水。/废气处理设施项目挤出、烘干定型产生的废气经集气罩+帘幕收集后引入“二级活性炭吸附”处理达标后引至15米G1排气筒排放/噪声治理合理调整设备布置，设备定期维护与保养，采用墙体隔声、距离衰减等治理措施/一般固体废物暂存房1个4平方米/危险废物暂存房1个4平方米/2、主要产品及产能项目主要产品及产能见下表：表2-2 项目产品方案序号名称单位产量备注1扫把丝吨/年1380φ1.5-2mm2刷丝吨/年20φ1.5-2mm3清洁扫把万把/年20每把需扫把丝250g4清洁刷万把/年2每把需刷丝160g3、主要...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H120" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；地方政策库；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I120" s="7" t="b">
         <x:v>1</x:v>
@@ -4106,7 +4106,7 @@
       <x:c r="J120" s="11" t="str"/>
       <x:c r="K120" s="11" t="str"/>
     </x:row>
-    <x:row r="121" ht="82.5" customHeight="1">
+    <x:row r="121" ht="88.5" customHeight="1">
       <x:c r="A121" s="6" t="str">
         <x:v>P012_Q10</x:v>
       </x:c>
@@ -4114,22 +4114,22 @@
         <x:v>佛山市润特龙清洁用品有限公司新建项目（修改意见）.docx</x:v>
       </x:c>
       <x:c r="C121" s="6" t="str">
-        <x:v>| 佛山市润特龙清洁用品有限公司新建项目</x:v>
+        <x:v>佛山市润特龙清洁用品有限公司新建项目</x:v>
       </x:c>
       <x:c r="D121" s="6" t="str">
-        <x:v>排放标准适用</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E121" s="6" t="str">
-        <x:v>请根据报告中的污染因子、排放方式和标准选取，判断废气排放标准适用是否合理。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F121" s="6" t="str">
-        <x:v>判断：需核查标准适用性。依据：报告涉及GB、DB排放标准、污染因子、厂界或厂区内无组织限值。审核意见：建议结合污染因子、排放方式和行业类别核查标准选取是否完整、是否遗漏厂区内VOCs控制要求。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G121" s="6" t="str">
-        <x:v>五、环境保护措施监督检查清单（表格）写明：内容要素 | 排放口(编号、名称)/污染源 | 污染物项目 | 环境保护措施 | 执行标准；大气环境 | 有组织（G1排气筒） | 非甲烷总烃 | 项目挤出和烘干定型废气经“集气罩+帘幕”收集后引入“二级活性炭吸附”处理达标后引至15米G1排气筒排放 | 《《合成树脂工业污染物排放标准（GB31572-2015）》表4大气污染物排放限值；臭气浓度 | 《恶臭污染物排放标准》（GB14554-1993）表2恶臭污染物排放标准值；...</x:v>
+        <x:v>表4-20 项目固体废物产生及处置情况一览表（表格）写明：...| 废机油 | 维修 | 0.05 | HW08 | 900-249-08 | 液体 | 机油 | T，I | 一年 | 25kg/铁桶 | 定期交有相应资质的危废单位回收处理 | 0.05 | 根据生产需要合理设置贮存量，尽量减少厂内的物料贮存量；严禁将危险废物混入生活垃圾；堆放危险废物的地方要有明显的标志，堆放点要防雨、防渗、防漏，应按要求进行包装贮存；废机油桶 | 维修 | 0.006 | HW08 | 900-249-08 | 固体 | 机油 | T/In | 一年 | 堆放 | 0.006；...</x:v>
       </x:c>
       <x:c r="H121" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#8_塑料制品业典型污染源及执行标准；GB_31572-2015；GB_37822-2019；DB44_2367-2022</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I121" s="7" t="b">
         <x:v>1</x:v>
@@ -4137,7 +4137,7 @@
       <x:c r="J121" s="11" t="str"/>
       <x:c r="K121" s="11" t="str"/>
     </x:row>
-    <x:row r="122" ht="82.5" customHeight="1">
+    <x:row r="122" ht="88.5" customHeight="1">
       <x:c r="A122" s="6" t="str">
         <x:v>P013_Q01</x:v>
       </x:c>
@@ -4145,22 +4145,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C122" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D122" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E122" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F122" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：补充原辅材料百分比，是否可以精确多克作为单位。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G122" s="6" t="str">
-        <x:v>Word批注/修改意见（第3条）写明：雷兆宇：补充原辅材料百分比，是否可以精确多克作为单位。</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...项目北面为智富园30栋工业厂房，西面为智富园16栋工业厂房，南面为智富园停车场，东面为智富园38栋工业厂房。项目所在楼层一共八层，项目位于该楼层第五层。项目主要生产工艺为投料、加热溶解、混合搅拌、分装，生产过程不涉及化学反应。根据《中华人民共和国环境影响评价法》（2018 年12 月29 日修正版）和《建设项目环境保护管理条例》（中华人民共和国国务院令第682 号，2017 年10月01 日起施行）的有关规定，一切可能对环境造成影响的新建、扩建或改建项目必须实行环境影响评价审批制度，以便能有效的控制新的污染和生态破坏，保护环境、利国利民。...</x:v>
       </x:c>
       <x:c r="H122" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I122" s="7" t="b">
         <x:v>1</x:v>
@@ -4168,7 +4168,7 @@
       <x:c r="J122" s="11" t="str"/>
       <x:c r="K122" s="11" t="str"/>
     </x:row>
-    <x:row r="123" ht="82.5" customHeight="1">
+    <x:row r="123" ht="88.5" customHeight="1">
       <x:c r="A123" s="6" t="str">
         <x:v>P013_Q02</x:v>
       </x:c>
@@ -4176,22 +4176,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C123" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D123" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E123" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F123" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：前后两个要求不一致，一个为罩面一个为控制面，罩面风速0.6如何确定控制面能达到0.5，这还跟集气罩距离控制面距离有关。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G123" s="6" t="str">
-        <x:v>Word批注/修改意见（第11条）写明：雷兆宇：前后两个要求不一致，一个为罩面一个为控制面，罩面风速0.6如何确定控制面能达到0.5，这还跟集气罩距离控制面距离有关。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | / | 项目审批（核准/备案）文号（选填） | /；总投资（万元） | 600 | 环保投资（万元） | 30；环保投资占比（%） | 5% | 施工工期 | 4个月</x:v>
       </x:c>
       <x:c r="H123" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I123" s="7" t="b">
         <x:v>1</x:v>
@@ -4199,7 +4199,7 @@
       <x:c r="J123" s="11" t="str"/>
       <x:c r="K123" s="11" t="str"/>
     </x:row>
-    <x:row r="124" ht="82.5" customHeight="1">
+    <x:row r="124" ht="88.5" customHeight="1">
       <x:c r="A124" s="6" t="str">
         <x:v>P013_Q03</x:v>
       </x:c>
@@ -4207,22 +4207,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C124" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D124" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E124" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F124" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：确认清楚”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G124" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：确认清楚</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 项目概况广东潜龙化工有限公司新建项目（以下简称“本项目”）拟选址广东省佛山市顺德区杏坛镇高赞村杏坛水乡大道628号顺德智富园35栋503。项目中心位置地理坐标东经113.204816º，北纬22.773321º（地理位置见附图1）。经营范围为化工产品生产（不含许可类化工产品），项目占地面积为1161.27平方米，经营面积1161.27平方米，总投资600万元，其中环保投资30万元。投产后主要从事固化剂的生产和销售，预计年产固化剂1500t。项目北面为智富园30栋工业厂房，西面为智富园16栋工业厂房，南...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H124" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I124" s="7" t="b">
         <x:v>1</x:v>
@@ -4230,7 +4230,7 @@
       <x:c r="J124" s="11" t="str"/>
       <x:c r="K124" s="11" t="str"/>
     </x:row>
-    <x:row r="125" ht="82.5" customHeight="1">
+    <x:row r="125" ht="88.5" customHeight="1">
       <x:c r="A125" s="6" t="str">
         <x:v>P013_Q04</x:v>
       </x:c>
@@ -4238,22 +4238,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C125" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D125" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E125" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F125" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G125" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...污染工序。；运营期环境影响和保护措施 | 环境空气影响和保护措施参考《排污许可证申请与核发技术规范专用化学品产品制造工业》（HJ 1103—2020）和《污染源源强核算技术指南准则》（HJ884-2018），项目废气产污环节、污染物项目、排放形式及污染防治设施见下表。...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 环境空气质量现状根据《顺德区生态环境保护“十四五”规划（2021-2025年）》的通知，顺德区全境为大气环境二类区，因此本项目所在区域属二类环境空气质量功能区，执行《环境空气质量标准》(GB3095-2012)二级标准及2018年修改单。（1）达标区判定为评价本项目所在区域的环境空气质量现状，引用《佛山市生态环境局顺德分局关于发布2022年度佛山市顺德区环境质量状况公报的通知》（佛环顺函〔2023〕26号），2022 年顺德区 AQI 达标率为78.8%，较2021年减少5.9个百分点。首要污染物...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H125" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I125" s="7" t="b">
         <x:v>1</x:v>
@@ -4261,7 +4261,7 @@
       <x:c r="J125" s="11" t="str"/>
       <x:c r="K125" s="11" t="str"/>
     </x:row>
-    <x:row r="126" ht="82.5" customHeight="1">
+    <x:row r="126" ht="88.5" customHeight="1">
       <x:c r="A126" s="6" t="str">
         <x:v>P013_Q05</x:v>
       </x:c>
@@ -4269,22 +4269,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C126" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D126" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E126" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F126" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G126" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...类管理名录（2021 年版）》，本项目属于“二十三、化学原料和化学制品制造业-44、专用化学产品制造265-“单纯物理分离、物理提纯、混合、分装的（不产生废水或挥发性有机物的除外）”类别，故该项目应编制环境影响报告表。工程规模本项目占地面积为1161.27平方米，经营面积为1161.27平方米，设有办公室、生产区、仓库等。项目从业人数为5人，年工作日为260天，每天8小时，工作时间为8:00-12:00，14:00-18:00。项目内部不设置宿舍和员工饭堂，建设项目组成见表2-1。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...投料工序，投料过程为人工投加。搅拌原料时为密闭操作且粉料溶解于水中，因此搅拌过程无粉尘产生，仅在投料过程产生少量粉尘。本项目参考《排放源统计调查产排污核算方法和系数手册》的公告（公告 2021 年第24 号）中《2669其他专用化学品制造行业系数手册》中颗粒物产污系数为0.14kg/t产品。项目年产固化剂1500t，则粉尘年产生量为0.21t。投料工序每天工作时间约为0.5h，项目年工作260d，则粉尘产生速率为1.615kg/h。该粉尘产生量较少，在加强车间换气及清洁打扫的基础下，粉尘无组织排放对周围环境影响较小。投料粉尘的产排情况见表4-3项目污染物产生排放情况表所示。...</x:v>
       </x:c>
       <x:c r="H126" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I126" s="7" t="b">
         <x:v>1</x:v>
@@ -4292,7 +4292,7 @@
       <x:c r="J126" s="11" t="str"/>
       <x:c r="K126" s="11" t="str"/>
     </x:row>
-    <x:row r="127" ht="82.5" customHeight="1">
+    <x:row r="127" ht="88.5" customHeight="1">
       <x:c r="A127" s="6" t="str">
         <x:v>P013_Q06</x:v>
       </x:c>
@@ -4300,22 +4300,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C127" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D127" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E127" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F127" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G127" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...放情况表4-3。②颗粒物本项目原材料粉剂为工业水杨酸、4,4二氨基二苯基甲烷，其他原材料都是液体，主要产生粉尘的工序为投料工序，投料过程为人工投加。搅拌原料时为密闭操作且粉料溶解于水中，因此搅拌过程无粉尘产生，仅在投料过程产生少量粉尘。本项目参考《排放源统计调查产排污核算方法和系数手册》的公告（公告 2021 年第24 号）中《2669其他专用化学品制造行业系数手册》中颗粒物产污系数为0.14kg/t产品。项目年产固化剂1500t，则粉尘年产生量为0.21t。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...污染工序。；运营期环境影响和保护措施 | 环境空气影响和保护措施参考《排污许可证申请与核发技术规范专用化学品产品制造工业》（HJ 1103—2020）和《污染源源强核算技术指南准则》（HJ884-2018），项目废气产污环节、污染物项目、排放形式及污染防治设施见下表。...</x:v>
       </x:c>
       <x:c r="H127" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I127" s="7" t="b">
         <x:v>1</x:v>
@@ -4323,7 +4323,7 @@
       <x:c r="J127" s="11" t="str"/>
       <x:c r="K127" s="11" t="str"/>
     </x:row>
-    <x:row r="128" ht="82.5" customHeight="1">
+    <x:row r="128" ht="88.5" customHeight="1">
       <x:c r="A128" s="6" t="str">
         <x:v>P013_Q07</x:v>
       </x:c>
@@ -4331,22 +4331,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C128" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D128" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E128" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F128" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G128" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：项目废气产生、排放情况详见下表：表4-3 项目废气产生、排放情况一览表污染源污染物污染物产生量（t/a）治理设施有组织无组织收集效率（%）处理能力（m3/h）去除效率（%）治理方式收集量（t/a）排放量（t/a）排放速率（kg/h）排放浓度（mg/m3）排放量（t/a）排放速率（kg/h）G1有机废气1.4205650600051二级活性炭0.71030.34800.167327.88460.71030.3415臭气浓度≤20000（无量纲）///≤20000（无量纲）/≤20（无量纲）投料粉尘0.21//////...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...施排放口类型污染防治设施名称及工艺是否为可行性技术化学试剂和助剂预处理、搅拌、加热、清洗有机废气、臭气浓度有组织收集后经“二级活性炭吸附装置”处理后经高空排放（排气筒G1）是一般排放口投料粉尘无组织//（1）废气源强分析①恶臭本项目生产期间产生少量的异味，该异味污染物以臭气浓度为表征。本文引用张欢等在《恶臭污染评价分级方法》中基于韦伯-费希纳公式所建立的臭气强度与臭气浓度的关系，将国外臭气强度6级法与我国《恶臭污染物排放标准》（GB14554-1993）结合（详见表 4-2），该分级法以臭气强度的嗅觉感觉和实验经验为分级依据，对臭气浓度进行等级划分，提高了分级的准确程度。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H128" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I128" s="7" t="b">
         <x:v>1</x:v>
@@ -4354,7 +4354,7 @@
       <x:c r="J128" s="11" t="str"/>
       <x:c r="K128" s="11" t="str"/>
     </x:row>
-    <x:row r="129" ht="82.5" customHeight="1">
+    <x:row r="129" ht="88.5" customHeight="1">
       <x:c r="A129" s="6" t="str">
         <x:v>P013_Q08</x:v>
       </x:c>
@@ -4362,22 +4362,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C129" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D129" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>废气收集风量与设计风量核算</x:v>
       </x:c>
       <x:c r="E129" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的集气罩尺寸、控制风速、收集点数量和风量计算过程，判断设计风量是否具有可复核性。</x:v>
       </x:c>
       <x:c r="F129" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查风量计算是否可复核。报告应说明收集点数量、罩口尺寸、控制风速或换气次数，并形成可追溯的设计风量。建议核查计算公式、取值依据、风机风量裕量和治理设施处理风量是否匹配。</x:v>
       </x:c>
       <x:c r="G129" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...水，总用水量为286.6t/a。 排水生活污水经三级化粪池处理后排入杏坛生活污水处理厂环保工程废气治理系统有机废气和臭气浓度经集气罩（设置胶帘）收集后通过“二级活性炭吸附装置”处理后至40m高排气筒G1排放。生活污水生活污水经三级化粪池预处理达标后排入杏坛污水处理厂处理，尾水排入顺德支流。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...0450.000225②冷却塔补充用水项目冷却水循环使用，定期添加新水以补充因蒸发、风吹及造成的水分损耗，循环水定期排放。项目设有1个冷却塔，冷却水循环水量为3m³/h，间接冷却系统作业时间与生产工序相同，共工作2080h/a，则项目总循环水量为6240m³/a。根据《工业循环冷却水处理设计规范》（GB/T50050-2017）开式系统的补充水量公式：Qm Qe Qb Qw（式1.1）Qm=N-1 Qe ▪ N （式1.2）Qe k t Qr （式 1.3）Qb=N-1-Qw Qe （式 1.4）式中： Qm——补充水量（m3/h）；Qb——排污水量（m3/h）；...</x:v>
       </x:c>
       <x:c r="H129" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集风量与设计风量核算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I129" s="7" t="b">
         <x:v>1</x:v>
@@ -4385,7 +4385,7 @@
       <x:c r="J129" s="11" t="str"/>
       <x:c r="K129" s="11" t="str"/>
     </x:row>
-    <x:row r="130" ht="82.5" customHeight="1">
+    <x:row r="130" ht="88.5" customHeight="1">
       <x:c r="A130" s="6" t="str">
         <x:v>P013_Q09</x:v>
       </x:c>
@@ -4393,22 +4393,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C130" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D130" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E130" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F130" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G130" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | 目涉及危险物质贮存量占临界量比值如下表：表4-20 贮存量占临界量比值Q危险源储存量，t临界量，tqi/Qi润滑油0.0525000.00002壬基酚0.7510.75废润滑油0.0325000.000012合计0.750032计算得Q=0.750032；根据《建设项目环境影响报告表编制技术指南（污染影响类）》规定，可不进行专项分析。（2）风险源分布情况及可能影响途径本项目主要为生产区、危废仓库、原料仓库和废气处理设施存在环境风险；表4-21生产过程...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...艺是否为可行性技术化学试剂和助剂预处理、搅拌、加热、清洗有机废气、臭气浓度有组织收集后经“二级活性炭吸附装置”处理后经高空排放（排气筒G1）是一般排放口投料粉尘无组织//（1）废气源强分析①恶臭本项目生产期间产生少量的异味，该异味污染物以臭气浓度为表征。本文引用张欢等在《恶臭污染评价分级方法》中基于韦伯-费希纳公式所建立的臭气强度与臭气浓度的关系，将国外臭气强度6级法与我国《恶臭污染物排放标准》（GB14554-1993）结合（详见表 4-2），该分级法以臭气强度的嗅觉感觉和实验经验为分级依据，对臭气浓度进行等级划分，提高了分级的准确程度。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H130" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I130" s="7" t="b">
         <x:v>1</x:v>
@@ -4416,7 +4416,7 @@
       <x:c r="J130" s="11" t="str"/>
       <x:c r="K130" s="11" t="str"/>
     </x:row>
-    <x:row r="131" ht="82.5" customHeight="1">
+    <x:row r="131" ht="88.5" customHeight="1">
       <x:c r="A131" s="6" t="str">
         <x:v>P013_Q10</x:v>
       </x:c>
@@ -4424,22 +4424,22 @@
         <x:v>20240327150247848广东潜龙化工有限公司新建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C131" s="6" t="str">
-        <x:v>| 广东潜龙化工有限公司新建项目</x:v>
+        <x:v>广东潜龙化工有限公司新建项目</x:v>
       </x:c>
       <x:c r="D131" s="6" t="str">
-        <x:v>总量控制</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E131" s="6" t="str">
-        <x:v>请根据报告中的VOCs总量控制指标和替代来源，判断总量控制论证是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F131" s="6" t="str">
-        <x:v>判断：需核查总量控制指标和替代来源。依据：报告涉及VOCs总量、替代来源或总量指标。审核意见：建议检查总量核算是否与源强排放量一致，替代来源或削减来源是否有明确证据。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G131" s="6" t="str">
-        <x:v>六、结论（表格）写明：...= 3 \* GB3 \* MERGEFORMAT ③ | 本项目排放量（固体废物产生量） = 4 \* GB3 \* MERGEFORMAT ④ | 以新带老削减量（新建项目不填） = 5 \* GB3 \* MERGEFORMAT ⑤ | 本项目建成后全厂排放量（固体废物产生量） = 6 \* GB3 \* MERGEFORMAT ⑥ | 变化量 = 7 \* GB3 \* MERGEFORMAT ⑦；...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | 目涉及危险物质贮存量占临界量比值如下表：表4-20 贮存量占临界量比值Q危险源储存量，t临界量，tqi/Qi润滑油0.0525000.00002壬基酚0.7510.75废润滑油0.0325000.000012合计0.750032计算得Q=0.750032；根据《建设项目环境影响报告表编制技术指南（污染影响类）》规定，可不进行专项分析。（2）风险源分布情况及可能影响途径本项目主要为生产区、危废仓库、原料仓库和废气处理设施存在环境风险；表4-21生产过程风险源识别危险目标事故类型事故引发可能原因及后果措施危废仓库泄漏装卸或存...</x:v>
       </x:c>
       <x:c r="H131" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；地方政策库；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I131" s="7" t="b">
         <x:v>1</x:v>
@@ -4447,7 +4447,7 @@
       <x:c r="J131" s="11" t="str"/>
       <x:c r="K131" s="11" t="str"/>
     </x:row>
-    <x:row r="132" ht="82.5" customHeight="1">
+    <x:row r="132" ht="88.5" customHeight="1">
       <x:c r="A132" s="6" t="str">
         <x:v>P014_Q01</x:v>
       </x:c>
@@ -4458,19 +4458,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D132" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E132" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F132" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：提供产品图片，胶粘剂用料？用于什么产品”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G132" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：提供产品图片，胶粘剂用料？用于什么产品</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...| 广东省佛山市顺德区杏坛镇齐杏社区杏坛工业区科技二路2号威和新科园7栋602；地理坐标 | 东经113°10′15.369″,北纬22°47′13.372″；国民经济行业类别 | C2669其他专用化学产品制造 | 建设项目行业类别 | 二十三、化学原料和化学制品制造业26，44专用化学产品制造266；建设性质 | 新建（迁建）改建扩建技术改造 | 建设项目申报情形 | 首次申报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | / | 项目审批（核准/备案）文号（选填） | /；...</x:v>
       </x:c>
       <x:c r="H132" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I132" s="7" t="b">
         <x:v>1</x:v>
@@ -4478,7 +4478,7 @@
       <x:c r="J132" s="11" t="str"/>
       <x:c r="K132" s="11" t="str"/>
     </x:row>
-    <x:row r="133" ht="82.5" customHeight="1">
+    <x:row r="133" ht="88.5" customHeight="1">
       <x:c r="A133" s="6" t="str">
         <x:v>P014_Q02</x:v>
       </x:c>
@@ -4489,19 +4489,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D133" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E133" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集效率与处理效率相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F133" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：收集效率与表格不一致”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G133" s="6" t="str">
-        <x:v>Word批注/修改意见（第11条）写明：雷兆宇：收集效率与表格不一致</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | / | 项目审批（核准/备案）文号（选填） | /；总投资（万元） | 100 | 环保投资（万元） | 15；环保投资占比（%） | 15 | 施工工期 | 已建成厂房</x:v>
       </x:c>
       <x:c r="H133" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I133" s="7" t="b">
         <x:v>1</x:v>
@@ -4509,7 +4509,7 @@
       <x:c r="J133" s="11" t="str"/>
       <x:c r="K133" s="11" t="str"/>
     </x:row>
-    <x:row r="134" ht="82.5" customHeight="1">
+    <x:row r="134" ht="88.5" customHeight="1">
       <x:c r="A134" s="6" t="str">
         <x:v>P014_Q03</x:v>
       </x:c>
@@ -4520,19 +4520,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D134" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E134" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F134" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：80”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G134" s="6" t="str">
-        <x:v>Word批注/修改意见（第2条）写明：雷兆宇：80</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1、总体要求佛山市瀚铭新材料有限公司新建项目选址于广东省佛山市顺德区杏坛镇齐杏社区杏坛工业区科技二路2号威和新科园7栋602（详见附图1项目地理位置图），厂址中心坐标：东经113°10′15.369″,北纬22°47′13.372″。项目总投资100万元，占地面积844.21m2，建筑面积844.21m2，项目主要从事基础化学原料以及专用化学产品加工生产，加工生产光学树脂600吨/年、硫醇固化剂360吨/年、巯基聚合物120吨/年、纳米硅树脂200吨/年、电子胶200吨/年。项目共有员工10人，均不在...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H134" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I134" s="7" t="b">
         <x:v>1</x:v>
@@ -4540,7 +4540,7 @@
       <x:c r="J134" s="11" t="str"/>
       <x:c r="K134" s="11" t="str"/>
     </x:row>
-    <x:row r="135" ht="82.5" customHeight="1">
+    <x:row r="135" ht="88.5" customHeight="1">
       <x:c r="A135" s="6" t="str">
         <x:v>P014_Q04</x:v>
       </x:c>
@@ -4551,19 +4551,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D135" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>环境质量执行标准准确性</x:v>
       </x:c>
       <x:c r="E135" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据项目所在功能区划、声环境功能区、大气和地表水功能区，判断环境质量执行标准选取是否合理。</x:v>
       </x:c>
       <x:c r="F135" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查功能区划与执行标准是否一致。报告应根据项目所在地的大气、声环境和地表水功能区选取相应标准级别。建议核查功能区划来源、标准级别、评价因子和现状评价结论是否前后一致。</x:v>
       </x:c>
       <x:c r="G135" s="6" t="str">
-        <x:v>主要环境影响和保护措施（表格）写明：运营期环境影响和保护措施 | 4、正常工况下污染源源强核算及保护措施（1）有机废气本项目生产光学树脂600吨/年、硫醇固化剂360吨/年、巯基聚合物120吨/年、纳米硅树脂200吨/年、电子胶200吨/年生产线使用的原料安全、无毒，在生产过程中在搅拌过程中无需加热、加压，在自然条件下进行混合，在该过程只涉及到物理变化，不发生化学反应。项目在投料和搅拌过程中会挥发产生少量有机废气，污染因子主要为VOCs，由于无法准确确定挥发系数，故本项目有机废气产生系数参照《广东省石油化工行业VOCs排...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：...情况评价指标为SO2、NO2、PM10、PM2.5、CO和O3，六项污染物全部达标即为城市环境空气质量达标。根据《佛山市人民政府办公室关于调整顺德区环境空气质量功能区划的复函》（佛府办函[2014]494号，2014年8月）和《佛山市顺德区生态环境保护“十四五”规划（2021-2025）》，顺德区全境为大气环境二类区，因此本项目所在区域属二类环境空气质量功能区，执行《环境空气质量标准》（GB3095-2012）及2018年修改单二级标准。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H135" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#7_环境质量标准限值速查；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I135" s="7" t="b">
         <x:v>1</x:v>
@@ -4571,7 +4571,7 @@
       <x:c r="J135" s="11" t="str"/>
       <x:c r="K135" s="11" t="str"/>
     </x:row>
-    <x:row r="136" ht="82.5" customHeight="1">
+    <x:row r="136" ht="88.5" customHeight="1">
       <x:c r="A136" s="6" t="str">
         <x:v>P014_Q05</x:v>
       </x:c>
@@ -4582,19 +4582,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D136" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E136" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F136" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G136" s="6" t="str">
-        <x:v>主要环境影响和保护措施（表格）写明：...m/s25℃一般排放口东经：113.170990°北纬：22.787129°3、大气自行监测计划根据《排污单位自行监测技术指南》和《排污许可证申请与核发技术规范涂料、油墨、颜料及类似产品制造业》（HJ1116-2020）的相关要求，大气环境监测计划：为掌握项目大气污染源排放情况，控制厂区、周围废气浓度、保证操作人员和周围人群健康，定期环境监测工作由有资质的第三方监测单位完成，并出具具有法律效力的监测报告，自行环境监测安排见下表。...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：...生少量有机废气，污染因子主要为VOCs，由于无法准确确定挥发系数，故本项目有机废气产生系数参照《广东省石油化工行业VOCs排放量计算方法》中“其他化工类产品”的产污系数：0.021kg/t-产品，本项目年生产光学树脂600吨/年、硫醇固化剂360吨/年、巯基聚合物120吨/年、纳米硅树脂200吨/年、电子胶200吨/年，则产生VOCs为0.031t/a，年工作300天，每天工作6小时，因此，产生速率为0.017kg/h。...</x:v>
       </x:c>
       <x:c r="H136" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I136" s="7" t="b">
         <x:v>1</x:v>
@@ -4602,7 +4602,7 @@
       <x:c r="J136" s="11" t="str"/>
       <x:c r="K136" s="11" t="str"/>
     </x:row>
-    <x:row r="137" ht="82.5" customHeight="1">
+    <x:row r="137" ht="88.5" customHeight="1">
       <x:c r="A137" s="6" t="str">
         <x:v>P014_Q06</x:v>
       </x:c>
@@ -4613,19 +4613,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D137" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E137" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F137" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G137" s="6" t="str">
-        <x:v>主要环境影响和保护措施（表格）写明：...天，每天工作6小时，因此，产生速率为0.017kg/h。（2）物料粉尘本项目生产光学树脂、纳米硅树脂过程中，物料投料过程会有微量粉尘逸出，但逸出量极少，搅拌过程密闭，不会有粉尘逸出，故粉尘主要来源于粉料投加过程，主要污染物为颗粒物。参考《逸散性工业粉尘控制技术》石灰生产的逸散尘排放因子，粉尘排放系数为0.015-0.2kg/t物料，按保守估算，本项目取投料粉尘产污系数取最大值，即0.2kg/t-物料。...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：运营期环境影响和保护措施 | 4、废水污染源源强核算及保护措施（1）设备清洗废水项目共设有6个主缸（容积为1.2m3）和6个副缸（容积为0.5m3）。项目使用自来水对分散搅拌缸进行内部清洗，清洗时只需用增压水枪冲洗缸内壁附着的少量原料，根据厂家提供的资料，清洗用水量占缸容积的10%。项目预计每周会更换产品批次（不同批次的产品原材料成分比例的差异不大），则项目需要每周清洗一次生产设备，项目工作时间按6天/周，年工作300天（按年工作50周计）。设备清洗用水核算表设备数量/个清洗次数/次单次用水量/m3总用水量m3/a1.2吨主缸6500.12360.5吨副缸6...</x:v>
       </x:c>
       <x:c r="H137" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I137" s="7" t="b">
         <x:v>1</x:v>
@@ -4633,7 +4633,7 @@
       <x:c r="J137" s="11" t="str"/>
       <x:c r="K137" s="11" t="str"/>
     </x:row>
-    <x:row r="138" ht="82.5" customHeight="1">
+    <x:row r="138" ht="88.5" customHeight="1">
       <x:c r="A138" s="6" t="str">
         <x:v>P014_Q07</x:v>
       </x:c>
@@ -4644,19 +4644,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D138" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E138" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F138" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G138" s="6" t="str">
-        <x:v>主要环境影响和保护措施（表格）写明：...（3）恶臭项目投料、分散搅拌生产过程中会产生少量的恶臭污染物，其主要污染因子为臭气浓度。加强车间通风换气。投料、分散搅拌工序产生的恶臭废气经配套的废气处理设施“二级活性炭吸附装置”收集处理后高空排放（55米），有组织排放臭气浓度低于2000无量纲，有组织排放部分的恶臭废气其臭气浓度达到《恶臭污染物排放标准》(GB14554-93)表2恶臭污染物排放标准值；...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：...天，每天工作6小时，因此，产生速率为0.017kg/h。（2）物料粉尘本项目生产光学树脂、纳米硅树脂过程中，物料投料过程会有微量粉尘逸出，但逸出量极少，搅拌过程密闭，不会有粉尘逸出，故粉尘主要来源于粉料投加过程，主要污染物为颗粒物。参考《逸散性工业粉尘控制技术》石灰生产的逸散尘排放因子，粉尘排放系数为0.015-0.2kg/t物料，按保守估算，本项目取投料粉尘产污系数取最大值，即0.2kg/t-物料。...</x:v>
       </x:c>
       <x:c r="H138" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I138" s="7" t="b">
         <x:v>1</x:v>
@@ -4664,7 +4664,7 @@
       <x:c r="J138" s="11" t="str"/>
       <x:c r="K138" s="11" t="str"/>
     </x:row>
-    <x:row r="139" ht="82.5" customHeight="1">
+    <x:row r="139" ht="88.5" customHeight="1">
       <x:c r="A139" s="6" t="str">
         <x:v>P014_Q08</x:v>
       </x:c>
@@ -4675,19 +4675,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D139" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>废气收集风量与设计风量核算</x:v>
       </x:c>
       <x:c r="E139" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的集气罩尺寸、控制风速、收集点数量和风量计算过程，判断设计风量是否具有可复核性。</x:v>
       </x:c>
       <x:c r="F139" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查风量计算是否可复核。报告应说明收集点数量、罩口尺寸、控制风速或换气次数，并形成可追溯的设计风量。建议核查计算公式、取值依据、风机风量裕量和治理设施处理风量是否匹配。</x:v>
       </x:c>
       <x:c r="G139" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...a）供电工程市政供电储运工程仓库仓库位于生产车间内（约584.21m2）环保工程废气有机废气、物料粉尘、恶臭项目有机废气、物料粉尘、恶臭经集气罩收集后通过“二级活性炭吸附”处理后，引至55m高的排气筒排放，剩余的以无组织形式排放至车间内，加强车间内通风换气废水生活污水生活污水经三级化粪池预处理后排入市政污水管网，进入杏坛镇污水处理厂处理清洗废水清洗废水经收集后，交由佛山市顺德区绿点废水回收有限公司回收处理噪声生产设备做减振处理，墙体隔音、距离衰减固体废物设置生活垃圾存放点位于办公室内、一般工业固废仓位于生产车...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：...集后通过“二级活性炭吸附”处理后，引至55m高的排气筒排放，废气收集效率为65%，二级活性炭吸附装置处理设施的处理效率为51%，剩余部分以无组织形式排放。（1）设计风量：集气罩：本项目投料、分散搅拌工序产生的废气设施集气罩收集，依据《简明通风设计手册》[主编：孙一坚（湖南大学），中国建筑工业出版社出版]，上吸式集气罩的排风量计算公式为：Q=K×P×H×Vx×3600式中：Q——设计风量（m3/h）；Vx——控制风速m/s，取Vx=0.5m/s；P——集气罩周长m，P=2（a+b）；K：考虑沿高度分布不均匀的安全系数，通常取1.4；H：控制点（废气发生源）至罩口的距离，取H=0.3m。...</x:v>
       </x:c>
       <x:c r="H139" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集风量与设计风量核算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I139" s="7" t="b">
         <x:v>1</x:v>
@@ -4695,7 +4695,7 @@
       <x:c r="J139" s="11" t="str"/>
       <x:c r="K139" s="11" t="str"/>
     </x:row>
-    <x:row r="140" ht="82.5" customHeight="1">
+    <x:row r="140" ht="88.5" customHeight="1">
       <x:c r="A140" s="6" t="str">
         <x:v>P014_Q09</x:v>
       </x:c>
@@ -4706,19 +4706,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D140" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E140" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F140" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G140" s="6" t="str">
-        <x:v>主要环境影响和保护措施（表格）写明：...化学品储存在仓库里，控制储存量。现场配置泄漏吸附收集等应急器材，防止泄漏物挥发泄漏化学品进入水体水环境通过雨水管排放到附近水体，影响内河涌水质，影响水生环境生产危险废物泄漏泄漏危险废物污染地表水及地下水危险废物水环境危废间危险废物暂存间设置围堰，做好防渗措施废气事故排放废气处理设施故障，导致废气未经处理直接排放至大气中废气大气环境对附近环境造成瞬时影响废气处理设施加强废气处理设施的日常运行维护管理，定期检修废气处理设施；...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：...织排放臭气浓度低于2000无量纲，有组织排放部分的恶臭废气其臭气浓度达到《恶臭污染物排放标准》(GB14554-93)表2恶臭污染物排放标准值；少部分未收集到的无组织恶臭废气其臭气浓度产生值较小，通过加强车间的机械通风，降低车间内的恶臭气味浓度，促使厂界臭气浓度低于20无量纲，臭气厂界浓度可满足《恶臭污染物排放标准》（GB14554-93）表1恶臭污染物厂界标准二级标准值的要求，建议企业为生产操作的一线员工配备必要的劳保用品，以确保员工身体健康不受到影响，对车间内环境空气及外界大气环境影响不大。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H140" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I140" s="7" t="b">
         <x:v>1</x:v>
@@ -4726,7 +4726,7 @@
       <x:c r="J140" s="11" t="str"/>
       <x:c r="K140" s="11" t="str"/>
     </x:row>
-    <x:row r="141" ht="82.5" customHeight="1">
+    <x:row r="141" ht="88.5" customHeight="1">
       <x:c r="A141" s="6" t="str">
         <x:v>P014_Q10</x:v>
       </x:c>
@@ -4737,19 +4737,19 @@
         <x:v>佛山市瀚铭新材料有限公司新建项目</x:v>
       </x:c>
       <x:c r="D141" s="6" t="str">
-        <x:v>总量控制</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E141" s="6" t="str">
-        <x:v>请根据报告中的VOCs总量控制指标和替代来源，判断总量控制论证是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F141" s="6" t="str">
-        <x:v>判断：需核查总量控制指标和替代来源。依据：报告涉及VOCs总量、替代来源或总量指标。审核意见：建议检查总量核算是否与源强排放量一致，替代来源或削减来源是否有明确证据。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G141" s="6" t="str">
-        <x:v>六、结论（表格）写明：...= 3 \* GB3 \* MERGEFORMAT ③ | 本项目排放量（固体废物产生量） = 4 \* GB3 \* MERGEFORMAT ④ | 以新带老削减量（新建项目不填） = 5 \* GB3 \* MERGEFORMAT ⑤ | 本项目建成后全厂排放量（固体废物产生量） = 6 \* GB3 \* MERGEFORMAT ⑥ | 变化量 = 7 \* GB3 \* MERGEFORMAT ⑦；...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：...m/s25℃一般排放口东经：113.170990°北纬：22.787129°3、大气自行监测计划根据《排污单位自行监测技术指南》和《排污许可证申请与核发技术规范涂料、油墨、颜料及类似产品制造业》（HJ1116-2020）的相关要求，大气环境监测计划：为掌握项目大气污染源排放情况，控制厂区、周围废气浓度、保证操作人员和周围人群健康，定期环境监测工作由有资质的第三方监测单位完成，并出具具有法律效力的监测报告，自行环境监测安排见下表。...</x:v>
       </x:c>
       <x:c r="H141" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；地方政策库；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I141" s="7" t="b">
         <x:v>1</x:v>
@@ -4757,7 +4757,7 @@
       <x:c r="J141" s="11" t="str"/>
       <x:c r="K141" s="11" t="str"/>
     </x:row>
-    <x:row r="142" ht="82.5" customHeight="1">
+    <x:row r="142" ht="88.5" customHeight="1">
       <x:c r="A142" s="6" t="str">
         <x:v>P015_Q01</x:v>
       </x:c>
@@ -4768,19 +4768,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D142" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E142" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F142" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：补充助焊剂以及锡膏的用量核算一览表”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G142" s="6" t="str">
-        <x:v>Word批注/修改意见（第2条）写明：雷兆宇：补充助焊剂以及锡膏的用量核算一览表</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...伦教街道办事处新塘村委会世龙工业区新塘村世龙大道1号厂房；地理坐标 | 北纬 22 度 52 分 27.287 秒，东经 113 度 11 分 1.383 秒；国民经济行业类别 | C3854家用厨房电器具制造 | 建设项目行业类别 | 三十五、电器机械和器材制造业38-家用电力器具制造385-其他（仅分割、焊接、组装的除外；年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）□改建扩建□技术改造 | 建设项目申报情形 | 首次申报项目 □不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H142" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I142" s="7" t="b">
         <x:v>1</x:v>
@@ -4788,7 +4788,7 @@
       <x:c r="J142" s="11" t="str"/>
       <x:c r="K142" s="11" t="str"/>
     </x:row>
-    <x:row r="143" ht="82.5" customHeight="1">
+    <x:row r="143" ht="88.5" customHeight="1">
       <x:c r="A143" s="6" t="str">
         <x:v>P015_Q02</x:v>
       </x:c>
@@ -4799,19 +4799,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D143" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E143" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F143" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：这里应该对应操作台的面积，而非仅仅罩口面积，否则没办法确保操作台的收集效率。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G143" s="6" t="str">
-        <x:v>Word批注/修改意见（第7条）写明：雷兆宇：这里应该对应操作台的面积，而非仅仅罩口面积，否则没办法确保操作台的收集效率。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 750 | 环保投资（万元） | 20；环保投资占比（%） | 2.67 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H143" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I143" s="7" t="b">
         <x:v>1</x:v>
@@ -4819,7 +4819,7 @@
       <x:c r="J143" s="11" t="str"/>
       <x:c r="K143" s="11" t="str"/>
     </x:row>
-    <x:row r="144" ht="82.5" customHeight="1">
+    <x:row r="144" ht="88.5" customHeight="1">
       <x:c r="A144" s="6" t="str">
         <x:v>P015_Q03</x:v>
       </x:c>
@@ -4830,19 +4830,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D144" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E144" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F144" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：是否还需调配。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G144" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：是否还需调配。</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1、项目组成搬迁前，项目位于佛山市顺德区伦教新塘村委会新龙大道8号之五；搬迁后，项目位于佛山市顺德区伦教街道办事处新塘村委会世龙工业区新塘村世龙大道1号，租用已建成的工业厂房，厂房共5层，占地面积为4500 m2，经营面积为13300 m2。项目主要从事电陶炉、电磁炉的生产和经营。项目生产车间包括插件区、波峰焊区、回流焊区、焊接区、总装区、检验区、测试区、包装区、办公室、仓库等。项目工程组成见表2-1。表2-1 项目工程组成项目内容规模用途主体工程生产车间一层共3300m2，其中夹层面积约800m2作...</x:v>
       </x:c>
       <x:c r="H144" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I144" s="7" t="b">
         <x:v>1</x:v>
@@ -4850,7 +4850,7 @@
       <x:c r="J144" s="11" t="str"/>
       <x:c r="K144" s="11" t="str"/>
     </x:row>
-    <x:row r="145" ht="82.5" customHeight="1">
+    <x:row r="145" ht="88.5" customHeight="1">
       <x:c r="A145" s="6" t="str">
         <x:v>P015_Q04</x:v>
       </x:c>
@@ -4861,19 +4861,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D145" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E145" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F145" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G145" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...，VOCs最大产生速率为0.496 kg/h。b）烟尘项目波峰焊需要使用无铅锡条，锡条熔融过程产生烟尘，其主要污染因子为锡及其化合物。根据《排放源统计调查产排污核算方法和系数手册》中的电子电气行业系数手册，“工段为焊接，原料为无铅焊料（锡条等），工艺为波峰焊，规模为所有规模的系数手册”，波峰焊中焊接烟尘产污系数为4.134×10-1g/kg-焊料，项目锡条年用量为10.98 t/a，每小时用量为6.1 kg/h，则该工序锡及其化合物产生速率为0.0025 kg/h，产生量为0.005 t/a。...</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1、大气环境根据佛山市顺德区人民政府办公室关于印发《佛山市顺德区生态环境保护“十四五”规划（2021-2025）》的通知，项目所在地属二类功能区，执行《环境空气质量标准》（GB3095-2012）及2018年修改单中的二级标准。根据《佛山市生态环境局顺德分局关于发布2022年度佛山市顺德区环境质量状况公报的通知》（佛环顺函〔2023〕26号），2022年全区空气质量综合指数为3.27，比2021年下降6.0%，在全市五区中排名第二。2022年全区二氧化硫（SO2）、二氧化氮（NO2）、可吸入颗粒物...</x:v>
       </x:c>
       <x:c r="H145" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报</x:v>
       </x:c>
       <x:c r="I145" s="7" t="b">
         <x:v>1</x:v>
@@ -4881,7 +4881,7 @@
       <x:c r="J145" s="11" t="str"/>
       <x:c r="K145" s="11" t="str"/>
     </x:row>
-    <x:row r="146" ht="82.5" customHeight="1">
+    <x:row r="146" ht="88.5" customHeight="1">
       <x:c r="A146" s="6" t="str">
         <x:v>P015_Q05</x:v>
       </x:c>
@@ -4892,19 +4892,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D146" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E146" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F146" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G146" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...C3854家用厨房电器具制造 | 建设项目行业类别 | 三十五、电器机械和器材制造业38-家用电力器具制造385-其他（仅分割、焊接、组装的除外；年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）□改建扩建□技术改造 | 建设项目申报情形 | 首次申报项目 □不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...最大产生速率为0.496 kg/h。b）烟尘项目波峰焊需要使用无铅锡条，锡条熔融过程产生烟尘，其主要污染因子为锡及其化合物。根据《排放源统计调查产排污核算方法和系数手册》中的电子电气行业系数手册，“工段为焊接，原料为无铅焊料（锡条等），工艺为波峰焊，规模为所有规模的系数手册”，波峰焊中焊接烟尘产污系数为4.134×10-1g/kg-焊料，项目锡条年用量为10.98 t/a，每小时用量为6.1 kg/h，则该工序锡及其化合物产生速率为0.0025 kg/h，产生量为0.005 t/a。波峰焊废气经集气管收集，经二级活性炭吸附处理后通过25m排气筒G1排放。...</x:v>
       </x:c>
       <x:c r="H146" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I146" s="7" t="b">
         <x:v>1</x:v>
@@ -4912,7 +4912,7 @@
       <x:c r="J146" s="11" t="str"/>
       <x:c r="K146" s="11" t="str"/>
     </x:row>
-    <x:row r="147" ht="82.5" customHeight="1">
+    <x:row r="147" ht="88.5" customHeight="1">
       <x:c r="A147" s="6" t="str">
         <x:v>P015_Q06</x:v>
       </x:c>
@@ -4923,19 +4923,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D147" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E147" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F147" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G147" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...、VOCs、臭气浓度有组织集气管95%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩30%烘干烘干机烘干隧道密闭收集95%补焊电烙铁锡及其化合物有组织移动软管+伞型罩30%/项目生产过程产生的大气污染物主要为回流焊、波峰焊过程产生有机废气、焊接烟尘和少量异味；刷三防漆、烘干工序产生的有机废气和少量异味；补焊过程产生的焊锡废气等。（1）有组织废气（排气筒 G1）①波峰焊废气a）有机废气项目波峰焊过程使用助焊剂，会产生有机废气，污染因子为VOCs。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...机废气，污染因子为VOCs。根据建设单位提供的MSDS，助焊剂中挥发成分有异丙醇、松香，VOCs挥发系数按99.2%计。助焊剂用量为1.1 t/a，则VOCs的产生量为1.091 t/a。助焊剂每小时最大使用量为5 kg/h，VOCs最大产生速率为0.496 kg/h。b）烟尘项目波峰焊需要使用无铅锡条，锡条熔融过程产生烟尘，其主要污染因子为锡及其化合物。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H147" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I147" s="7" t="b">
         <x:v>1</x:v>
@@ -4943,7 +4943,7 @@
       <x:c r="J147" s="11" t="str"/>
       <x:c r="K147" s="11" t="str"/>
     </x:row>
-    <x:row r="148" ht="82.5" customHeight="1">
+    <x:row r="148" ht="88.5" customHeight="1">
       <x:c r="A148" s="6" t="str">
         <x:v>P015_Q07</x:v>
       </x:c>
@@ -4954,19 +4954,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D148" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E148" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F148" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G148" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...影响和保护措施 | 1、废气表4-1 项目废气产污环节、污染物种类、排放形式及污染防治设施一览表产污环节生产设施污染物种类排放形式污染防治设施排放口类型收集方式收集效率处理效率污染防治设施名称及工艺是否为可行性技术焊接波峰焊机、回流焊机锡及其化合物、VOCs、臭气浓度有组织集气管95%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩30%烘干烘干机烘干隧道密闭收集95%补焊电烙铁锡及其化合物有组织移动软管+伞型罩30%/项目生产过程产生的大气污染物主要为回流焊...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...营期环境影响和保护措施 | 1、废气表4-1 项目废气产污环节、污染物种类、排放形式及污染防治设施一览表产污环节生产设施污染物种类排放形式污染防治设施排放口类型收集方式收集效率处理效率污染防治设施名称及工艺是否为可行性技术焊接波峰焊机、回流焊机锡及其化合物、VOCs、臭气浓度有组织集气管95%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩30%烘干烘干机烘干隧道密闭收集95%补焊电烙铁锡及其化合物有组织移动软管+伞型罩30%/项目生产过程产生的大气污染物主要为回流焊、波峰焊过程产生有机废气、焊接烟尘和少量异味；...</x:v>
       </x:c>
       <x:c r="H148" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022</x:v>
       </x:c>
       <x:c r="I148" s="7" t="b">
         <x:v>1</x:v>
@@ -4974,7 +4974,7 @@
       <x:c r="J148" s="11" t="str"/>
       <x:c r="K148" s="11" t="str"/>
     </x:row>
-    <x:row r="149" ht="82.5" customHeight="1">
+    <x:row r="149" ht="88.5" customHeight="1">
       <x:c r="A149" s="6" t="str">
         <x:v>P015_Q08</x:v>
       </x:c>
@@ -4985,19 +4985,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D149" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E149" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F149" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G149" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...过市政管道排入伦教污水处理厂处理废气处理设施一套波峰焊机、回流焊机、烘干机产生的废气经管道收集，补焊、刷三防漆工序产生的废气通过移动软管+伞型罩收集，然后经两级活性炭吸附处理后引至25m高排气筒G1排放一般固废间1个位于厂房一层，10 m2，用于一般固废暂存危险废物暂存点1个位于厂房一层，10 m2，危险废物暂存2、主要产品及产能搬迁前后，项目经营范围不变，项目主要从事电陶炉、电磁炉的生产制造及经营工作，项目建成后产品产量见表2-2。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...影响和保护措施 | 1、废气表4-1 项目废气产污环节、污染物种类、排放形式及污染防治设施一览表产污环节生产设施污染物种类排放形式污染防治设施排放口类型收集方式收集效率处理效率污染防治设施名称及工艺是否为可行性技术焊接波峰焊机、回流焊机锡及其化合物、VOCs、臭气浓度有组织集气管95%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩30%烘干烘干机烘干隧道密闭收集95%补焊电烙铁锡及其化合物有组织移动软管+伞型罩30%/项目生产过程产生的大气污染物主要为回流焊、波峰焊过程产生有机废气、焊接烟尘和少量异味；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H149" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I149" s="7" t="b">
         <x:v>1</x:v>
@@ -5005,7 +5005,7 @@
       <x:c r="J149" s="11" t="str"/>
       <x:c r="K149" s="11" t="str"/>
     </x:row>
-    <x:row r="150" ht="82.5" customHeight="1">
+    <x:row r="150" ht="88.5" customHeight="1">
       <x:c r="A150" s="6" t="str">
         <x:v>P015_Q09</x:v>
       </x:c>
@@ -5016,19 +5016,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D150" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E150" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F150" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G150" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...，其中夹层面积约800m2作为仓库，用于来料检验办公区、原辅材料和成品储存等二层共2500m2作为生产车间，主要用于电源线加工区、检验区、产品总装、备料区、成品暂存区等三层共2500m2作为生产车间，主要用于SMT生产线、波峰焊区、回流焊区、办公区、电子仓等四层共2500m2作为办公室，用于员工日常办公、会议、研发用途五层共2500m2作为仓库，用于验货区和成品储存等辅助工程办公室共2700m2用于员工日常办公用途储运工程仓库共6500m2用于原料和成品储存公用工程配电系统一套供应生产用电和办公生活用电给排水...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...染防治设施排放口类型收集方式收集效率处理效率污染防治设施名称及工艺是否为可行性技术焊接波峰焊机、回流焊机锡及其化合物、VOCs、臭气浓度有组织集气管95%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩30%烘干烘干机烘干隧道密闭收集95%补焊电烙铁锡及其化合物有组织移动软管+伞型罩30%/项目生产过程产生的大气污染物主要为回流焊、波峰焊过程产生有机废气、焊接烟尘和少量异味；刷三防漆、烘干工序产生的有机废气和少量异味；补焊过程产生的焊锡废气等。...</x:v>
       </x:c>
       <x:c r="H150" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则</x:v>
       </x:c>
       <x:c r="I150" s="7" t="b">
         <x:v>1</x:v>
@@ -5036,7 +5036,7 @@
       <x:c r="J150" s="11" t="str"/>
       <x:c r="K150" s="11" t="str"/>
     </x:row>
-    <x:row r="151" ht="82.5" customHeight="1">
+    <x:row r="151" ht="88.5" customHeight="1">
       <x:c r="A151" s="6" t="str">
         <x:v>P015_Q10</x:v>
       </x:c>
@@ -5047,19 +5047,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D151" s="6" t="str">
-        <x:v>总量控制</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E151" s="6" t="str">
-        <x:v>请根据报告中的VOCs总量控制指标和替代来源，判断总量控制论证是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F151" s="6" t="str">
-        <x:v>判断：需核查总量控制指标和替代来源。依据：报告涉及VOCs总量、替代来源或总量指标。审核意见：建议检查总量核算是否与源强排放量一致，替代来源或削减来源是否有明确证据。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G151" s="6" t="str">
-        <x:v>六、结论（表格）写明：...= 3 \* GB3 \* MERGEFORMAT ③ | 本项目排放量（固体废物产生量） = 4 \* GB3 \* MERGEFORMAT ④ | 以新带老削减量（新建项目不填） = 5 \* GB3 \* MERGEFORMAT ⑤ | 本项目建成后全厂排放量（固体废物产生量） = 6 \* GB3 \* MERGEFORMAT ⑥ | 变化量 = 7 \* GB3 \* MERGEFORMAT ⑦；...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...用厨房电器具制造 | 建设项目行业类别 | 三十五、电器机械和器材制造业38-家用电力器具制造385-其他（仅分割、焊接、组装的除外；年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）□改建扩建□技术改造 | 建设项目申报情形 | 首次申报项目 □不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 750 | 环保投资（万元） | 20；环保投资占比（%） | 2.67 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H151" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；地方政策库；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则</x:v>
       </x:c>
       <x:c r="I151" s="7" t="b">
         <x:v>1</x:v>
@@ -5067,7 +5067,7 @@
       <x:c r="J151" s="11" t="str"/>
       <x:c r="K151" s="11" t="str"/>
     </x:row>
-    <x:row r="152" ht="82.5" customHeight="1">
+    <x:row r="152" ht="88.5" customHeight="1">
       <x:c r="A152" s="6" t="str">
         <x:v>P016_Q01</x:v>
       </x:c>
@@ -5078,19 +5078,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D152" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E152" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F152" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：原项目需现行方法进行分析，重新核算出项目的VOcs，颗粒物。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G152" s="6" t="str">
-        <x:v>Word批注/修改意见（第9条）写明：雷兆宇：原项目需现行方法进行分析，重新核算出项目的VOcs，颗粒物。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...伦教街道办事处新塘村委会世龙工业区新塘村世龙大道1号厂房；地理坐标 | 北纬 22 度 52 分 27.287 秒，东经 113 度 11 分 1.383 秒；国民经济行业类别 | C3854家用厨房电器具制造 | 建设项目行业类别 | 三十五、电器机械和器材制造业38-家用电力器具制造385-其他（仅分割、焊接、组装的除外；年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）□改建扩建□技术改造 | 建设项目申报情形 | 首次申报项目 □不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H152" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I152" s="7" t="b">
         <x:v>1</x:v>
@@ -5098,7 +5098,7 @@
       <x:c r="J152" s="11" t="str"/>
       <x:c r="K152" s="11" t="str"/>
     </x:row>
-    <x:row r="153" ht="82.5" customHeight="1">
+    <x:row r="153" ht="88.5" customHeight="1">
       <x:c r="A153" s="6" t="str">
         <x:v>P016_Q02</x:v>
       </x:c>
@@ -5109,19 +5109,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D153" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E153" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F153" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：不执行的依据，文件中描述“溶剂型底色漆[载货汽车用、客车(机动车)用、汽车修补用、轨道交通车辆用]等涂料产品，目前暂无低VOC含量的溶剂型涂料产品，但考虑到该产品在溶剂型涂层体系的配套性需求是必不可少的，VOC含量的限量值应符合相应产品的强制性国家标准中VOC项目的技术要求”。“本标准不适用于航空航天涂料、核电涂料、军事装备和设施用涂料 ”。...”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G153" s="6" t="str">
-        <x:v>Word批注/修改意见（第5条）写明：雷兆宇：不执行的依据，文件中描述“溶剂型底色漆[载货汽车用、客车(机动车)用、汽车修补用、轨道交通车辆用]等涂料产品，目前暂无低VOC含量的溶剂型涂料产品，但考虑到该产品在溶剂型涂层体系的配套性需求是必不可少的，VOC含量的限量值应符合相应产品的强制性国家标准中VOC项目的技术要求”。“本标准不适用于航空航天涂料、核电涂料、军事装备和设施用涂料 ”。请按要求执行。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 750 | 环保投资（万元） | 20；环保投资占比（%） | 2.67 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H153" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I153" s="7" t="b">
         <x:v>1</x:v>
@@ -5129,7 +5129,7 @@
       <x:c r="J153" s="11" t="str"/>
       <x:c r="K153" s="11" t="str"/>
     </x:row>
-    <x:row r="154" ht="82.5" customHeight="1">
+    <x:row r="154" ht="88.5" customHeight="1">
       <x:c r="A154" s="6" t="str">
         <x:v>P016_Q03</x:v>
       </x:c>
@@ -5140,19 +5140,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D154" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E154" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F154" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：采用国家减排，伞型罩不带垂帘30%，管道收集95%。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G154" s="6" t="str">
-        <x:v>Word批注/修改意见（第11条）写明：雷兆宇：采用国家减排，伞型罩不带垂帘30%，管道收集95%。</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1、项目组成搬迁前，项目位于佛山市顺德区伦教新塘村委会新龙大道8号之五；搬迁后，项目位于佛山市顺德区伦教街道办事处新塘村委会世龙工业区新塘村世龙大道1号，租用已建成的工业厂房，厂房共5层，占地面积为4500 m2，经营面积为13300 m2。项目主要从事电陶炉、电磁炉的生产和经营。项目生产车间包括插件区、波峰焊区、回流焊区、焊接区、总装区、检验区、测试区、包装区、办公室、仓库等。项目工程组成见表2-1。表2-1 项目工程组成项目内容规模用途主体工程生产车间一层共3300m2，其中夹层面积约800m2作...</x:v>
       </x:c>
       <x:c r="H154" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I154" s="7" t="b">
         <x:v>1</x:v>
@@ -5160,7 +5160,7 @@
       <x:c r="J154" s="11" t="str"/>
       <x:c r="K154" s="11" t="str"/>
     </x:row>
-    <x:row r="155" ht="82.5" customHeight="1">
+    <x:row r="155" ht="88.5" customHeight="1">
       <x:c r="A155" s="6" t="str">
         <x:v>P016_Q04</x:v>
       </x:c>
@@ -5171,19 +5171,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D155" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E155" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F155" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：主要生产设备标注好”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G155" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：主要生产设备标注好</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1、大气环境根据佛山市顺德区人民政府办公室关于印发《佛山市顺德区生态环境保护“十四五”规划（2021-2025）》的通知，项目所在地属二类功能区，执行《环境空气质量标准》（GB3095-2012）及2018年修改单中的二级标准。根据《佛山市生态环境局顺德分局关于发布2022年度佛山市顺德区环境质量状况公报的通知》（佛环顺函〔2023〕26号），2022年全区空气质量综合指数为3.27，比2021年下降6.0%，在全市五区中排名第二。2022年全区二氧化硫（SO2）、二氧化氮（NO2）、可吸入颗粒物...</x:v>
       </x:c>
       <x:c r="H155" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报</x:v>
       </x:c>
       <x:c r="I155" s="7" t="b">
         <x:v>1</x:v>
@@ -5191,7 +5191,7 @@
       <x:c r="J155" s="11" t="str"/>
       <x:c r="K155" s="11" t="str"/>
     </x:row>
-    <x:row r="156" ht="82.5" customHeight="1">
+    <x:row r="156" ht="88.5" customHeight="1">
       <x:c r="A156" s="6" t="str">
         <x:v>P016_Q05</x:v>
       </x:c>
@@ -5202,19 +5202,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D156" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E156" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F156" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G156" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...，VOCs最大产生速率为1.984 kg/h。b）烟尘项目波峰焊需要使用无铅锡条，锡条熔融过程产生烟尘，其主要污染因子为锡及其化合物。根据《排放源统计调查产排污核算方法和系数手册》中的电子电气行业系数手册，“工段为焊接，原料为无铅焊料（锡条等），工艺为波峰焊，规模为所有规模的系数手册”，波峰焊中焊接烟尘产污系数为4.134×10-1g/kg-焊料，项目锡条年用量为10.98 t/a，每小时用量为6.1 kg/h，则该工序锡及其化合物产生速率为0.0025 kg/h，产生量为0.005 t/a。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...最大产生速率为1.984 kg/h。b）烟尘项目波峰焊需要使用无铅锡条，锡条熔融过程产生烟尘，其主要污染因子为锡及其化合物。根据《排放源统计调查产排污核算方法和系数手册》中的电子电气行业系数手册，“工段为焊接，原料为无铅焊料（锡条等），工艺为波峰焊，规模为所有规模的系数手册”，波峰焊中焊接烟尘产污系数为4.134×10-1g/kg-焊料，项目锡条年用量为10.98 t/a，每小时用量为6.1 kg/h，则该工序锡及其化合物产生速率为0.0025 kg/h，产生量为0.005 t/a。波峰焊废气经集气管收集，经二级活性炭吸附处理后通过25m排气筒G1排放。...</x:v>
       </x:c>
       <x:c r="H156" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I156" s="7" t="b">
         <x:v>1</x:v>
@@ -5222,7 +5222,7 @@
       <x:c r="J156" s="11" t="str"/>
       <x:c r="K156" s="11" t="str"/>
     </x:row>
-    <x:row r="157" ht="82.5" customHeight="1">
+    <x:row r="157" ht="88.5" customHeight="1">
       <x:c r="A157" s="6" t="str">
         <x:v>P016_Q06</x:v>
       </x:c>
@@ -5233,19 +5233,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D157" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E157" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F157" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G157" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...C3854家用厨房电器具制造 | 建设项目行业类别 | 三十五、电器机械和器材制造业38-家用电力器具制造385-其他（仅分割、焊接、组装的除外；年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）□改建扩建□技术改造 | 建设项目申报情形 | 首次申报项目 □不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...机废气，污染因子为VOCs。根据建设单位提供的MSDS，助焊剂中挥发成分有异丙醇、松香，VOCs挥发系数按99.2%计。助焊剂用量为3.6 t/a，则VOCs的产生量为3.571 t/a。助焊剂每小时最大使用量为2 kg/h，VOCs最大产生速率为1.984 kg/h。b）烟尘项目波峰焊需要使用无铅锡条，锡条熔融过程产生烟尘，其主要污染因子为锡及其化合物。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H157" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I157" s="7" t="b">
         <x:v>1</x:v>
@@ -5253,7 +5253,7 @@
       <x:c r="J157" s="11" t="str"/>
       <x:c r="K157" s="11" t="str"/>
     </x:row>
-    <x:row r="158" ht="82.5" customHeight="1">
+    <x:row r="158" ht="88.5" customHeight="1">
       <x:c r="A158" s="6" t="str">
         <x:v>P016_Q07</x:v>
       </x:c>
@@ -5264,19 +5264,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D158" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E158" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F158" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G158" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...、VOCs、臭气浓度有组织集气管85%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩50%烘干烘干机烘干隧道密闭收集85%补焊电烙铁锡及其化合物有组织移动软管+伞型罩50%/项目生产过程产生的大气污染物主要为回流焊、波峰焊过程产生有机废气、焊接烟尘和少量异味；刷三防漆、烘干工序产生的有机废气和少量异味；补焊过程产生的焊锡废气等。（1）有组织废气（排气筒 G1）①波峰焊废气a）有机废气项目波峰焊过程使用助焊剂，会产生有机废气，污染因子为VOCs。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...营期环境影响和保护措施 | 1、废气表4-1 项目废气产污环节、污染物种类、排放形式及污染防治设施一览表产污环节生产设施污染物种类排放形式污染防治设施排放口类型收集方式收集效率处理效率污染防治设施名称及工艺是否为可行性技术焊接波峰焊机、回流焊机锡及其化合物、VOCs、臭气浓度有组织集气管85%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩50%烘干烘干机烘干隧道密闭收集85%补焊电烙铁锡及其化合物有组织移动软管+伞型罩50%/项目生产过程产生的大气污染物主要为回流焊、波峰焊过程产生有机废气、焊接烟尘和少量异味；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H158" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I158" s="7" t="b">
         <x:v>1</x:v>
@@ -5284,7 +5284,7 @@
       <x:c r="J158" s="11" t="str"/>
       <x:c r="K158" s="11" t="str"/>
     </x:row>
-    <x:row r="159" ht="82.5" customHeight="1">
+    <x:row r="159" ht="88.5" customHeight="1">
       <x:c r="A159" s="6" t="str">
         <x:v>P016_Q08</x:v>
       </x:c>
@@ -5295,19 +5295,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D159" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E159" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F159" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G159" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...影响和保护措施 | 1、废气表4-1 项目废气产污环节、污染物种类、排放形式及污染防治设施一览表产污环节生产设施污染物种类排放形式污染防治设施排放口类型收集方式收集效率处理效率污染防治设施名称及工艺是否为可行性技术焊接波峰焊机、回流焊机锡及其化合物、VOCs、臭气浓度有组织集气管85%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩50%烘干烘干机烘干隧道密闭收集85%补焊电烙铁锡及其化合物有组织移动软管+伞型罩50%/项目生产过程产生的大气污染物主要为回流焊...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...影响和保护措施 | 1、废气表4-1 项目废气产污环节、污染物种类、排放形式及污染防治设施一览表产污环节生产设施污染物种类排放形式污染防治设施排放口类型收集方式收集效率处理效率污染防治设施名称及工艺是否为可行性技术焊接波峰焊机、回流焊机锡及其化合物、VOCs、臭气浓度有组织集气管85%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩50%烘干烘干机烘干隧道密闭收集85%补焊电烙铁锡及其化合物有组织移动软管+伞型罩50%/项目生产过程产生的大气污染物主要为回流焊、波峰焊过程产生有机废气、焊接烟尘和少量异味；...</x:v>
       </x:c>
       <x:c r="H159" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则</x:v>
       </x:c>
       <x:c r="I159" s="7" t="b">
         <x:v>1</x:v>
@@ -5315,7 +5315,7 @@
       <x:c r="J159" s="11" t="str"/>
       <x:c r="K159" s="11" t="str"/>
     </x:row>
-    <x:row r="160" ht="82.5" customHeight="1">
+    <x:row r="160" ht="88.5" customHeight="1">
       <x:c r="A160" s="6" t="str">
         <x:v>P016_Q09</x:v>
       </x:c>
@@ -5326,19 +5326,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D160" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E160" s="6" t="str">
-        <x:v>请根据报告中的活性炭类型、碘值、装填量、过滤风速、停留时间和更换周期，判断活性炭治理参数是否充分。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F160" s="6" t="str">
-        <x:v>判断：活性炭参数需重点复核。依据：报告涉及活性炭类型、碘值、装填量、过滤风速、停留时间或更换周期。审核意见：建议检查设计风量、装填量、吸附容量、废活性炭产生量和更换周期是否相互匹配。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G160" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...过市政管道排入伦教污水处理厂处理废气处理设施一套波峰焊机、回流焊机、烘干机产生的废气经管道收集，补焊、刷三防漆工序产生的废气通过移动软管+伞型罩收集，然后经两级活性炭吸附处理后引至25m高排气筒G1排放一般固废间1个位于厂房一层，10 m2，用于一般固废暂存危险废物暂存点1个位于厂房一层，10 m2，危险废物暂存2、主要产品及产能搬迁前后，项目经营范围不变，项目主要从事电陶炉、电磁炉的生产制造及经营工作，项目建成后产品产量见表2-2。...</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...染防治设施排放口类型收集方式收集效率处理效率污染防治设施名称及工艺是否为可行性技术焊接波峰焊机、回流焊机锡及其化合物、VOCs、臭气浓度有组织集气管85%51%二级活性炭吸附（排气筒G1）是否一般排放口刷三防漆/VOCs、臭气浓度有组织移动软管+伞型罩50%烘干烘干机烘干隧道密闭收集85%补焊电烙铁锡及其化合物有组织移动软管+伞型罩50%/项目生产过程产生的大气污染物主要为回流焊、波峰焊过程产生有机废气、焊接烟尘和少量异味；刷三防漆、烘干工序产生的有机废气和少量异味；补焊过程产生的焊锡废气等。...</x:v>
       </x:c>
       <x:c r="H160" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；HJ_2026-2013；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则</x:v>
       </x:c>
       <x:c r="I160" s="7" t="b">
         <x:v>1</x:v>
@@ -5346,7 +5346,7 @@
       <x:c r="J160" s="11" t="str"/>
       <x:c r="K160" s="11" t="str"/>
     </x:row>
-    <x:row r="161" ht="82.5" customHeight="1">
+    <x:row r="161" ht="88.5" customHeight="1">
       <x:c r="A161" s="6" t="str">
         <x:v>P016_Q10</x:v>
       </x:c>
@@ -5357,19 +5357,19 @@
         <x:v>佛山市顺德区百洛电器有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D161" s="6" t="str">
-        <x:v>危险废物识别</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E161" s="6" t="str">
-        <x:v>请根据报告中的原辅材料、治理设施和危废清单，判断危险废物识别及暂存要求是否完整。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F161" s="6" t="str">
-        <x:v>判断：需核查危废识别完整性。依据：报告涉及废活性炭、废包装桶、危废代码或暂存措施。审核意见：建议结合原辅材料、治理设施和产污环节核查危废类别、代码、产生量和暂存能力是否完整。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G161" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...，其中夹层面积约800m2作为仓库，用于来料检验办公区、原辅材料和成品储存等二层共2500m2作为生产车间，主要用于电源线加工区、检验区、产品总装、备料区、成品暂存区等三层共2500m2作为生产车间，主要用于SMT生产线、波峰焊区、回流焊区、办公区、电子仓等四层共2500m2作为办公室，用于员工日常办公、会议、研发用途五层共2500m2作为仓库，用于验货区和成品储存等辅助工程办公室共2700m2用于员工日常办公用途储运工程仓库共6500m2用于原料和成品储存公用工程配电系统一套供应生产用电和办公生活用电给排水...</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...用厨房电器具制造 | 建设项目行业类别 | 三十五、电器机械和器材制造业38-家用电力器具制造385-其他（仅分割、焊接、组装的除外；年用非溶剂型低VOCs含量涂料10吨以下的除外）；建设性质 | 新建（迁建）□改建扩建□技术改造 | 建设项目申报情形 | 首次申报项目 □不予批准后再次申报项目□超五年重新审核项目 □重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 750 | 环保投资（万元） | 20；环保投资占比（%） | 2.67 | 施工工期 | 1个月；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H161" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；标准条款；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I161" s="7" t="b">
         <x:v>1</x:v>
@@ -5377,7 +5377,7 @@
       <x:c r="J161" s="11" t="str"/>
       <x:c r="K161" s="11" t="str"/>
     </x:row>
-    <x:row r="162" ht="82.5" customHeight="1">
+    <x:row r="162" ht="88.5" customHeight="1">
       <x:c r="A162" s="6" t="str">
         <x:v>P017_Q01</x:v>
       </x:c>
@@ -5385,22 +5385,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C162" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D162" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E162" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F162" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：判断是否为低VOCs涂料、油墨。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G162" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：判断是否为低VOCs涂料、油墨。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...广东省佛山市顺德区杏坛镇昌教工业园八路11号之三；地理坐标 | （东经： 113 度 9 分 44.711 秒，北纬： 22 度 46 分 12.601 秒）；国民经济行业类别 | C2641涂料制造 | 建设项目行业类别 | 二十三、化学原料和化学制品制造业26-44涂料、油墨、颜料及类似产品制造264,单纯物理分离、物理提纯、混合、分装的（不产生废水或挥发性有机物的除外）；建设性质 | 新建（迁建）改建扩建技术改造 | 建设项目申报情形 | 首次申报项目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；...</x:v>
       </x:c>
       <x:c r="H162" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification</x:v>
       </x:c>
       <x:c r="I162" s="7" t="b">
         <x:v>1</x:v>
@@ -5408,7 +5408,7 @@
       <x:c r="J162" s="11" t="str"/>
       <x:c r="K162" s="11" t="str"/>
     </x:row>
-    <x:row r="163" ht="82.5" customHeight="1">
+    <x:row r="163" ht="88.5" customHeight="1">
       <x:c r="A163" s="6" t="str">
         <x:v>P017_Q02</x:v>
       </x:c>
@@ -5416,22 +5416,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C163" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D163" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E163" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F163" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：落实清楚是否为单层密闭，如果是，提供原项目收集照片。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G163" s="6" t="str">
-        <x:v>Word批注/修改意见（第10条）写明：雷兆宇：落实清楚是否为单层密闭，如果是，提供原项目收集照片。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...目 不予批准后再次申报项目超五年重新审核项目 重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 100.00 | 环保投资（万元） | 10；环保投资占比（%） | 10 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H163" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I163" s="7" t="b">
         <x:v>1</x:v>
@@ -5439,7 +5439,7 @@
       <x:c r="J163" s="11" t="str"/>
       <x:c r="K163" s="11" t="str"/>
     </x:row>
-    <x:row r="164" ht="82.5" customHeight="1">
+    <x:row r="164" ht="88.5" customHeight="1">
       <x:c r="A164" s="6" t="str">
         <x:v>P017_Q03</x:v>
       </x:c>
@@ -5447,22 +5447,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C164" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D164" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E164" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集效率与处理效率相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F164" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：收集效率是否不合理。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G164" s="6" t="str">
-        <x:v>Word批注/修改意见（第8条）写明：雷兆宇：收集效率是否不合理。</x:v>
+        <x:v>建设项目工程分析（表格）写明：...术资料的基础上，根据《建设项目环境影响报告表编制技术指南（污染影响类）（试行）》，编制了《佛山市顺德区蓝顿涂料有限公司迁建项目环境影响报告表》。2、项目组成具体工程组成见下表：表2-1 项目工程组成类别工程名称工程内容依托工程情况迁建前建设内容迁建后建设内容主体工程主体生产车间生产车间1个，含投料分散区、研磨区、测试区、实验室和仓库，总面积约为2500m2生产车间1个，单层建筑，高度约为8m，含实验室及检测区273m2，试验喷漆房50m2，投料分散区300m2，研磨区50m2，打包区50m2，原材料区2000m2，成品区2000m2，一般固废暂存间50m2，危废暂存间50m2以及走道和公...</x:v>
       </x:c>
       <x:c r="H164" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I164" s="7" t="b">
         <x:v>1</x:v>
@@ -5470,7 +5470,7 @@
       <x:c r="J164" s="11" t="str"/>
       <x:c r="K164" s="11" t="str"/>
     </x:row>
-    <x:row r="165" ht="82.5" customHeight="1">
+    <x:row r="165" ht="88.5" customHeight="1">
       <x:c r="A165" s="6" t="str">
         <x:v>P017_Q04</x:v>
       </x:c>
@@ -5478,22 +5478,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C165" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D165" s="6" t="str">
-        <x:v>废水去向与冷却水</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E165" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废水去向与冷却水相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F165" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：五天是如何得出这数据，是否出货就需要对桶进行清洗，那是否要考虑最不利因素。一天两个批次，一个批次8个桶，一年清洗4800桶次，请核实。清洗废水应该根据桶的容积计算”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G165" s="6" t="str">
-        <x:v>Word批注/修改意见（第7条）写明：雷兆宇：五天是如何得出这数据，是否出货就需要对桶进行清洗，那是否要考虑最不利因素。一天两个批次，一个批次8个桶，一年清洗4800桶次，请核实。清洗废水应该根据桶的容积计算</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1、大气环境根据《佛山市顺德区生态环境保护“十四五”规划（2021-2025）》，顺德区全境为大气环境二类区，因此本项目所在区域属二类环境空气质量功能区，执行《环境空气质量标准》（GB3095-2012）及2018年修改单二级标准。①基本污染物环境质量现状及达标区判定根据《环境影响评价技术导则 大气环境》（HJ2.2-2018）第6.4.1.2条规定，国家或地方生态环境主管部门公开发布的城市环境空气质量达标情况，判断项目所在区域是否属于达标区，本报告采用佛山市生态环境局顺德分局关于发布2022年度...</x:v>
       </x:c>
       <x:c r="H165" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报</x:v>
       </x:c>
       <x:c r="I165" s="7" t="b">
         <x:v>1</x:v>
@@ -5501,7 +5501,7 @@
       <x:c r="J165" s="11" t="str"/>
       <x:c r="K165" s="11" t="str"/>
     </x:row>
-    <x:row r="166" ht="82.5" customHeight="1">
+    <x:row r="166" ht="88.5" customHeight="1">
       <x:c r="A166" s="6" t="str">
         <x:v>P017_Q05</x:v>
       </x:c>
@@ -5509,22 +5509,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C166" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D166" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E166" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F166" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：4+2有管理要求，活性炭两月一换，请修改。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G166" s="6" t="str">
-        <x:v>Word批注/修改意见（第22条）写明：雷兆宇：4+2有管理要求，活性炭两月一换，请修改。</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...t/a，则迁建后投料粉尘产生量为0.708t/a，实际生产中，项目投料过程为人工投料，大部分粉尘会因自身的重量沉降在设备附近。根据《未纳入排污许可管理行业适用的排污系数、物料衡算方法（试行）》可知，木工粉尘的沉降率为85%，而滑石粉和色粉粉尘的比重大于木料粉尘，更易沉降，本项目以85%计，沉降量为0.602t/a，沉降粉尘及时清理后作为固废处理。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H166" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I166" s="7" t="b">
         <x:v>1</x:v>
@@ -5532,7 +5532,7 @@
       <x:c r="J166" s="11" t="str"/>
       <x:c r="K166" s="11" t="str"/>
     </x:row>
-    <x:row r="167" ht="82.5" customHeight="1">
+    <x:row r="167" ht="88.5" customHeight="1">
       <x:c r="A167" s="6" t="str">
         <x:v>P017_Q06</x:v>
       </x:c>
@@ -5540,22 +5540,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C167" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D167" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E167" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F167" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：原项目申报仅有色浆?”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G167" s="6" t="str">
-        <x:v>Word批注/修改意见（第3条）写明：雷兆宇：原项目申报仅有色浆?</x:v>
+        <x:v>四、主要环境影响和保护措施（表格）写明：...气污染物排放源项目生产过程中主要的大气污染物为生产过程和实验、辊涂/试喷过程产生的颗粒物、VOCs、颗粒物和臭气浓度。废气产排情况一览表如表4-10。1.2废气源强核算①生产过程产生的投料粉尘 迁建后水性涂料生产过程中需投入滑石粉，色浆生产过程中需投入色粉，期间会产生投料粉尘，主要表征因子为颗粒物。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H167" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I167" s="7" t="b">
         <x:v>1</x:v>
@@ -5563,7 +5563,7 @@
       <x:c r="J167" s="11" t="str"/>
       <x:c r="K167" s="11" t="str"/>
     </x:row>
-    <x:row r="168" ht="82.5" customHeight="1">
+    <x:row r="168" ht="88.5" customHeight="1">
       <x:c r="A168" s="6" t="str">
         <x:v>P017_Q07</x:v>
       </x:c>
@@ -5571,22 +5571,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C168" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D168" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E168" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F168" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G168" s="6" t="str">
-        <x:v>四、主要环境影响和保护措施（表格）写明：...气污染物排放源项目生产过程中主要的大气污染物为生产过程和实验、辊涂/试喷过程产生的颗粒物、VOCs、颗粒物和臭气浓度。废气产排情况一览表如表4-10。1.2废气源强核算①生产过程产生的投料粉尘 迁建后水性涂料生产过程中需投入滑石粉，色浆生产过程中需投入色粉，期间会产生投料粉尘，主要表征因子为颗粒物。...</x:v>
+        <x:v>建设项目工程分析（表格）写明：...区绿点废水回收处理有限公司处置水帘机定期更换废水、设备清洗废水委托佛山市顺德区绿点废水回收处理有限公司处置/废气污染物防治措施投料、分散、研磨、打包废气经包围型集气罩收集和经密闭收集经“水帘机”处理的试喷废气一同通过“漆雾净化器+二级活性炭吸附设施”处理后引至15米排气筒FQ-04034高空排放投料、分散、研磨、打包废气经密闭正压收集、实验室废气经密闭正压+外部集气罩收集和经密闭正压收集通过“水帘机”处理后的试喷废气一起引至“漆雾净化器+二级活性炭吸附设施”处理后通过15米排气筒G1高空排放/实验投料、分散、烘干废气在车间内呈无组织形式扩散至厂界外噪声污染防治措施采用低噪声设备、做好设备...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H168" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I168" s="7" t="b">
         <x:v>1</x:v>
@@ -5594,7 +5594,7 @@
       <x:c r="J168" s="11" t="str"/>
       <x:c r="K168" s="11" t="str"/>
     </x:row>
-    <x:row r="169" ht="82.5" customHeight="1">
+    <x:row r="169" ht="88.5" customHeight="1">
       <x:c r="A169" s="6" t="str">
         <x:v>P017_Q08</x:v>
       </x:c>
@@ -5602,22 +5602,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C169" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D169" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E169" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F169" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G169" s="6" t="str">
-        <x:v>表4-10 项目大气各污染物产生及排放情况表（表格）写明：...集通过“水帘机”处理后的试喷废气一起引至“漆雾净化器+二级活性炭吸附设施”处理后通过15米排气筒G1高空排放，期间产生的颗粒物、TVOC有组织排放浓度均可达到《涂料、油墨及胶粘剂工业大气污染物排放标准》（GB37824-2019）中表2大气污染物特别排放限值。迁建后项目生产过程（含抽检）和实验、辊涂/试喷过程会产生少量的异味，异味强度一般在1-2级，折合臭气浓度为23-51（无量纲），项目异味随有机废气一起收集后引至“漆雾净化器+二级活性炭吸附装置”处理后通过15米排气筒（G1）排放。...</x:v>
+        <x:v>建设项目工程分析（表格）写明：...区绿点废水回收处理有限公司处置水帘机定期更换废水、设备清洗废水委托佛山市顺德区绿点废水回收处理有限公司处置/废气污染物防治措施投料、分散、研磨、打包废气经包围型集气罩收集和经密闭收集经“水帘机”处理的试喷废气一同通过“漆雾净化器+二级活性炭吸附设施”处理后引至15米排气筒FQ-04034高空排放投料、分散、研磨、打包废气经密闭正压收集、实验室废气经密闭正压+外部集气罩收集和经密闭正压收集通过“水帘机”处理后的试喷废气一起引至“漆雾净化器+二级活性炭吸附设施”处理后通过15米排气筒G1高空排放/实验投料、分散、烘干废气在车间内呈无组织形式扩散至厂界外噪声污染防治措施采用低噪声设备、做好设备...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H169" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I169" s="7" t="b">
         <x:v>1</x:v>
@@ -5625,7 +5625,7 @@
       <x:c r="J169" s="11" t="str"/>
       <x:c r="K169" s="11" t="str"/>
     </x:row>
-    <x:row r="170" ht="82.5" customHeight="1">
+    <x:row r="170" ht="88.5" customHeight="1">
       <x:c r="A170" s="6" t="str">
         <x:v>P017_Q09</x:v>
       </x:c>
@@ -5633,22 +5633,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C170" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D170" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E170" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F170" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G170" s="6" t="str">
-        <x:v>一、建设项目基本情况（表格）写明：...区绿点废水回收处理有限公司处置水帘机定期更换废水、设备清洗废水委托佛山市顺德区绿点废水回收处理有限公司处置/废气污染物防治措施投料、分散、研磨、打包废气经包围型集气罩收集和经密闭收集经“水帘机”处理的试喷废气一同通过“漆雾净化器+二级活性炭吸附设施”处理后引至15米排气筒FQ-04034高空排放投料、分散、研磨、打包废气经密闭正压收集、实验室废气经密闭正压+外部集气罩收集和经密闭正压收集通过“水帘机”处理后的试喷废气一起引至“漆雾净化器+二级活性炭吸附设施”处理后通过15米排气筒G1高空排放/实验投料、分散、...</x:v>
+        <x:v>建设项目工程分析（表格）写明：...市顺德区绿点废水回收处理有限公司处置/废气污染物防治措施投料、分散、研磨、打包废气经包围型集气罩收集和经密闭收集经“水帘机”处理的试喷废气一同通过“漆雾净化器+二级活性炭吸附设施”处理后引至15米排气筒FQ-04034高空排放投料、分散、研磨、打包废气经密闭正压收集、实验室废气经密闭正压+外部集气罩收集和经密闭正压收集通过“水帘机”处理后的试喷废气一起引至“漆雾净化器+二级活性炭吸附设施”处理后通过15米排气筒G1高空排放/实验投料、分散、烘干废气在车间内呈无组织形式扩散至厂界外噪声污染防治措施采用低噪声设备、做好设备隔音、减振处理、合理布局车间采用低噪声设备、做好设备隔音、减振处理、合...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H170" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I170" s="7" t="b">
         <x:v>1</x:v>
@@ -5656,7 +5656,7 @@
       <x:c r="J170" s="11" t="str"/>
       <x:c r="K170" s="11" t="str"/>
     </x:row>
-    <x:row r="171" ht="82.5" customHeight="1">
+    <x:row r="171" ht="88.5" customHeight="1">
       <x:c r="A171" s="6" t="str">
         <x:v>P017_Q10</x:v>
       </x:c>
@@ -5664,22 +5664,22 @@
         <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目修改意见.docx</x:v>
       </x:c>
       <x:c r="C171" s="6" t="str">
-        <x:v>| 佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
+        <x:v>佛山市顺德区蓝顿涂料有限公司迁建项目</x:v>
       </x:c>
       <x:c r="D171" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E171" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F171" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G171" s="6" t="str">
-        <x:v>表4-10 项目大气各污染物产生及排放情况表（表格）写明：...t/a | 排放形式 | 污染物产生情况 | 治理设施 | 污染物排放情况 | 排放时间h/a；产生量t/a | 产生浓度mg/m3 | 处理能力m3/h | 收集效率 | 治理工艺 | 处理效率 | 是否为可行性技术 | 排放浓度mg/m3 | 排放速率kg/h | 排放量t/a；...</x:v>
+        <x:v>建设项目工程分析（表格）写明：项目由来佛山市顺德区蓝顿涂料有限公司原项目位于佛山市顺德区杏坛镇七滘工业区百安公路以西17号地块之7，占地面积为3000m2，建筑面积为3000m2，中心经纬度为：东经113度6分19.965秒，北纬22度46分39.342秒，已于2016年5月16日取得“佛山市顺德区蓝顿涂料有限公司新建UV和水性涂料项目”环境影响报告批准证（20160129），并于2016年12月通过环保验收。2023年11月8日已完成排污许可证续证办理，排污许可证书编号为9[手机号已脱敏]778914001U，原审批规模为：年产UV涂料2500t、水性涂料500t和...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H171" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I171" s="7" t="b">
         <x:v>1</x:v>
@@ -5687,7 +5687,7 @@
       <x:c r="J171" s="11" t="str"/>
       <x:c r="K171" s="11" t="str"/>
     </x:row>
-    <x:row r="172" ht="82.5" customHeight="1">
+    <x:row r="172" ht="88.5" customHeight="1">
       <x:c r="A172" s="6" t="str">
         <x:v>P018_Q01</x:v>
       </x:c>
@@ -5698,19 +5698,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D172" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>国民经济行业分类判断</x:v>
       </x:c>
       <x:c r="E172" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断VOCs源强核算相关内容是否需要补充或修改。</x:v>
+        <x:v>请结合报告中的产品方案、原辅材料、主要设备和生产工艺，判断报告填报的国民经济行业类别是否合理。</x:v>
       </x:c>
       <x:c r="F172" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：根据现时收集效率、处理效率进行重新核算。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需结合报告填报内容进一步核查。报告现有内容涉及产品方案、原辅材料、设备或工艺信息，应与填报的国民经济行业类别相互印证。建议核查产品主导属性、关键生产工艺和行业代码是否一致，避免仅按企业名称或单一产品名称判断。</x:v>
       </x:c>
       <x:c r="G172" s="6" t="str">
-        <x:v>Word批注/修改意见（第7条）写明：雷兆宇：根据现时收集效率、处理效率进行重新核算。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...设地点 | 佛山市顺德区杏坛镇逢简工业区横二路3号厂区3号车间；地理坐标 | （ 113 度 8 分 34.481 秒， 22 度 48 分32.929 秒）；国民经济行业类别 | C3360金属表面处理及热处理加工 | 建设项目行业类别 | 三十、“金属制品业33”中的67金属表面处理及热处理加工（其他）；建设性质 | 新建（迁建）改建扩建技术改造 | 建设项目申报情形 | 首次申报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H172" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#1_塑料橡胶行业分类说明、national_economic_classification；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I172" s="7" t="b">
         <x:v>1</x:v>
@@ -5718,7 +5718,7 @@
       <x:c r="J172" s="11" t="str"/>
       <x:c r="K172" s="11" t="str"/>
     </x:row>
-    <x:row r="173" ht="82.5" customHeight="1">
+    <x:row r="173" ht="88.5" customHeight="1">
       <x:c r="A173" s="6" t="str">
         <x:v>P018_Q02</x:v>
       </x:c>
@@ -5729,19 +5729,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D173" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>环评投资核算</x:v>
       </x:c>
       <x:c r="E173" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断原辅材料与VOCs物料相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的总投资、环保投资构成和污染防治措施，判断环保投资核算是否完整、合理。</x:v>
       </x:c>
       <x:c r="F173" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：数据应采用近三年的检测报告。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查环保投资构成是否完整。报告列明总投资或环保投资时，应与废气、废水、噪声、固废、风险防范等污染防治措施对应。建议核查环保投资明细是否覆盖主要治理设施，金额和占比是否前后一致。</x:v>
       </x:c>
       <x:c r="G173" s="6" t="str">
-        <x:v>Word批注/修改意见（第8条）写明：雷兆宇：数据应采用近三年的检测报告。</x:v>
+        <x:v>一、建设项目基本情况（表格）写明：...报项目不予批准后再次申报项目超五年重新审核项目重大变动重新报批项目；项目审批（核准/备案）部门（选填） | 无 | 项目审批（核准/备案）文号（选填） | 无；总投资（万元） | 200 | 环保投资（万元） | 20；环保投资占比（%） | 10 | 施工工期 | 1个月</x:v>
       </x:c>
       <x:c r="H173" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：环评投资核算</x:v>
       </x:c>
       <x:c r="I173" s="7" t="b">
         <x:v>1</x:v>
@@ -5749,7 +5749,7 @@
       <x:c r="J173" s="11" t="str"/>
       <x:c r="K173" s="11" t="str"/>
     </x:row>
-    <x:row r="174" ht="82.5" customHeight="1">
+    <x:row r="174" ht="88.5" customHeight="1">
       <x:c r="A174" s="6" t="str">
         <x:v>P018_Q03</x:v>
       </x:c>
@@ -5760,19 +5760,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D174" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>建设内容编制完整性</x:v>
       </x:c>
       <x:c r="E174" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废气收集形式与设计风量相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的工程组成、产品方案、原辅材料、设备清单和工艺流程，判断建设内容是否足以支撑后续产污分析。</x:v>
       </x:c>
       <x:c r="F174" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：烘干工序是否有必要上集气罩收集，增大风量稀释VOCs浓度，增加活性炭使用量以及处理效率。如若需要可单独一个排放口，专门排放燃烧废气”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查建设内容与产污分析的闭合性。报告应使工程组成、产品方案、原辅材料、设备清单、工艺流程和产污环节能够相互对应。建议核查是否存在设备或原辅材料未进入工艺分析、工艺环节未进入源强核算、治理措施与产污环节不匹配等问题。</x:v>
       </x:c>
       <x:c r="G174" s="6" t="str">
-        <x:v>Word批注/修改意见（第12条）写明：雷兆宇：烘干工序是否有必要上集气罩收集，增大风量稀释VOCs浓度，增加活性炭使用量以及处理效率。如若需要可单独一个排放口，专门排放燃烧废气</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：建设内容 | 1、工程组成项目租用一栋单层工业厂房作为生产经营场所，所在厂房高度约为8m，厂房占地3795m2，项目工程组成见下表。表2-1 本项目工程组成项目工程名称迁扩建前迁扩建后基本信息建设地点位于佛山市顺德区杏坛镇麦村七滘工业区九路36号之三，占地面积2880m2，建筑面积2880m2位于佛山市顺德区杏坛镇逢简工业区横二路3号厂区3号车间，占地面积3795m2，建筑面积3795m2生产工艺主要有钻孔、焊接、除油、表调、陶化、清洗、烘干、喷粉、固化等主要有钻孔、焊接、除油、陶化、清洗烘干、喷粉、固化等主体工程...</x:v>
       </x:c>
       <x:c r="H174" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：建设内容编制完整性判断</x:v>
       </x:c>
       <x:c r="I174" s="7" t="b">
         <x:v>1</x:v>
@@ -5780,7 +5780,7 @@
       <x:c r="J174" s="11" t="str"/>
       <x:c r="K174" s="11" t="str"/>
     </x:row>
-    <x:row r="175" ht="82.5" customHeight="1">
+    <x:row r="175" ht="88.5" customHeight="1">
       <x:c r="A175" s="6" t="str">
         <x:v>P018_Q04</x:v>
       </x:c>
@@ -5791,19 +5791,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D175" s="6" t="str">
-        <x:v>废水去向与冷却水</x:v>
+        <x:v>环境质量现状数据引用</x:v>
       </x:c>
       <x:c r="E175" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断废水去向与冷却水相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告引用的环境质量公报、监测数据和功能区划，判断环境质量现状数据引用是否准确、充分。</x:v>
       </x:c>
       <x:c r="F175" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：根据《佛山市生态环境局佛山市水利局关于进一步加强工业企业废水污染防治的函》不再审批零星废水外运处置，建议除油、陶化废水通过“混凝沉淀处置”有条件上“混凝沉淀+生化处理”进行回用”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查现状数据来源、年份和适用性。报告引用环境质量公报或监测数据时，应与项目所在区域、评价因子和功能区划相匹配。建议核查数据年份是否合理、因子是否覆盖项目特征污染物、引用结论是否与现状数据一致。</x:v>
       </x:c>
       <x:c r="G175" s="6" t="str">
-        <x:v>Word批注/修改意见（第3条）写明：雷兆宇：根据《佛山市生态环境局佛山市水利局关于进一步加强工业企业废水污染防治的函》不再审批零星废水外运处置，建议除油、陶化废水通过“混凝沉淀处置”有条件上“混凝沉淀+生化处理”进行回用</x:v>
+        <x:v>三、区域环境质量现状、环境保护目标及评价标准（表格）写明：区域环境质量现状 | 1、大气环境质量现状根据《佛山市顺德区人民政府办公室关于印发佛山市顺德区生态环境保护“十四五”规划（2021-2025）的通知》（顺府办发〔2022〕16号），项目所在区域为环境空气质量功能二类区，执行《环境空气质量标准》（GB3095-2012）及2018年修改单中的二级标准。（1）基本污染物环境质量现状为评价项目所在地环境空气质量现状，引用佛山市生态环境局顺德分局发布的《2022年度佛山市顺德区环境质量状况公报》中的数据，项目所在区域基本污染物环境质量现状评价如下：表3-1 2022年顺德区（...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H175" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#6_顺德区生态环境状况公报；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I175" s="7" t="b">
         <x:v>1</x:v>
@@ -5811,7 +5811,7 @@
       <x:c r="J175" s="11" t="str"/>
       <x:c r="K175" s="11" t="str"/>
     </x:row>
-    <x:row r="176" ht="82.5" customHeight="1">
+    <x:row r="176" ht="88.5" customHeight="1">
       <x:c r="A176" s="6" t="str">
         <x:v>P018_Q05</x:v>
       </x:c>
@@ -5822,19 +5822,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D176" s="6" t="str">
-        <x:v>活性炭治理参数</x:v>
+        <x:v>运营期产污系数适用性</x:v>
       </x:c>
       <x:c r="E176" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断活性炭治理参数相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的行业代码、产品类型、生产工艺和核算基准，判断运营期产污系数选取是否合理。</x:v>
       </x:c>
       <x:c r="F176" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：活性炭不再生适用于10000以下，请确定？是否放该表”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查产污系数适用条件。报告使用产污系数时，应说明行业代码、产品类型、工艺类型和核算基准与系数来源一致。建议核查是否存在跨行业套用、工艺不匹配、核算基准不清或未说明系数来源的问题。</x:v>
       </x:c>
       <x:c r="G176" s="6" t="str">
-        <x:v>Word批注/修改意见（第13条）写明：雷兆宇：活性炭不再生适用于10000以下，请确定？是否放该表</x:v>
+        <x:v>表4-2 废气污染物源强核算结果及相关参数一览表（表格）写明：...量为0.01t/a，产生速率为0.017kg/h。焊接烟尘在车间内无组织排放。③喷粉粉尘项目喷粉过程会产生粉尘，以颗粒物计。参考《排放源统计调查产排污核算方法和系数手册—33 金属制品业、34 通用设备制造业、35 专用设备制造业、36 汽车制造业、37 铁路、船舶、航空航天和其他运输设备制造业、431 金属制品修理、432 通用设备修理、433 专用设备修理、434 铁路、船舶、航空航天等运输设备修理（不包括电镀工艺）行业系数手册》，喷塑工艺的颗粒物产污系数为“300kg/t-原料”。...</x:v>
       </x:c>
       <x:c r="H176" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数</x:v>
       </x:c>
       <x:c r="I176" s="7" t="b">
         <x:v>1</x:v>
@@ -5842,7 +5842,7 @@
       <x:c r="J176" s="11" t="str"/>
       <x:c r="K176" s="11" t="str"/>
     </x:row>
-    <x:row r="177" ht="82.5" customHeight="1">
+    <x:row r="177" ht="88.5" customHeight="1">
       <x:c r="A177" s="6" t="str">
         <x:v>P018_Q06</x:v>
       </x:c>
@@ -5853,19 +5853,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D177" s="6" t="str">
-        <x:v>真实批注/修改意见</x:v>
+        <x:v>运营期产污系数与定量核算</x:v>
       </x:c>
       <x:c r="E177" s="6" t="str">
-        <x:v>请根据报告原文及批注/修改意见，判断真实批注/修改意见相关内容是否需要补充或修改。</x:v>
+        <x:v>请根据报告中的原辅材料用量、产品产量、产污系数和计算过程，判断污染物源强核算是否准确、前后一致。</x:v>
       </x:c>
       <x:c r="F177" s="6" t="str">
-        <x:v>判断：存在审核关注点，建议人工优先复核。依据：Word批注/修改意见指出“雷兆宇：备注说明综合利用率计算。”。审核意见：请核查批注意见是否已在报告相应章节、表格或核算过程中落实，并补充必要依据或修改不一致内容。</x:v>
+        <x:v>判断：需核查源强核算链条。报告应能从原辅材料用量、产品产量、VOCs含量或产污系数推导出产生量、收集量、处理量和排放量。建议核查计算过程、单位换算、效率取值和正文、附表、总量控制指标是否一致。</x:v>
       </x:c>
       <x:c r="G177" s="6" t="str">
-        <x:v>Word批注/修改意见（第1条）写明：雷兆宇：备注说明综合利用率计算。</x:v>
+        <x:v>表4-2 废气污染物源强核算结果及相关参数一览表（表格）写明：...）高度（m）直径（m）温度（℃）DA001无300003000151.525一般排气筒113°8′34.33″E22°48′31.99″N表4-4 污染源非正常排放量核算表序号污染源非正常排放原因污染物非正常排放浓度/(mg/m3)非正常排放速率/(kg/h）单次持续时间/h年发生频次/次应对措施1DA001治理设施故障VOCs1.3330.0400.51定期检查设备，发现问题立即停止生产表4-5 废气污染源监测点位、监测指标及监测频次一览表有组织排放生产单元监测点位监测指标监测频次执行标准烘干、固化排气筒DA001VOCs一年一次《固定污染源挥发性有机物综合排放标准》（DB44/236...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H177" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；真实批注/修改意见；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：运营期间产污系数与定量核算判定；Dify工作流_标准库：#9_塑料制品业产污系数；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I177" s="7" t="b">
         <x:v>1</x:v>
@@ -5873,7 +5873,7 @@
       <x:c r="J177" s="11" t="str"/>
       <x:c r="K177" s="11" t="str"/>
     </x:row>
-    <x:row r="178" ht="82.5" customHeight="1">
+    <x:row r="178" ht="88.5" customHeight="1">
       <x:c r="A178" s="6" t="str">
         <x:v>P018_Q07</x:v>
       </x:c>
@@ -5884,19 +5884,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D178" s="6" t="str">
-        <x:v>VOCs源强核算</x:v>
+        <x:v>废气收集形式及排气量</x:v>
       </x:c>
       <x:c r="E178" s="6" t="str">
-        <x:v>请根据报告中的产污系数、VOCs产生量、收集量、处理量和排放量，判断源强核算是否具有可复核性。</x:v>
+        <x:v>请根据报告中的产污工序、废气产生位置、收集方式和排气去向，判断废气收集形式是否合理。</x:v>
       </x:c>
       <x:c r="F178" s="6" t="str">
-        <x:v>判断：需核查核算链条是否可复核。依据：报告涉及VOCs或非甲烷总烃产生、收集、处理、排放或产污系数。审核意见：建议检查原辅材料用量、VOCs含量、产污系数、收集效率和处理效率是否前后一致。</x:v>
+        <x:v>判断：需核查废气收集方式与产污工序是否匹配。报告应说明废气产生位置、收集方式、排气去向和治理设施连接关系。建议核查开放式作业是否仅用高效率收集取值、密闭或集气罩设置是否有空间和运行条件支撑。</x:v>
       </x:c>
       <x:c r="G178" s="6" t="str">
-        <x:v>表4-2 废气污染物源强核算结果及相关参数一览表（表格）写明：...）高度（m）直径（m）温度（℃）DA001无300003000151.525一般排气筒113°8′34.33″E22°48′31.99″N表4-4 污染源非正常排放量核算表序号污染源非正常排放原因污染物非正常排放浓度/(mg/m3)非正常排放速率/(kg/h）单次持续时间/h年发生频次/次应对措施1DA001治理设施故障VOCs1.3330.0400.51定期检查设备，发现问题立即停止生产表4-5 废气污染源监测点位、监测指标及监测频次一览表有组织排放生产单元监测点位监测指标监测频次执行标准烘干、固化排气筒D...</x:v>
+        <x:v>表4-2 废气污染物源强核算结果及相关参数一览表（表格）写明：表4-3 项目排气筒基本情况表排气筒参数排气筒类型地理坐标编号许可证编号废气量（m3/h）排放时间（h）高度（m）直径（m）温度（℃）DA001无300003000151.525一般排气筒113°8′34.33″E22°48′31.99″N表4-4 污染源非正常排放量核算表序号污染源非正常排放原因污染物非正常排放浓度/(mg/m3)非正常排放速率/(kg/h）单次持续时间/h年发生频次/次应对措施1DA001治理设施故障VOCs1.3330.0400.51定期检查设备，发现问题立即停止生产表4-5 废气污染源监测点位、监测指标及...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H178" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库：#9_塑料制品业产污系数；标准条款；QA测试集</x:v>
+        <x:v>报告原文；Dify工作流：废气收集形式及排气量计算；GB_37822-2019；DB44_2367-2022；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I178" s="7" t="b">
         <x:v>1</x:v>
@@ -5904,7 +5904,7 @@
       <x:c r="J178" s="11" t="str"/>
       <x:c r="K178" s="11" t="str"/>
     </x:row>
-    <x:row r="179" ht="82.5" customHeight="1">
+    <x:row r="179" ht="88.5" customHeight="1">
       <x:c r="A179" s="6" t="str">
         <x:v>P018_Q08</x:v>
       </x:c>
@@ -5915,19 +5915,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D179" s="6" t="str">
-        <x:v>原辅材料与VOCs物料</x:v>
+        <x:v>废气收集效率判定</x:v>
       </x:c>
       <x:c r="E179" s="6" t="str">
-        <x:v>请根据报告中的原辅材料及VOCs含量信息，判断涉VOCs物料识别和源强核算依据是否充分。</x:v>
+        <x:v>请根据报告中的废气收集形式、控制风速、集气罩与产污点距离和收集效率取值，判断收集效率是否有充分依据。</x:v>
       </x:c>
       <x:c r="F179" s="6" t="str">
-        <x:v>判断：证据需重点复核。依据：报告涉及胶水、涂料、油墨、清洗剂或VOCs含量等原辅材料信息。审核意见：建议核查VOCs含量证明、MSDS或检测报告是否支撑源强核算和低VOCs物料判定。</x:v>
+        <x:v>判断：需核查收集效率取值依据。报告应使收集效率与密闭程度、集气罩形式、控制风速、产污点距离和运行管理条件相匹配。建议补充效率取值依据，核查是否存在开放或半开放工序套用过高收集效率的问题。</x:v>
       </x:c>
       <x:c r="G179" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...1条手动前处理线，主要工序有除油、陶化、清洗、烘干、喷粉、固化等机加工区/约100m2，用于产品的机加工，主要工序有钻孔和焊接仓储工程普通仓库约400m2，储存原辅材料和产品约1345m2，储存原辅材料和产品化学品仓库/约50m2，储存除油剂、陶化剂、粉末涂料等化学用品辅助工程办公室约100m2，供日常办公使用约300m2，供日常办公使用公用工程给排水系统供水来源为市政自来水，生活污水经独立的生活污水处理设施处理后排入附近内河涌。...</x:v>
+        <x:v>表4-2 废气污染物源强核算结果及相关参数一览表（表格）写明：...年一次广东省关于贯彻落实《工业炉窑大气污染综合治理方案》的实施意见（粤环函[2019]1112号）臭气浓度一年一次《恶臭污染物排放标准》（GB14554-93）无组织排放监测点位监测指标监测频次执行标准厂内NMHC一年一次《固定污染源挥发性有机物综合排放标准》（DB44/2367-2022）厂界颗粒物、SO2、NOx一年一次广东省《大气污染物排放限值》（DB44/27-2001）臭气浓度一年一次《恶臭污染物排放标准》（GB14554-93）3、废气污染物排放源强核算过程（1）颗粒物①钻孔粉尘项目的少量工件钻孔过程会产生少量粉尘。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H179" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流：废气收集效率判定；GB_37822-2019；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I179" s="7" t="b">
         <x:v>1</x:v>
@@ -5935,7 +5935,7 @@
       <x:c r="J179" s="11" t="str"/>
       <x:c r="K179" s="11" t="str"/>
     </x:row>
-    <x:row r="180" ht="82.5" customHeight="1">
+    <x:row r="180" ht="88.5" customHeight="1">
       <x:c r="A180" s="6" t="str">
         <x:v>P018_Q09</x:v>
       </x:c>
@@ -5946,19 +5946,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D180" s="6" t="str">
-        <x:v>废气收集形式与设计风量</x:v>
+        <x:v>活性炭治理设施参数</x:v>
       </x:c>
       <x:c r="E180" s="6" t="str">
-        <x:v>请根据报告中的废气收集形式、集气罩参数、控制风速和设计风量，判断风量设计是否具有可复核性。</x:v>
+        <x:v>请根据报告中的废气风量、VOCs进口浓度、活性炭类型、装填厚度、过滤风速和停留时间，判断活性炭治理设施参数是否合理。</x:v>
       </x:c>
       <x:c r="F180" s="6" t="str">
-        <x:v>判断：证据不足时应补充风量计算依据。依据：报告涉及集气罩、密闭、垂帘、控制风速或设计风量。审核意见：建议补充罩口尺寸、控制面风速、集气罩至污染源距离和设计风量计算过程。</x:v>
+        <x:v>判断：需核查活性炭设施参数完整性。报告应说明活性炭类型、碘值、装填量或装填厚度、过滤风速、停留时间和适用风量。建议核查治理设施参数是否能支撑处理效率取值，并与废气风量和VOCs负荷相匹配。</x:v>
       </x:c>
       <x:c r="G180" s="6" t="str">
-        <x:v>二、建设项目工程分析（表格）写明：...气通过集气管道接入固化炉顶部设置的排气口收集，收集后通过“喷淋塔+UV光解+活性炭吸附”处理后通过15m排气筒（FQ-13728）排放在固化炉的工件进出口处设置集气罩进行收集，收集后经“喷淋塔+干式过滤+二级活性炭吸附”装置处理后通过15m排气筒（DA001）高空排放燃烧废气/经烘干炉和固化线进出口设置的集气罩进行收集，收集后通过15m排气筒（DA001）高空排放噪声设备噪声厂房隔声、风机消声、设备减振厂房隔声、风机消声、设备减振固废生活垃圾定期交由环卫部门清理定期交由环卫部门清理一般工业固体废物定点收集后交...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...排放经设备自带的集尘系统收集和滤筒除尘器处理后在车间无组织排放固化有机废气固化有机废气通过集气管道接入固化炉顶部设置的排气口收集，收集后通过“喷淋塔+UV光解+活性炭吸附”处理后通过15m排气筒（FQ-13728）排放在固化炉的工件进出口处设置集气罩进行收集，收集后经“喷淋塔+干式过滤+二级活性炭吸附”装置处理后通过15m排气筒（DA001）高空排放燃烧废气/经烘干炉和固化线进出口设置的集气罩进行收集，收集后通过15m排气筒（DA001）高空排放噪声设备噪声厂房隔声、风机消声、设备减振厂房隔声、风机消声、设备减振固废生活垃圾定期交由环卫部门清理定期交由环卫部门清理一般工业固体废物定点收集...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H180" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流_标准库：HJ_2026-2013、DB44_2367-2022；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I180" s="7" t="b">
         <x:v>1</x:v>
@@ -5966,7 +5966,7 @@
       <x:c r="J180" s="11" t="str"/>
       <x:c r="K180" s="11" t="str"/>
     </x:row>
-    <x:row r="181" ht="82.5" customHeight="1">
+    <x:row r="181" ht="88.5" customHeight="1">
       <x:c r="A181" s="6" t="str">
         <x:v>P018_Q10</x:v>
       </x:c>
@@ -5977,19 +5977,19 @@
         <x:v>佛山市镪优金属制品有限公司迁扩建项目</x:v>
       </x:c>
       <x:c r="D181" s="6" t="str">
-        <x:v>废气收集效率与处理效率</x:v>
+        <x:v>环境风险物质识别</x:v>
       </x:c>
       <x:c r="E181" s="6" t="str">
-        <x:v>请根据报告中的收集效率、处理效率和废气治理工艺，判断效率取值是否需要补充依据。</x:v>
+        <x:v>请根据报告中的原辅材料、危险废物、风险物质和贮存方式，判断环境风险物质识别是否完整。</x:v>
       </x:c>
       <x:c r="F181" s="6" t="str">
-        <x:v>判断：效率取值需补充依据。依据：报告涉及收集效率、处理效率或治理效率取值。审核意见：建议核查收集形式是否与效率取值匹配，处理效率是否有设备参数、规范或类案经验支撑。</x:v>
+        <x:v>判断：需核查环境风险物质识别是否完整。报告应结合原辅材料、危险废物、最大贮存量和风险物质临界量判断风险等级。建议核查涉VOCs液态物料、危废、燃料或化学品是否纳入风险物质识别，Q值计算是否有依据。</x:v>
       </x:c>
       <x:c r="G181" s="6" t="str">
-        <x:v>四、主要环境影响和护措施（表格）写明：...目废气产污环节、污染物项目、排放形式及污染防治设施见下表。表4-1 项目废气治理设施一览表产污环节污染物项目排放形式污染防治技术排放口编号污染防治设施名称及工艺收集效率（%）去除效率（%）是否为可行技术焊接工序颗粒物无组织/////喷粉工序颗粒物无组织滤筒除尘器9599是/固化工序VOCs有组织喷淋塔+干式过滤+二级活性炭吸附5075是DA001天然气燃烧SO2、NOX和烟尘有组织////DA001；产污环节 | 污染物项目 | 排放形式 | 污染防治技术 | 排放口编号；...</x:v>
+        <x:v>二、建设项目工程分析（表格）写明：...的机加工，主要工序有钻孔和焊接仓储工程普通仓库约400m2，储存原辅材料和产品约1345m2，储存原辅材料和产品化学品仓库/约50m2，储存除油剂、陶化剂、粉末涂料等化学用品辅助工程办公室约100m2，供日常办公使用约300m2，供日常办公使用公用工程给排水系统供水来源为市政自来水，生活污水经独立的生活污水处理设施处理后排入附近内河涌。...；后台参考：该问题在修改意见中被指出，人工审核时可优先核查。</x:v>
       </x:c>
       <x:c r="H181" s="6" t="str">
-        <x:v>报告原文；Dify工作流_标准库；GB_37822-2019；DB44_2367-2022；经验规则</x:v>
+        <x:v>报告原文；Dify工作流；环境风险相关导则；经验规则；后台来源：真实修改意见；题面已去除修改意见信息</x:v>
       </x:c>
       <x:c r="I181" s="7" t="b">
         <x:v>1</x:v>
@@ -6000,7 +6000,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e579b6156e34bd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf814a254910f4924"/>
   </x:tableParts>
 </x:worksheet>
 </file>